--- a/Measurements/Efficiency_DutyCycleVariation_Measurements/Type4/Type4_wirkungsgrad.xlsx
+++ b/Measurements/Efficiency_DutyCycleVariation_Measurements/Type4/Type4_wirkungsgrad.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FHTW_Daniel_Stevic\Masterarbeit\Messungen\Wirkungsgradmessung\Type4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6CC8F3-4A97-422A-BA61-1BD842B29569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9533119-EB04-4767-A94B-80BB6D46CB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Uebersetzung_ccm" sheetId="1" r:id="rId1"/>
     <sheet name="Wirkungsgradkurven" sheetId="5" r:id="rId2"/>
     <sheet name="Bildverzeichnis" sheetId="3" r:id="rId3"/>
     <sheet name="Messmittel" sheetId="4" r:id="rId4"/>
+    <sheet name="Simulationsvergleich" sheetId="6" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Uebersetzung_ccm!$B$7:$N$229</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="101">
   <si>
     <t>Berechnet für Continuous Conduction Mode</t>
   </si>
@@ -338,15 +342,43 @@
   <si>
     <t>IL21</t>
   </si>
+  <si>
+    <t>P1[W]</t>
+  </si>
+  <si>
+    <t>P2[W]</t>
+  </si>
+  <si>
+    <t>Simulation 12V\_24V\_20$\Omega$</t>
+  </si>
+  <si>
+    <t>Simulation 24V\_48V\_25$\Omega$</t>
+  </si>
+  <si>
+    <t>Messung 12V\_24V\_20$\Omega$</t>
+  </si>
+  <si>
+    <t>Messung 24V\_48V\_25$\Omega$</t>
+  </si>
+  <si>
+    <t>η [\%]</t>
+  </si>
+  <si>
+    <t>Arbeitspunkt Betrachtung</t>
+  </si>
+  <si>
+    <t>d [\%]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -381,6 +413,28 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -436,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -481,10 +535,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -502,6 +583,3486 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-AT" sz="1500" b="1" i="0"/>
+              <a:t>Übersetzung</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-AT" sz="1500" b="1" i="0" baseline="0"/>
+              <a:t>sverhältnis über Tastgrad im KLB des Typ 4 bei verschiedenen Eingangsspannungen</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-AT" sz="1500" b="1" i="0"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-AT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.839928037210389E-2"/>
+          <c:y val="5.7540807399075113E-2"/>
+          <c:w val="0.93281951122804196"/>
+          <c:h val="0.87044422955902445"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Übersetzung_Ideal</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>(Uebersetzung_ccm!$B$8,Uebersetzung_ccm!$B$44,Uebersetzung_ccm!$B$77,Uebersetzung_ccm!$B$105,Uebersetzung_ccm!$B$133,Uebersetzung_ccm!$B$158,Uebersetzung_ccm!$B$181,Uebersetzung_ccm!$B$202,Uebersetzung_ccm!$B$218)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.000">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.000">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.000">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.000">
+                  <c:v>0.42857142857142855</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.000">
+                  <c:v>0.45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(Uebersetzung_ccm!$C$8,Uebersetzung_ccm!$C$44,Uebersetzung_ccm!$C$77,Uebersetzung_ccm!$C$105,Uebersetzung_ccm!$C$133,Uebersetzung_ccm!$C$158,Uebersetzung_ccm!$C$181,Uebersetzung_ccm!$C$202,Uebersetzung_ccm!$C$218)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.1111111111111112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.0000000000000009</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.9999999999999973</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.000000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2AF5-431E-91A6-3AB4157C3616}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>3,3 V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>(Uebersetzung_ccm!$B$8,Uebersetzung_ccm!$B$44,Uebersetzung_ccm!$B$77,Uebersetzung_ccm!$B$105,Uebersetzung_ccm!$B$133,Uebersetzung_ccm!$B$158,Uebersetzung_ccm!$B$181,Uebersetzung_ccm!$B$202,Uebersetzung_ccm!$B$218)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.000">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.000">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.000">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.000">
+                  <c:v>0.42857142857142855</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.000">
+                  <c:v>0.45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(Uebersetzung_ccm!$I$8,Uebersetzung_ccm!$I$44,Uebersetzung_ccm!$I$77,Uebersetzung_ccm!$I$105,Uebersetzung_ccm!$I$133,Uebersetzung_ccm!$I$158,Uebersetzung_ccm!$I$181,Uebersetzung_ccm!$I$202,Uebersetzung_ccm!$I$218)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.93134183804724502</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0467652047492124</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4024113174396413</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7065319755206112</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.6593197278911562</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.6053268765133177</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.4872881355932206</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.5228008593820928</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.7985825054519022</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2AF5-431E-91A6-3AB4157C3616}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>5 V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>(Uebersetzung_ccm!$B$16,Uebersetzung_ccm!$B$52,Uebersetzung_ccm!$B$84,Uebersetzung_ccm!$B$112,Uebersetzung_ccm!$B$140,Uebersetzung_ccm!$B$164,Uebersetzung_ccm!$B$187,Uebersetzung_ccm!$B$207,Uebersetzung_ccm!$B$223)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.000">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.000">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.000">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.000">
+                  <c:v>0.42857142857142855</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.000">
+                  <c:v>0.45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(Uebersetzung_ccm!$I$16,Uebersetzung_ccm!$I$52,Uebersetzung_ccm!$I$84,Uebersetzung_ccm!$I$112,Uebersetzung_ccm!$I$140,Uebersetzung_ccm!$I$164,Uebersetzung_ccm!$I$187,Uebersetzung_ccm!$I$207,Uebersetzung_ccm!$I$223)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.0010583465875795</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1211909792953998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5027845978801126</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.8164462265844754</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.8076255115280966</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.7986045860738491</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.7889726299087663</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.9285628670741941</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.442240793314406</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-2AF5-431E-91A6-3AB4157C3616}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>9 V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>(Uebersetzung_ccm!$B$24,Uebersetzung_ccm!$B$59,Uebersetzung_ccm!$B$90,Uebersetzung_ccm!$B$118,Uebersetzung_ccm!$B$146,Uebersetzung_ccm!$B$169,Uebersetzung_ccm!$B$192,Uebersetzung_ccm!$B$211,Uebersetzung_ccm!$B$228)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.000">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.000">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.000">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.000">
+                  <c:v>0.42857142857142855</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.000">
+                  <c:v>0.45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(Uebersetzung_ccm!$I$24,Uebersetzung_ccm!$I$59,Uebersetzung_ccm!$I$90,Uebersetzung_ccm!$I$118,Uebersetzung_ccm!$I$146,Uebersetzung_ccm!$I$169,Uebersetzung_ccm!$I$192,Uebersetzung_ccm!$I$211,Uebersetzung_ccm!$I$228)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1.0737276812826431</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1877997327192318</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5887110212515414</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.9154228855721396</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9364815061498155</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.9995559995559988</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.0452619200816482</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.3854204859838015</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11.418596918984818</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-2AF5-431E-91A6-3AB4157C3616}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>12 V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>(Uebersetzung_ccm!$B$31,Uebersetzung_ccm!$B$66,Uebersetzung_ccm!$B$96,Uebersetzung_ccm!$B$123,Uebersetzung_ccm!$B$151,Uebersetzung_ccm!$B$173,Uebersetzung_ccm!$B$197,Uebersetzung_ccm!$B$215)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.000">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.000">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.000">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.000">
+                  <c:v>0.42857142857142855</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(Uebersetzung_ccm!$I$31,Uebersetzung_ccm!$I$66,Uebersetzung_ccm!$I$96,Uebersetzung_ccm!$I$123,Uebersetzung_ccm!$I$151,Uebersetzung_ccm!$I$173,Uebersetzung_ccm!$I$197,Uebersetzung_ccm!$I$215)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.092151308115314</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2140774677217825</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6212171599600931</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.9520177206335461</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9840912876894885</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0641995841995842</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.1454604512480531</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.6191308691308688</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-2AF5-431E-91A6-3AB4157C3616}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>24 V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>(Uebersetzung_ccm!$B$38,Uebersetzung_ccm!$B$72,Uebersetzung_ccm!$B$101,Uebersetzung_ccm!$B$128,Uebersetzung_ccm!$B$155,Uebersetzung_ccm!$B$178)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.000">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.000">
+                  <c:v>0.375</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(Uebersetzung_ccm!$I$38,Uebersetzung_ccm!$I$72,Uebersetzung_ccm!$I$101,Uebersetzung_ccm!$I$128,Uebersetzung_ccm!$I$155,Uebersetzung_ccm!$I$178)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.1141201321562044</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2449665546274418</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6649889771640114</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0040578261050701</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.0822128793239809</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.2047531992687386</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000D-2AF5-431E-91A6-3AB4157C3616}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1141425631"/>
+        <c:axId val="724655519"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1141425631"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-AT" sz="1400" b="1"/>
+                  <a:t>d [1]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.4815241625060952"/>
+              <c:y val="0.96056324538380056"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="724655519"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="724655519"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-AT" sz="1400" b="1"/>
+                  <a:t>U2/U1 [1]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="7.0107781716984604E-4"/>
+              <c:y val="5.5956163374315049E-3"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1141425631"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.7903857532103256E-2"/>
+          <c:y val="5.9329127718684295E-2"/>
+          <c:w val="0.18638613408334331"/>
+          <c:h val="0.21871455541741491"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-AT" sz="1500" b="1" i="0"/>
+              <a:t>Wirkungsgrad über</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-AT" sz="1500" b="1" i="0" baseline="0"/>
+              <a:t> Ausgangsleistung des Typ 4 bei konstanter Ein/Ausgangsspannung</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-AT" sz="1500" b="1" i="0"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-AT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.4460030415579296E-2"/>
+          <c:y val="5.7540789857408167E-2"/>
+          <c:w val="0.93281951122804196"/>
+          <c:h val="0.87044422955902445"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>3,3V_12V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$K$8:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.0043568</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5231612000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.99816854</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.5075280500000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.023601999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12.01951661</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$M$8:$M$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.7016706009981788</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.73964509452264127</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.72129713543376484</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.68914605580719257</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.64545859893205193</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.62569698836534104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8521-47C8-9E4C-A2ACAED45E56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>3,3V_24V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$K$15:$K$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.1562278399999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5096719999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.0140047900000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.5281250000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.9704096800000013</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11.7648972</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$M$15:$M$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.58350455388297862</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.61105864031217971</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.63617980775035077</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.62783978266829443</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.60185981407702538</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.58197915601055916</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8521-47C8-9E4C-A2ACAED45E56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>5V_12V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$K$22:$K$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.48079500000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99744929999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.4863638800000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.9928228000000008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.4997152099999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.9711317200000007</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21.656142000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$M$22:$M$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.78755847780791777</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.79910043395642383</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.81122008852861471</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.82116818631017152</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.81505101337184327</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.80570507718041429</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.74478388680668783</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8521-47C8-9E4C-A2ACAED45E56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>5V_24V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$K$30:$K$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.1448</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.30688</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.0379544000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.5803963999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.9432001999999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19.947558400000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$M$30:$M$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.71645333071318018</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7423287100828736</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.74404559730387998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75716133285388953</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.75696985545449558</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.7240421582770582</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-8521-47C8-9E4C-A2ACAED45E56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>5V_48V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="002060"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$K$37:$K$41</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.3211469819999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.9926394000000007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.4923851799999994</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.984802890000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.157430299999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$M$37:$M$41</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.56961779564333337</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.56115281003543627</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.60092237998174258</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.61876453157063416</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.62961599184097516</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-8521-47C8-9E4C-A2ACAED45E56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>12V_24V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:ln w="25400">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-8521-47C8-9E4C-A2ACAED45E56}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$K$43:$K$53</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.5813566</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4393925000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.4059418899999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.01408056</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.5831208199999995</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.9387405700000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.537522559999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28.699623799999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30.212356</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>47.660952799999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>63.408471200000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$M$43:$M$53</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.66110861088880768</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.83861114224862687</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.83987620847264255</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.87447234534186524</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.87644856557285566</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.89001405197203998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.8953024761107623</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.88979054173002359</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8936124980508211</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.88334400882156483</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.87648693227741892</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-8521-47C8-9E4C-A2ACAED45E56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>12V_48V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="00B0F0"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-8521-47C8-9E4C-A2ACAED45E56}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="00B0F0"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000A-8521-47C8-9E4C-A2ACAED45E56}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$K$55:$K$61</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2.3227757700000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.968</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.034089999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.223846600000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29.841772800000005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>49.97873288000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60.629428499999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$M$55:$M$61</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.68342373955938396</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.80247915662154323</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.80511036468066388</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.82910707895030056</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.83870497625786677</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.8464752656667015</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.84429300975508426</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-8521-47C8-9E4C-A2ACAED45E56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>24V_48V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="7030A0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:ln w="25400">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000C-8521-47C8-9E4C-A2ACAED45E56}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$K$63:$K$72</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2.3232075999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.01746465</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.46993284</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.230727725000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29.903388900000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50.112211800000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>69.931585260000006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>93.324786099999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>100.3227602</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>133.45703591999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Wirkungsgradkurven!$M$63:$M$72</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.7579193365710768</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.83867835800992507</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.88966539329633942</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.90083652318182861</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.90901178483813116</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.91869808346201998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.92280632285765629</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.92038614569959587</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.92372985289692122</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.92252497427898161</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000D-8521-47C8-9E4C-A2ACAED45E56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1141425631"/>
+        <c:axId val="724655519"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1141425631"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="95"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr">
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-AT" sz="1400" b="1"/>
+                  <a:t>Ausgangsleistung [W]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.42810886774545714"/>
+              <c:y val="0.96056324538380056"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr">
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="724655519"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="5"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="724655519"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0.5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR" sz="1400" b="1"/>
+                  <a:t>η</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-AT" sz="1400" b="1"/>
+                  <a:t> [1]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="7.0107781716984604E-4"/>
+              <c:y val="1.1833433101564058E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1141425631"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.86764021746484854"/>
+          <c:y val="0.5801868275237525"/>
+          <c:w val="9.4731067373506672E-2"/>
+          <c:h val="0.34312412702798117"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,10 +4121,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:f>
                       <m:fPr>
                         <m:ctrlPr>
@@ -771,6 +4329,85 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Diagramm 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1CAE81B-6722-9F36-B63D-832FAD19269B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>44824</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Diagramm 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EC07560-C0EA-4BAD-9282-3EF837D4CB09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1145,19 +4782,19 @@
       <c r="D6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="19" t="s">
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
       <c r="N6" s="6" t="s">
         <v>30</v>
       </c>
@@ -1208,11 +4845,11 @@
         <v>0.05</v>
       </c>
       <c r="C8" s="4">
-        <f>1/(1-2*B8)</f>
+        <f t="shared" ref="C8:C14" si="0">1/(1-2*B8)</f>
         <v>1.1111111111111112</v>
       </c>
       <c r="D8" s="4" t="str">
-        <f>TEXT(ROUND(E8,3),"#,#")&amp;"_"&amp;TEXT(B8,"0,##")</f>
+        <f t="shared" ref="D8:D14" si="1">TEXT(ROUND(E8,3),"#,#")&amp;"_"&amp;TEXT(B8,"0,##")</f>
         <v>3,3_0,05</v>
       </c>
       <c r="E8" s="7">
@@ -1228,23 +4865,23 @@
         <v>5.1150000000000001E-2</v>
       </c>
       <c r="I8" s="4">
-        <f>G8/E8</f>
+        <f t="shared" ref="I8:I14" si="2">G8/E8</f>
         <v>0.93134183804724502</v>
       </c>
       <c r="J8" s="4">
-        <f>F8*E8</f>
+        <f t="shared" ref="J8:J14" si="3">F8*E8</f>
         <v>0.207956907</v>
       </c>
       <c r="K8" s="4">
-        <f>H8*G8</f>
+        <f t="shared" ref="K8:K14" si="4">H8*G8</f>
         <v>0.15739877999999999</v>
       </c>
       <c r="L8" s="4">
-        <f>J8-K8</f>
+        <f t="shared" ref="L8:L14" si="5">J8-K8</f>
         <v>5.0558127000000008E-2</v>
       </c>
       <c r="M8" s="4">
-        <f>K8/J8</f>
+        <f t="shared" ref="M8:M14" si="6">K8/J8</f>
         <v>0.75688171299835683</v>
       </c>
       <c r="N8" s="6">
@@ -1256,11 +4893,11 @@
         <v>0.05</v>
       </c>
       <c r="C9" s="4">
-        <f>1/(1-2*B9)</f>
+        <f t="shared" si="0"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D9" s="4" t="str">
-        <f t="shared" ref="D9:D11" si="0">TEXT(ROUND(E9,3),"#,#")&amp;"_"&amp;TEXT(B9,"0,##")</f>
+        <f t="shared" si="1"/>
         <v>3,3_0,05</v>
       </c>
       <c r="E9" s="7">
@@ -1276,23 +4913,23 @@
         <v>9.8070000000000004E-2</v>
       </c>
       <c r="I9" s="4">
-        <f>G9/E9</f>
+        <f t="shared" si="2"/>
         <v>0.90003030303030307</v>
       </c>
       <c r="J9" s="4">
-        <f>F9*E9</f>
+        <f t="shared" si="3"/>
         <v>0.38359199999999999</v>
       </c>
       <c r="K9" s="4">
-        <f>H9*G9</f>
+        <f t="shared" si="4"/>
         <v>0.291277707</v>
       </c>
       <c r="L9" s="4">
-        <f>J9-K9</f>
+        <f t="shared" si="5"/>
         <v>9.2314292999999992E-2</v>
       </c>
       <c r="M9" s="4">
-        <f>K9/J9</f>
+        <f t="shared" si="6"/>
         <v>0.75934249671526</v>
       </c>
       <c r="N9" s="6">
@@ -1304,11 +4941,11 @@
         <v>0.05</v>
       </c>
       <c r="C10" s="4">
-        <f>1/(1-2*B10)</f>
+        <f t="shared" si="0"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D10" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3,3_0,05</v>
       </c>
       <c r="E10" s="7">
@@ -1324,23 +4961,23 @@
         <v>0.19116</v>
       </c>
       <c r="I10" s="4">
-        <f>G10/E10</f>
+        <f t="shared" si="2"/>
         <v>0.87282473727247956</v>
       </c>
       <c r="J10" s="4">
-        <f>F10*E10</f>
+        <f t="shared" si="3"/>
         <v>0.73143688799999995</v>
       </c>
       <c r="K10" s="4">
-        <f>H10*G10</f>
+        <f t="shared" si="4"/>
         <v>0.55091929679999996</v>
       </c>
       <c r="L10" s="4">
-        <f t="shared" ref="L10" si="1">J10-K10</f>
+        <f t="shared" si="5"/>
         <v>0.18051759119999999</v>
       </c>
       <c r="M10" s="4">
-        <f t="shared" ref="M10" si="2">K10/J10</f>
+        <f t="shared" si="6"/>
         <v>0.75320141195832058</v>
       </c>
       <c r="N10" s="6">
@@ -1352,11 +4989,11 @@
         <v>0.05</v>
       </c>
       <c r="C11" s="4">
-        <f>1/(1-2*B11)</f>
+        <f t="shared" si="0"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D11" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3,3_0,05</v>
       </c>
       <c r="E11" s="7">
@@ -1372,23 +5009,23 @@
         <v>0.75788</v>
       </c>
       <c r="I11" s="4">
-        <f>G11/E11</f>
+        <f t="shared" si="2"/>
         <v>0.81829452676141523</v>
       </c>
       <c r="J11" s="4">
-        <f>F11*E11</f>
+        <f t="shared" si="3"/>
         <v>2.840713</v>
       </c>
       <c r="K11" s="4">
-        <f>H11*G11</f>
+        <f t="shared" si="4"/>
         <v>2.0508990680000001</v>
       </c>
       <c r="L11" s="4">
-        <f>J11-K11</f>
+        <f t="shared" si="5"/>
         <v>0.78981393199999994</v>
       </c>
       <c r="M11" s="4">
-        <f>K11/J11</f>
+        <f t="shared" si="6"/>
         <v>0.72196630493823211</v>
       </c>
       <c r="N11" s="6">
@@ -1400,11 +5037,11 @@
         <v>0.05</v>
       </c>
       <c r="C12" s="4">
-        <f>1/(1-2*B12)</f>
+        <f t="shared" si="0"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D12" s="4" t="str">
-        <f>TEXT(ROUND(E12,3),"#,#")&amp;"_"&amp;TEXT(B12,"0,##")</f>
+        <f t="shared" si="1"/>
         <v>3,3_0,05</v>
       </c>
       <c r="E12" s="7">
@@ -1420,23 +5057,23 @@
         <v>2.2987500000000001</v>
       </c>
       <c r="I12" s="4">
-        <f>G12/E12</f>
+        <f t="shared" si="2"/>
         <v>0.74528643944887596</v>
       </c>
       <c r="J12" s="4">
-        <f>F12*E12</f>
+        <f t="shared" si="3"/>
         <v>8.5811308799999999</v>
       </c>
       <c r="K12" s="4">
-        <f>H12*G12</f>
+        <f t="shared" si="4"/>
         <v>5.6700967500000008</v>
       </c>
       <c r="L12" s="4">
-        <f>J12-K12</f>
+        <f t="shared" si="5"/>
         <v>2.9110341299999991</v>
       </c>
       <c r="M12" s="4">
-        <f>K12/J12</f>
+        <f t="shared" si="6"/>
         <v>0.66076334568154271</v>
       </c>
       <c r="N12" s="6">
@@ -1448,11 +5085,11 @@
         <v>0.05</v>
       </c>
       <c r="C13" s="4">
-        <f t="shared" ref="C13:C14" si="3">1/(1-2*B13)</f>
+        <f t="shared" si="0"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D13" s="4" t="str">
-        <f t="shared" ref="D13:D14" si="4">TEXT(ROUND(E13,3),"#,#")&amp;"_"&amp;TEXT(B13,"0,##")</f>
+        <f t="shared" si="1"/>
         <v>3,3_0,05</v>
       </c>
       <c r="E13" s="7">
@@ -1468,23 +5105,23 @@
         <v>3.92205</v>
       </c>
       <c r="I13" s="4">
-        <f t="shared" ref="I13:I14" si="5">G13/E13</f>
+        <f t="shared" si="2"/>
         <v>0.68169440242057489</v>
       </c>
       <c r="J13" s="4">
-        <f t="shared" ref="J13:J14" si="6">F13*E13</f>
+        <f t="shared" si="3"/>
         <v>14.573397500000002</v>
       </c>
       <c r="K13" s="4">
-        <f t="shared" ref="K13:K14" si="7">H13*G13</f>
+        <f t="shared" si="4"/>
         <v>8.8363786500000003</v>
       </c>
       <c r="L13" s="4">
-        <f t="shared" ref="L13:L14" si="8">J13-K13</f>
+        <f t="shared" si="5"/>
         <v>5.7370188500000019</v>
       </c>
       <c r="M13" s="4">
-        <f t="shared" ref="M13:M14" si="9">K13/J13</f>
+        <f t="shared" si="6"/>
         <v>0.6063362129524017</v>
       </c>
       <c r="N13" s="6">
@@ -1496,11 +5133,11 @@
         <v>0.05</v>
       </c>
       <c r="C14" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D14" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>3,3_0,05</v>
       </c>
       <c r="E14" s="7">
@@ -1516,23 +5153,23 @@
         <v>5.4039999999999999</v>
       </c>
       <c r="I14" s="4">
+        <f t="shared" si="2"/>
+        <v>0.64707664344138138</v>
+      </c>
+      <c r="J14" s="4">
+        <f t="shared" si="3"/>
+        <v>19.990195799999999</v>
+      </c>
+      <c r="K14" s="4">
+        <f t="shared" si="4"/>
+        <v>11.542944</v>
+      </c>
+      <c r="L14" s="4">
         <f t="shared" si="5"/>
-        <v>0.64707664344138138</v>
-      </c>
-      <c r="J14" s="4">
+        <v>8.4472517999999983</v>
+      </c>
+      <c r="M14" s="4">
         <f t="shared" si="6"/>
-        <v>19.990195799999999</v>
-      </c>
-      <c r="K14" s="4">
-        <f t="shared" si="7"/>
-        <v>11.542944</v>
-      </c>
-      <c r="L14" s="4">
-        <f t="shared" si="8"/>
-        <v>8.4472517999999983</v>
-      </c>
-      <c r="M14" s="4">
-        <f t="shared" si="9"/>
         <v>0.57743026208877857</v>
       </c>
       <c r="N14" s="6">
@@ -1544,11 +5181,11 @@
         <v>0.05</v>
       </c>
       <c r="C16" s="4">
-        <f t="shared" ref="C16:C21" si="10">1/(1-2*B16)</f>
+        <f t="shared" ref="C16:C22" si="7">1/(1-2*B16)</f>
         <v>1.1111111111111112</v>
       </c>
       <c r="D16" s="4" t="str">
-        <f>TEXT(ROUND(E16,3),"#")&amp;"_"&amp;TEXT(B16,"0,##")</f>
+        <f t="shared" ref="D16:D22" si="8">TEXT(ROUND(E16,3),"#")&amp;"_"&amp;TEXT(B16,"0,##")</f>
         <v>5_0,05</v>
       </c>
       <c r="E16" s="7">
@@ -1564,23 +5201,23 @@
         <v>8.3333000000000004E-2</v>
       </c>
       <c r="I16" s="4">
-        <f t="shared" ref="I16:I21" si="11">G16/E16</f>
+        <f t="shared" ref="I16:I22" si="9">G16/E16</f>
         <v>1.0010583465875795</v>
       </c>
       <c r="J16" s="4">
-        <f t="shared" ref="J16:J21" si="12">F16*E16</f>
+        <f t="shared" ref="J16:J22" si="10">F16*E16</f>
         <v>0.50880033660000001</v>
       </c>
       <c r="K16" s="4">
-        <f t="shared" ref="K16:K21" si="13">H16*G16</f>
+        <f t="shared" ref="K16:K22" si="11">H16*G16</f>
         <v>0.41854582580999999</v>
       </c>
       <c r="L16" s="4">
-        <f>J16-K16</f>
+        <f t="shared" ref="L16:L22" si="12">J16-K16</f>
         <v>9.025451079000002E-2</v>
       </c>
       <c r="M16" s="4">
-        <f>K16/J16</f>
+        <f t="shared" ref="M16:M22" si="13">K16/J16</f>
         <v>0.82261310715099867</v>
       </c>
       <c r="N16" s="6">
@@ -1592,11 +5229,11 @@
         <v>0.05</v>
       </c>
       <c r="C17" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D17" s="4" t="str">
-        <f t="shared" ref="D17:D21" si="14">TEXT(ROUND(E17,3),"#")&amp;"_"&amp;TEXT(B17,"0,##")</f>
+        <f t="shared" si="8"/>
         <v>5_0,05</v>
       </c>
       <c r="E17" s="7">
@@ -1612,23 +5249,23 @@
         <v>0.16108</v>
       </c>
       <c r="I17" s="4">
+        <f t="shared" si="9"/>
+        <v>0.97617073146362676</v>
+      </c>
+      <c r="J17" s="4">
+        <f t="shared" si="10"/>
+        <v>0.9491750645</v>
+      </c>
+      <c r="K17" s="4">
         <f t="shared" si="11"/>
-        <v>0.97617073146362676</v>
-      </c>
-      <c r="J17" s="4">
+        <v>0.78689190800000008</v>
+      </c>
+      <c r="L17" s="4">
         <f t="shared" si="12"/>
-        <v>0.9491750645</v>
-      </c>
-      <c r="K17" s="4">
+        <v>0.16228315649999991</v>
+      </c>
+      <c r="M17" s="4">
         <f t="shared" si="13"/>
-        <v>0.78689190800000008</v>
-      </c>
-      <c r="L17" s="4">
-        <f t="shared" ref="L17" si="15">J17-K17</f>
-        <v>0.16228315649999991</v>
-      </c>
-      <c r="M17" s="4">
-        <f t="shared" ref="M17" si="16">K17/J17</f>
         <v>0.82902715993125431</v>
       </c>
       <c r="N17" s="6">
@@ -1640,11 +5277,11 @@
         <v>0.05</v>
       </c>
       <c r="C18" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D18" s="4" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>5_0,05</v>
       </c>
       <c r="E18" s="7">
@@ -1660,23 +5297,23 @@
         <v>0.31657999999999997</v>
       </c>
       <c r="I18" s="4">
+        <f t="shared" si="9"/>
+        <v>0.95415067178502888</v>
+      </c>
+      <c r="J18" s="4">
+        <f t="shared" si="10"/>
+        <v>1.8278847359999999</v>
+      </c>
+      <c r="K18" s="4">
         <f t="shared" si="11"/>
-        <v>0.95415067178502888</v>
-      </c>
-      <c r="J18" s="4">
+        <v>1.5108084023999999</v>
+      </c>
+      <c r="L18" s="4">
         <f t="shared" si="12"/>
-        <v>1.8278847359999999</v>
-      </c>
-      <c r="K18" s="4">
+        <v>0.31707633359999998</v>
+      </c>
+      <c r="M18" s="4">
         <f t="shared" si="13"/>
-        <v>1.5108084023999999</v>
-      </c>
-      <c r="L18" s="4">
-        <f t="shared" ref="L18" si="17">J18-K18</f>
-        <v>0.31707633359999998</v>
-      </c>
-      <c r="M18" s="4">
-        <f t="shared" ref="M18" si="18">K18/J18</f>
         <v>0.82653373740957814</v>
       </c>
       <c r="N18" s="6">
@@ -1688,11 +5325,11 @@
         <v>0.05</v>
       </c>
       <c r="C19" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D19" s="4" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>5_0,05</v>
       </c>
       <c r="E19" s="7">
@@ -1708,23 +5345,23 @@
         <v>0.61728000000000005</v>
       </c>
       <c r="I19" s="4">
+        <f t="shared" si="9"/>
+        <v>0.93346375741121523</v>
+      </c>
+      <c r="J19" s="4">
+        <f t="shared" si="10"/>
+        <v>3.5291520359999997</v>
+      </c>
+      <c r="K19" s="4">
         <f t="shared" si="11"/>
-        <v>0.93346375741121523</v>
-      </c>
-      <c r="J19" s="4">
+        <v>2.8864012800000003</v>
+      </c>
+      <c r="L19" s="4">
         <f t="shared" si="12"/>
-        <v>3.5291520359999997</v>
-      </c>
-      <c r="K19" s="4">
+        <v>0.64275075599999942</v>
+      </c>
+      <c r="M19" s="4">
         <f t="shared" si="13"/>
-        <v>2.8864012800000003</v>
-      </c>
-      <c r="L19" s="4">
-        <f t="shared" ref="L19" si="19">J19-K19</f>
-        <v>0.64275075599999942</v>
-      </c>
-      <c r="M19" s="4">
-        <f t="shared" ref="M19" si="20">K19/J19</f>
         <v>0.81787388317548826</v>
       </c>
       <c r="N19" s="6">
@@ -1736,11 +5373,11 @@
         <v>0.05</v>
       </c>
       <c r="C20" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D20" s="4" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>5_0,05</v>
       </c>
       <c r="E20" s="7">
@@ -1756,23 +5393,23 @@
         <v>1.7396499999999999</v>
       </c>
       <c r="I20" s="4">
+        <f t="shared" si="9"/>
+        <v>0.89255340387302839</v>
+      </c>
+      <c r="J20" s="4">
+        <f t="shared" si="10"/>
+        <v>9.864023340000001</v>
+      </c>
+      <c r="K20" s="4">
         <f t="shared" si="11"/>
-        <v>0.89255340387302839</v>
-      </c>
-      <c r="J20" s="4">
+        <v>7.7776272199999994</v>
+      </c>
+      <c r="L20" s="4">
         <f t="shared" si="12"/>
-        <v>9.864023340000001</v>
-      </c>
-      <c r="K20" s="4">
+        <v>2.0863961200000016</v>
+      </c>
+      <c r="M20" s="4">
         <f t="shared" si="13"/>
-        <v>7.7776272199999994</v>
-      </c>
-      <c r="L20" s="4">
-        <f t="shared" ref="L20" si="21">J20-K20</f>
-        <v>2.0863961200000016</v>
-      </c>
-      <c r="M20" s="4">
-        <f t="shared" ref="M20" si="22">K20/J20</f>
         <v>0.78848426771869318</v>
       </c>
       <c r="N20" s="6">
@@ -1784,11 +5421,11 @@
         <v>0.05</v>
       </c>
       <c r="C21" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D21" s="4" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>5_0,05</v>
       </c>
       <c r="E21" s="7">
@@ -1804,23 +5441,23 @@
         <v>3.9059699999999999</v>
       </c>
       <c r="I21" s="4">
+        <f t="shared" si="9"/>
+        <v>0.83799240151969612</v>
+      </c>
+      <c r="J21" s="4">
+        <f t="shared" si="10"/>
+        <v>22.053909900000004</v>
+      </c>
+      <c r="K21" s="4">
         <f t="shared" si="11"/>
-        <v>0.83799240151969612</v>
-      </c>
-      <c r="J21" s="4">
+        <v>16.369139076</v>
+      </c>
+      <c r="L21" s="4">
         <f t="shared" si="12"/>
-        <v>22.053909900000004</v>
-      </c>
-      <c r="K21" s="4">
+        <v>5.6847708240000046</v>
+      </c>
+      <c r="M21" s="4">
         <f t="shared" si="13"/>
-        <v>16.369139076</v>
-      </c>
-      <c r="L21" s="4">
-        <f t="shared" ref="L21" si="23">J21-K21</f>
-        <v>5.6847708240000046</v>
-      </c>
-      <c r="M21" s="4">
-        <f t="shared" ref="M21" si="24">K21/J21</f>
         <v>0.74223297139705813</v>
       </c>
       <c r="N21" s="6">
@@ -1832,11 +5469,11 @@
         <v>0.05</v>
       </c>
       <c r="C22" s="4">
-        <f t="shared" ref="C22" si="25">1/(1-2*B22)</f>
+        <f t="shared" si="7"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D22" s="4" t="str">
-        <f t="shared" ref="D22" si="26">TEXT(ROUND(E22,3),"#")&amp;"_"&amp;TEXT(B22,"0,##")</f>
+        <f t="shared" si="8"/>
         <v>5_0,05</v>
       </c>
       <c r="E22" s="7">
@@ -1852,23 +5489,23 @@
         <v>5.2573999999999996</v>
       </c>
       <c r="I22" s="4">
-        <f t="shared" ref="I22" si="27">G22/E22</f>
+        <f t="shared" si="9"/>
         <v>0.81350649350649351</v>
       </c>
       <c r="J22" s="4">
-        <f t="shared" ref="J22" si="28">F22*E22</f>
+        <f t="shared" si="10"/>
         <v>29.669639999999998</v>
       </c>
       <c r="K22" s="4">
-        <f t="shared" ref="K22" si="29">H22*G22</f>
+        <f t="shared" si="11"/>
         <v>21.406029839999999</v>
       </c>
       <c r="L22" s="4">
-        <f t="shared" ref="L22" si="30">J22-K22</f>
+        <f t="shared" si="12"/>
         <v>8.2636101599999989</v>
       </c>
       <c r="M22" s="4">
-        <f t="shared" ref="M22" si="31">K22/J22</f>
+        <f t="shared" si="13"/>
         <v>0.72147925758452081</v>
       </c>
       <c r="N22" s="6">
@@ -1880,11 +5517,11 @@
         <v>0.05</v>
       </c>
       <c r="C24" s="4">
-        <f t="shared" ref="C24:C29" si="32">1/(1-2*B24)</f>
+        <f t="shared" ref="C24:C29" si="14">1/(1-2*B24)</f>
         <v>1.1111111111111112</v>
       </c>
       <c r="D24" s="4" t="str">
-        <f>TEXT(ROUND(E24,3),"#")&amp;"_"&amp;TEXT(B24,"0,##")</f>
+        <f t="shared" ref="D24:D29" si="15">TEXT(ROUND(E24,3),"#")&amp;"_"&amp;TEXT(B24,"0,##")</f>
         <v>9_0,05</v>
       </c>
       <c r="E24" s="7">
@@ -1900,23 +5537,23 @@
         <v>0.12135</v>
       </c>
       <c r="I24" s="4">
-        <f t="shared" ref="I24:I29" si="33">G24/E24</f>
+        <f t="shared" ref="I24:I29" si="16">G24/E24</f>
         <v>1.0737276812826431</v>
       </c>
       <c r="J24" s="4">
-        <f t="shared" ref="J24:J29" si="34">F24*E24</f>
+        <f t="shared" ref="J24:J29" si="17">F24*E24</f>
         <v>1.3426417564999999</v>
       </c>
       <c r="K24" s="4">
-        <f t="shared" ref="K24:K29" si="35">H24*G24</f>
+        <f t="shared" ref="K24:K29" si="18">H24*G24</f>
         <v>1.1800074</v>
       </c>
       <c r="L24" s="4">
-        <f>J24-K24</f>
+        <f t="shared" ref="L24:L29" si="19">J24-K24</f>
         <v>0.16263435649999991</v>
       </c>
       <c r="M24" s="4">
-        <f>K24/J24</f>
+        <f t="shared" ref="M24:M29" si="20">K24/J24</f>
         <v>0.87886988043336645</v>
       </c>
       <c r="N24" s="6">
@@ -1928,11 +5565,11 @@
         <v>0.05</v>
       </c>
       <c r="C25" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="14"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D25" s="4" t="str">
-        <f t="shared" ref="D25:D28" si="36">TEXT(ROUND(E25,3),"#")&amp;"_"&amp;TEXT(B25,"0,##")</f>
+        <f t="shared" si="15"/>
         <v>9_0,05</v>
       </c>
       <c r="E25" s="7">
@@ -1948,23 +5585,23 @@
         <v>0.23649999999999999</v>
       </c>
       <c r="I25" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="16"/>
         <v>1.0528475572561415</v>
       </c>
       <c r="J25" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="17"/>
         <v>2.5165051500000004</v>
       </c>
       <c r="K25" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="18"/>
         <v>2.2450945</v>
       </c>
       <c r="L25" s="4">
-        <f t="shared" ref="L25:L29" si="37">J25-K25</f>
+        <f t="shared" si="19"/>
         <v>0.27141065000000042</v>
       </c>
       <c r="M25" s="4">
-        <f t="shared" ref="M25:M29" si="38">K25/J25</f>
+        <f t="shared" si="20"/>
         <v>0.89214778678279261</v>
       </c>
       <c r="N25" s="6">
@@ -1976,11 +5613,11 @@
         <v>0.05</v>
       </c>
       <c r="C26" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="14"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D26" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="15"/>
         <v>9_0,05</v>
       </c>
       <c r="E26" s="7">
@@ -1996,23 +5633,23 @@
         <v>0.46454000000000001</v>
       </c>
       <c r="I26" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="16"/>
         <v>1.0348140989324712</v>
       </c>
       <c r="J26" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="17"/>
         <v>4.8352619645999999</v>
       </c>
       <c r="K26" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="18"/>
         <v>4.3274223699999999</v>
       </c>
       <c r="L26" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="19"/>
         <v>0.50783959460000005</v>
       </c>
       <c r="M26" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="20"/>
         <v>0.89497164821306396</v>
       </c>
       <c r="N26" s="6">
@@ -2024,11 +5661,11 @@
         <v>0.05</v>
       </c>
       <c r="C27" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="14"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D27" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="15"/>
         <v>9_0,05</v>
       </c>
       <c r="E27" s="7">
@@ -2044,23 +5681,23 @@
         <v>0.91043600000000002</v>
       </c>
       <c r="I27" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="16"/>
         <v>1.0183201021484483</v>
       </c>
       <c r="J27" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="17"/>
         <v>9.370812925000001</v>
       </c>
       <c r="K27" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="18"/>
         <v>8.3500637740000005</v>
       </c>
       <c r="L27" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="19"/>
         <v>1.0207491510000004</v>
       </c>
       <c r="M27" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="20"/>
         <v>0.89107144074162592</v>
       </c>
       <c r="N27" s="6">
@@ -2072,11 +5709,11 @@
         <v>0.05</v>
       </c>
       <c r="C28" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="14"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D28" s="4" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="15"/>
         <v>9_0,05</v>
       </c>
       <c r="E28" s="7">
@@ -2092,23 +5729,23 @@
         <v>1.7767999999999999</v>
       </c>
       <c r="I28" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="16"/>
         <v>0.99980018427450246</v>
       </c>
       <c r="J28" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="17"/>
         <v>18.182713052</v>
       </c>
       <c r="K28" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="18"/>
         <v>16.0027492</v>
       </c>
       <c r="L28" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="19"/>
         <v>2.1799638520000002</v>
       </c>
       <c r="M28" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="20"/>
         <v>0.88010788897313563</v>
       </c>
       <c r="N28" s="6">
@@ -2120,11 +5757,11 @@
         <v>0.05</v>
       </c>
       <c r="C29" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="14"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D29" s="4" t="str">
-        <f>TEXT(ROUND(E29,3),"#")&amp;"_"&amp;TEXT(B29,"0,##")</f>
+        <f t="shared" si="15"/>
         <v>9_0,05</v>
       </c>
       <c r="E29" s="7">
@@ -2140,23 +5777,23 @@
         <v>5.4345999999999997</v>
       </c>
       <c r="I29" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="16"/>
         <v>0.95054499394451175</v>
       </c>
       <c r="J29" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="17"/>
         <v>55.354755045999994</v>
       </c>
       <c r="K29" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="18"/>
         <v>46.493002999999995</v>
       </c>
       <c r="L29" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="19"/>
         <v>8.8617520459999994</v>
       </c>
       <c r="M29" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="20"/>
         <v>0.83990983179970979</v>
       </c>
       <c r="N29" s="6">
@@ -2168,11 +5805,11 @@
         <v>0.05</v>
       </c>
       <c r="C31" s="4">
-        <f t="shared" ref="C31:C36" si="39">1/(1-2*B31)</f>
+        <f t="shared" ref="C31:C36" si="21">1/(1-2*B31)</f>
         <v>1.1111111111111112</v>
       </c>
       <c r="D31" s="4" t="str">
-        <f>TEXT(ROUND(E31,3),"#")&amp;"_"&amp;TEXT(B31,"0,##")</f>
+        <f t="shared" ref="D31:D36" si="22">TEXT(ROUND(E31,3),"#")&amp;"_"&amp;TEXT(B31,"0,##")</f>
         <v>12_0,05</v>
       </c>
       <c r="E31" s="7">
@@ -2188,23 +5825,23 @@
         <v>0.16306899999999999</v>
       </c>
       <c r="I31" s="4">
-        <f t="shared" ref="I31:I36" si="40">G31/E31</f>
+        <f t="shared" ref="I31:I36" si="23">G31/E31</f>
         <v>1.092151308115314</v>
       </c>
       <c r="J31" s="4">
-        <f t="shared" ref="J31:J36" si="41">F31*E31</f>
+        <f t="shared" ref="J31:J36" si="24">F31*E31</f>
         <v>2.3767560600000004</v>
       </c>
       <c r="K31" s="4">
-        <f t="shared" ref="K31:K36" si="42">H31*G31</f>
+        <f t="shared" ref="K31:K36" si="25">H31*G31</f>
         <v>2.1375084520000001</v>
       </c>
       <c r="L31" s="4">
-        <f>J31-K31</f>
+        <f t="shared" ref="L31:L36" si="26">J31-K31</f>
         <v>0.23924760800000033</v>
       </c>
       <c r="M31" s="4">
-        <f>K31/J31</f>
+        <f t="shared" ref="M31:M36" si="27">K31/J31</f>
         <v>0.89933859346087019</v>
       </c>
       <c r="N31" s="6">
@@ -2216,11 +5853,11 @@
         <v>0.05</v>
       </c>
       <c r="C32" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="21"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D32" s="4" t="str">
-        <f t="shared" ref="D32:D36" si="43">TEXT(ROUND(E32,3),"#")&amp;"_"&amp;TEXT(B32,"0,##")</f>
+        <f t="shared" si="22"/>
         <v>12_0,05</v>
       </c>
       <c r="E32" s="7">
@@ -2236,23 +5873,23 @@
         <v>0.32155</v>
       </c>
       <c r="I32" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="23"/>
         <v>1.0735351684504226</v>
       </c>
       <c r="J32" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="24"/>
         <v>4.5397296890000005</v>
       </c>
       <c r="K32" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="25"/>
         <v>4.1445865700000004</v>
       </c>
       <c r="L32" s="4">
-        <f t="shared" ref="L32:L36" si="44">J32-K32</f>
+        <f t="shared" si="26"/>
         <v>0.3951431190000001</v>
       </c>
       <c r="M32" s="4">
-        <f t="shared" ref="M32:M36" si="45">K32/J32</f>
+        <f t="shared" si="27"/>
         <v>0.91295888828855776</v>
       </c>
       <c r="N32" s="6">
@@ -2264,11 +5901,11 @@
         <v>0.05</v>
       </c>
       <c r="C33" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="21"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D33" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="22"/>
         <v>12_0,05</v>
       </c>
       <c r="E33" s="7">
@@ -2284,23 +5921,23 @@
         <v>0.63324000000000003</v>
       </c>
       <c r="I33" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="23"/>
         <v>1.0572047490106229</v>
       </c>
       <c r="J33" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="24"/>
         <v>8.7702267499999991</v>
       </c>
       <c r="K33" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="25"/>
         <v>8.0352456839999995</v>
       </c>
       <c r="L33" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="26"/>
         <v>0.73498106599999957</v>
       </c>
       <c r="M33" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="27"/>
         <v>0.91619588786572714</v>
       </c>
       <c r="N33" s="6">
@@ -2312,11 +5949,11 @@
         <v>0.05</v>
       </c>
       <c r="C34" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="21"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D34" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="22"/>
         <v>12_0,05</v>
       </c>
       <c r="E34" s="7">
@@ -2332,23 +5969,23 @@
         <v>1.24295</v>
       </c>
       <c r="I34" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="23"/>
         <v>1.0423051299133912</v>
       </c>
       <c r="J34" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="24"/>
         <v>17.042954399999999</v>
       </c>
       <c r="K34" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="25"/>
         <v>15.5567622</v>
       </c>
       <c r="L34" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="26"/>
         <v>1.4861921999999996</v>
       </c>
       <c r="M34" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="27"/>
         <v>0.9127972671217145</v>
       </c>
       <c r="N34" s="6">
@@ -2360,11 +5997,11 @@
         <v>0.05</v>
       </c>
       <c r="C35" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="21"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D35" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="22"/>
         <v>12_0,05</v>
       </c>
       <c r="E35" s="7">
@@ -2380,23 +6017,23 @@
         <v>2.4288799999999999</v>
       </c>
       <c r="I35" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="23"/>
         <v>1.0249565195682748</v>
       </c>
       <c r="J35" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="24"/>
         <v>33.163759943999999</v>
       </c>
       <c r="K35" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="25"/>
         <v>29.916029183999999</v>
       </c>
       <c r="L35" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="26"/>
         <v>3.2477307599999996</v>
       </c>
       <c r="M35" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="27"/>
         <v>0.9020698869644429</v>
       </c>
       <c r="N35" s="6">
@@ -2408,11 +6045,11 @@
         <v>0.05</v>
       </c>
       <c r="C36" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="21"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="D36" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="22"/>
         <v>12_0,05</v>
       </c>
       <c r="E36" s="7">
@@ -2428,23 +6065,23 @@
         <v>5.2957000000000001</v>
       </c>
       <c r="I36" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="23"/>
         <v>0.99664637933176004</v>
       </c>
       <c r="J36" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="24"/>
         <v>72.495229499999994</v>
       </c>
       <c r="K36" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="25"/>
         <v>63.7390452</v>
       </c>
       <c r="L36" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="26"/>
         <v>8.7561842999999939</v>
       </c>
       <c r="M36" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="27"/>
         <v>0.87921709662288894</v>
       </c>
       <c r="N36" s="6">
@@ -2508,7 +6145,7 @@
         <v>1.1111111111111112</v>
       </c>
       <c r="D39" s="4" t="str">
-        <f t="shared" ref="D39:D41" si="46">TEXT(ROUND(E39,3),"#")&amp;"_"&amp;TEXT(B39,"0,##")</f>
+        <f>TEXT(ROUND(E39,3),"#")&amp;"_"&amp;TEXT(B39,"0,##")</f>
         <v>24_0,05</v>
       </c>
       <c r="E39" s="7">
@@ -2536,11 +6173,11 @@
         <v>17.455691999000003</v>
       </c>
       <c r="L39" s="4">
-        <f t="shared" ref="L39:L41" si="47">J39-K39</f>
+        <f>J39-K39</f>
         <v>1.0453529609999954</v>
       </c>
       <c r="M39" s="4">
-        <f t="shared" ref="M39:M41" si="48">K39/J39</f>
+        <f>K39/J39</f>
         <v>0.9434976260389567</v>
       </c>
       <c r="N39" s="6">
@@ -2556,7 +6193,7 @@
         <v>1.1111111111111112</v>
       </c>
       <c r="D40" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f>TEXT(ROUND(E40,3),"#")&amp;"_"&amp;TEXT(B40,"0,##")</f>
         <v>24_0,05</v>
       </c>
       <c r="E40" s="7">
@@ -2584,11 +6221,11 @@
         <v>34.172534800000001</v>
       </c>
       <c r="L40" s="4">
-        <f t="shared" si="47"/>
+        <f>J40-K40</f>
         <v>1.884962900000005</v>
       </c>
       <c r="M40" s="4">
-        <f t="shared" si="48"/>
+        <f>K40/J40</f>
         <v>0.94772341343032229</v>
       </c>
       <c r="N40" s="6">
@@ -2604,7 +6241,7 @@
         <v>1.1111111111111112</v>
       </c>
       <c r="D41" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f>TEXT(ROUND(E41,3),"#")&amp;"_"&amp;TEXT(B41,"0,##")</f>
         <v>24_0,05</v>
       </c>
       <c r="E41" s="7">
@@ -2632,11 +6269,11 @@
         <v>66.777933999999988</v>
       </c>
       <c r="L41" s="4">
-        <f t="shared" si="47"/>
+        <f>J41-K41</f>
         <v>3.8792825600000214</v>
       </c>
       <c r="M41" s="4">
-        <f t="shared" si="48"/>
+        <f>K41/J41</f>
         <v>0.94509715003129435</v>
       </c>
       <c r="N41" s="6">
@@ -2652,7 +6289,7 @@
         <v>1.1111111111111112</v>
       </c>
       <c r="D42" s="4" t="str">
-        <f t="shared" ref="D42" si="49">TEXT(ROUND(E42,3),"#")&amp;"_"&amp;TEXT(B42,"0,##")</f>
+        <f>TEXT(ROUND(E42,3),"#")&amp;"_"&amp;TEXT(B42,"0,##")</f>
         <v>24_0,05</v>
       </c>
       <c r="E42" s="7">
@@ -2680,11 +6317,11 @@
         <v>129.67623500000002</v>
       </c>
       <c r="L42" s="4">
-        <f t="shared" ref="L42" si="50">J42-K42</f>
+        <f>J42-K42</f>
         <v>8.7981893999999841</v>
       </c>
       <c r="M42" s="4">
-        <f t="shared" ref="M42" si="51">K42/J42</f>
+        <f>K42/J42</f>
         <v>0.93646343403757104</v>
       </c>
       <c r="N42" s="6">
@@ -2696,11 +6333,11 @@
         <v>0.1</v>
       </c>
       <c r="C44" s="4">
-        <f t="shared" ref="C44:C50" si="52">1/(1-2*B44)</f>
+        <f t="shared" ref="C44:C50" si="28">1/(1-2*B44)</f>
         <v>1.25</v>
       </c>
       <c r="D44" s="4" t="str">
-        <f>TEXT(ROUND(E44,3),"#,#")&amp;"_"&amp;TEXT(B44,"0,##")</f>
+        <f t="shared" ref="D44:D50" si="29">TEXT(ROUND(E44,3),"#,#")&amp;"_"&amp;TEXT(B44,"0,##")</f>
         <v>3,3_0,1</v>
       </c>
       <c r="E44" s="7">
@@ -2716,23 +6353,23 @@
         <v>7.5759999999999994E-2</v>
       </c>
       <c r="I44" s="4">
-        <f t="shared" ref="I44:I50" si="53">G44/E44</f>
+        <f t="shared" ref="I44:I50" si="30">G44/E44</f>
         <v>1.0467652047492124</v>
       </c>
       <c r="J44" s="4">
-        <f t="shared" ref="J44:J50" si="54">F44*E44</f>
+        <f t="shared" ref="J44:J50" si="31">F44*E44</f>
         <v>0.34108829600000001</v>
       </c>
       <c r="K44" s="4">
-        <f t="shared" ref="K44:K50" si="55">H44*G44</f>
+        <f t="shared" ref="K44:K50" si="32">H44*G44</f>
         <v>0.26182655999999999</v>
       </c>
       <c r="L44" s="4">
-        <f>J44-K44</f>
+        <f t="shared" ref="L44:L50" si="33">J44-K44</f>
         <v>7.9261736000000027E-2</v>
       </c>
       <c r="M44" s="4">
-        <f>K44/J44</f>
+        <f t="shared" ref="M44:M50" si="34">K44/J44</f>
         <v>0.76762106196689894</v>
       </c>
       <c r="N44" s="6">
@@ -2744,11 +6381,11 @@
         <v>0.1</v>
       </c>
       <c r="C45" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="28"/>
         <v>1.25</v>
       </c>
       <c r="D45" s="4" t="str">
-        <f t="shared" ref="D45:D47" si="56">TEXT(ROUND(E45,3),"#,#")&amp;"_"&amp;TEXT(B45,"0,##")</f>
+        <f t="shared" si="29"/>
         <v>3,3_0,1</v>
       </c>
       <c r="E45" s="7">
@@ -2764,23 +6401,23 @@
         <v>0.16528999999999999</v>
       </c>
       <c r="I45" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="30"/>
         <v>1.0072703038381146</v>
       </c>
       <c r="J45" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="31"/>
         <v>0.71848441500000004</v>
       </c>
       <c r="K45" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="32"/>
         <v>0.54960577899999996</v>
       </c>
       <c r="L45" s="4">
-        <f t="shared" ref="L45:L47" si="57">J45-K45</f>
+        <f t="shared" si="33"/>
         <v>0.16887863600000008</v>
       </c>
       <c r="M45" s="4">
-        <f t="shared" ref="M45:M47" si="58">K45/J45</f>
+        <f t="shared" si="34"/>
         <v>0.76495156683391652</v>
       </c>
       <c r="N45" s="6">
@@ -2792,11 +6429,11 @@
         <v>0.1</v>
       </c>
       <c r="C46" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="28"/>
         <v>1.25</v>
       </c>
       <c r="D46" s="4" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="29"/>
         <v>3,3_0,1</v>
       </c>
       <c r="E46" s="7">
@@ -2812,23 +6449,23 @@
         <v>0.320795</v>
       </c>
       <c r="I46" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="30"/>
         <v>0.97794407246947623</v>
       </c>
       <c r="J46" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="31"/>
         <v>1.371803927</v>
       </c>
       <c r="K46" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="32"/>
         <v>1.0354941805</v>
       </c>
       <c r="L46" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="33"/>
         <v>0.33630974650000001</v>
       </c>
       <c r="M46" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="34"/>
         <v>0.75484124233739713</v>
       </c>
       <c r="N46" s="6">
@@ -2840,11 +6477,11 @@
         <v>0.1</v>
       </c>
       <c r="C47" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="28"/>
         <v>1.25</v>
       </c>
       <c r="D47" s="4" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="29"/>
         <v>3,3_0,1</v>
       </c>
       <c r="E47" s="7">
@@ -2860,23 +6497,23 @@
         <v>0.6169</v>
       </c>
       <c r="I47" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="30"/>
         <v>0.94651564250885867</v>
       </c>
       <c r="J47" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="31"/>
         <v>2.60982176</v>
       </c>
       <c r="K47" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="32"/>
         <v>1.92799757</v>
       </c>
       <c r="L47" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="33"/>
         <v>0.68182418999999994</v>
       </c>
       <c r="M47" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="34"/>
         <v>0.73874683687210885</v>
       </c>
       <c r="N47" s="6">
@@ -2888,11 +6525,11 @@
         <v>0.1</v>
       </c>
       <c r="C48" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="28"/>
         <v>1.25</v>
       </c>
       <c r="D48" s="4" t="str">
-        <f>TEXT(ROUND(E48,3),"#,#")&amp;"_"&amp;TEXT(B48,"0,##")</f>
+        <f t="shared" si="29"/>
         <v>3,3_0,1</v>
       </c>
       <c r="E48" s="7">
@@ -2908,23 +6545,23 @@
         <v>1.1625000000000001</v>
       </c>
       <c r="I48" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="30"/>
         <v>0.90566952516590404</v>
       </c>
       <c r="J48" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="31"/>
         <v>4.8954343419999997</v>
       </c>
       <c r="K48" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="32"/>
         <v>3.4744800000000002</v>
       </c>
       <c r="L48" s="4">
-        <f t="shared" ref="L48:L49" si="59">J48-K48</f>
+        <f t="shared" si="33"/>
         <v>1.4209543419999995</v>
       </c>
       <c r="M48" s="4">
-        <f t="shared" ref="M48:M49" si="60">K48/J48</f>
+        <f t="shared" si="34"/>
         <v>0.70973886222739591</v>
       </c>
       <c r="N48" s="6">
@@ -2936,11 +6573,11 @@
         <v>0.1</v>
       </c>
       <c r="C49" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="28"/>
         <v>1.25</v>
       </c>
       <c r="D49" s="4" t="str">
-        <f t="shared" ref="D49" si="61">TEXT(ROUND(E49,3),"#,#")&amp;"_"&amp;TEXT(B49,"0,##")</f>
+        <f t="shared" si="29"/>
         <v>3,3_0,1</v>
       </c>
       <c r="E49" s="7">
@@ -2956,23 +6593,23 @@
         <v>2.54236</v>
       </c>
       <c r="I49" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="30"/>
         <v>0.82548098772913192</v>
       </c>
       <c r="J49" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="31"/>
         <v>10.6705165</v>
       </c>
       <c r="K49" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="32"/>
         <v>6.9266598199999994</v>
       </c>
       <c r="L49" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="33"/>
         <v>3.7438566800000004</v>
       </c>
       <c r="M49" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="34"/>
         <v>0.64914006927405998</v>
       </c>
       <c r="N49" s="6">
@@ -2984,11 +6621,11 @@
         <v>0.1</v>
       </c>
       <c r="C50" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="28"/>
         <v>1.25</v>
       </c>
       <c r="D50" s="4" t="str">
-        <f>TEXT(ROUND(E50,3),"#,#")&amp;"_"&amp;TEXT(B50,"0,##")</f>
+        <f t="shared" si="29"/>
         <v>3,3_0,1</v>
       </c>
       <c r="E50" s="7">
@@ -3004,23 +6641,23 @@
         <v>4.6082000000000001</v>
       </c>
       <c r="I50" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="30"/>
         <v>0.7316777710478497</v>
       </c>
       <c r="J50" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="31"/>
         <v>19.259245200000002</v>
       </c>
       <c r="K50" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="32"/>
         <v>11.133411199999999</v>
       </c>
       <c r="L50" s="4">
-        <f t="shared" ref="L50" si="62">J50-K50</f>
+        <f t="shared" si="33"/>
         <v>8.1258340000000029</v>
       </c>
       <c r="M50" s="4">
-        <f t="shared" ref="M50" si="63">K50/J50</f>
+        <f t="shared" si="34"/>
         <v>0.57808138815325938</v>
       </c>
       <c r="N50" s="6">
@@ -3032,11 +6669,11 @@
         <v>0.1</v>
       </c>
       <c r="C52" s="4">
-        <f t="shared" ref="C52:C57" si="64">1/(1-2*B52)</f>
+        <f t="shared" ref="C52:C57" si="35">1/(1-2*B52)</f>
         <v>1.25</v>
       </c>
       <c r="D52" s="4" t="str">
-        <f>TEXT(ROUND(E52,3),"#")&amp;"_"&amp;TEXT(B52,"0,##")</f>
+        <f t="shared" ref="D52:D57" si="36">TEXT(ROUND(E52,3),"#")&amp;"_"&amp;TEXT(B52,"0,##")</f>
         <v>5_0,1</v>
       </c>
       <c r="E52" s="7">
@@ -3052,23 +6689,23 @@
         <v>0.12429</v>
       </c>
       <c r="I52" s="4">
-        <f t="shared" ref="I52:I57" si="65">G52/E52</f>
+        <f t="shared" ref="I52:I57" si="37">G52/E52</f>
         <v>1.1211909792953998</v>
       </c>
       <c r="J52" s="4">
-        <f t="shared" ref="J52:J57" si="66">F52*E52</f>
+        <f t="shared" ref="J52:J57" si="38">F52*E52</f>
         <v>0.83928086060000007</v>
       </c>
       <c r="K52" s="4">
-        <f t="shared" ref="K52:K57" si="67">H52*G52</f>
+        <f t="shared" ref="K52:K57" si="39">H52*G52</f>
         <v>0.69708046499999998</v>
       </c>
       <c r="L52" s="4">
-        <f>J52-K52</f>
+        <f t="shared" ref="L52:L57" si="40">J52-K52</f>
         <v>0.14220039560000008</v>
       </c>
       <c r="M52" s="4">
-        <f>K52/J52</f>
+        <f t="shared" ref="M52:M57" si="41">K52/J52</f>
         <v>0.83056876157244752</v>
       </c>
       <c r="N52" s="6">
@@ -3080,11 +6717,11 @@
         <v>0.1</v>
       </c>
       <c r="C53" s="4">
-        <f t="shared" si="64"/>
+        <f t="shared" si="35"/>
         <v>1.25</v>
       </c>
       <c r="D53" s="4" t="str">
-        <f t="shared" ref="D53:D56" si="68">TEXT(ROUND(E53,3),"#")&amp;"_"&amp;TEXT(B53,"0,##")</f>
+        <f t="shared" si="36"/>
         <v>5_0,1</v>
       </c>
       <c r="E53" s="7">
@@ -3100,23 +6737,23 @@
         <v>0.27245999999999998</v>
       </c>
       <c r="I53" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="37"/>
         <v>1.0939131060796947</v>
       </c>
       <c r="J53" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="38"/>
         <v>1.7853570774</v>
       </c>
       <c r="K53" s="4">
-        <f t="shared" si="67"/>
+        <f t="shared" si="39"/>
         <v>1.490410692</v>
       </c>
       <c r="L53" s="4">
-        <f t="shared" ref="L53:L56" si="69">J53-K53</f>
+        <f t="shared" si="40"/>
         <v>0.29494638540000007</v>
       </c>
       <c r="M53" s="4">
-        <f t="shared" ref="M53:M56" si="70">K53/J53</f>
+        <f t="shared" si="41"/>
         <v>0.83479697751582116</v>
       </c>
       <c r="N53" s="6">
@@ -3128,11 +6765,11 @@
         <v>0.1</v>
       </c>
       <c r="C54" s="4">
-        <f t="shared" si="64"/>
+        <f t="shared" si="35"/>
         <v>1.25</v>
       </c>
       <c r="D54" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="36"/>
         <v>5_0,1</v>
       </c>
       <c r="E54" s="7">
@@ -3148,23 +6785,23 @@
         <v>0.52985000000000004</v>
       </c>
       <c r="I54" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="37"/>
         <v>1.0680428440110306</v>
       </c>
       <c r="J54" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="38"/>
         <v>3.426175572</v>
       </c>
       <c r="K54" s="4">
-        <f t="shared" si="67"/>
+        <f t="shared" si="39"/>
         <v>2.8318892949999999</v>
       </c>
       <c r="L54" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="40"/>
         <v>0.59428627700000014</v>
       </c>
       <c r="M54" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="41"/>
         <v>0.82654529386738618</v>
       </c>
       <c r="N54" s="6">
@@ -3176,11 +6813,11 @@
         <v>0.1</v>
       </c>
       <c r="C55" s="4">
-        <f t="shared" si="64"/>
+        <f t="shared" si="35"/>
         <v>1.25</v>
       </c>
       <c r="D55" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="36"/>
         <v>5_0,1</v>
       </c>
       <c r="E55" s="7">
@@ -3196,23 +6833,23 @@
         <v>1.0248280000000001</v>
       </c>
       <c r="I55" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="37"/>
         <v>1.0396152461704593</v>
       </c>
       <c r="J55" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="38"/>
         <v>6.5702883400000012</v>
       </c>
       <c r="K55" s="4">
-        <f t="shared" si="67"/>
+        <f t="shared" si="39"/>
         <v>5.3277733235999998</v>
       </c>
       <c r="L55" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="40"/>
         <v>1.2425150164000014</v>
       </c>
       <c r="M55" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="41"/>
         <v>0.8108888145995734</v>
       </c>
       <c r="N55" s="6">
@@ -3224,11 +6861,11 @@
         <v>0.1</v>
       </c>
       <c r="C56" s="4">
-        <f t="shared" si="64"/>
+        <f t="shared" si="35"/>
         <v>1.25</v>
       </c>
       <c r="D56" s="4" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="36"/>
         <v>5_0,1</v>
       </c>
       <c r="E56" s="7">
@@ -3244,23 +6881,23 @@
         <v>1.9396</v>
       </c>
       <c r="I56" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="37"/>
         <v>1.000879982400352</v>
       </c>
       <c r="J56" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="38"/>
         <v>12.38574771</v>
       </c>
       <c r="K56" s="4">
-        <f t="shared" si="67"/>
+        <f t="shared" si="39"/>
         <v>9.7067282000000006</v>
       </c>
       <c r="L56" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="40"/>
         <v>2.6790195099999998</v>
       </c>
       <c r="M56" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="41"/>
         <v>0.78370143065024533</v>
       </c>
       <c r="N56" s="6">
@@ -3272,11 +6909,11 @@
         <v>0.1</v>
       </c>
       <c r="C57" s="4">
-        <f t="shared" si="64"/>
+        <f t="shared" si="35"/>
         <v>1.25</v>
       </c>
       <c r="D57" s="4" t="str">
-        <f t="shared" ref="D57" si="71">TEXT(ROUND(E57,3),"#")&amp;"_"&amp;TEXT(B57,"0,##")</f>
+        <f t="shared" si="36"/>
         <v>5_0,1</v>
       </c>
       <c r="E57" s="7">
@@ -3292,23 +6929,23 @@
         <v>4.2918000000000003</v>
       </c>
       <c r="I57" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="37"/>
         <v>0.92489004398240704</v>
       </c>
       <c r="J57" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="38"/>
         <v>27.332178499999998</v>
       </c>
       <c r="K57" s="4">
-        <f t="shared" si="67"/>
+        <f t="shared" si="39"/>
         <v>19.855154339999999</v>
       </c>
       <c r="L57" s="4">
-        <f t="shared" ref="L57" si="72">J57-K57</f>
+        <f t="shared" si="40"/>
         <v>7.4770241599999991</v>
       </c>
       <c r="M57" s="4">
-        <f t="shared" ref="M57" si="73">K57/J57</f>
+        <f t="shared" si="41"/>
         <v>0.72643877764811171</v>
       </c>
       <c r="N57" s="6">
@@ -3320,11 +6957,11 @@
         <v>0.1</v>
       </c>
       <c r="C59" s="4">
-        <f t="shared" ref="C59:C64" si="74">1/(1-2*B59)</f>
+        <f t="shared" ref="C59:C64" si="42">1/(1-2*B59)</f>
         <v>1.25</v>
       </c>
       <c r="D59" s="4" t="str">
-        <f>TEXT(ROUND(E59,3),"#")&amp;"_"&amp;TEXT(B59,"0,##")</f>
+        <f t="shared" ref="D59:D64" si="43">TEXT(ROUND(E59,3),"#")&amp;"_"&amp;TEXT(B59,"0,##")</f>
         <v>9_0,1</v>
       </c>
       <c r="E59" s="7">
@@ -3340,23 +6977,23 @@
         <v>0.19339000000000001</v>
       </c>
       <c r="I59" s="4">
-        <f t="shared" ref="I59:I64" si="75">G59/E59</f>
+        <f t="shared" ref="I59:I64" si="44">G59/E59</f>
         <v>1.1877997327192318</v>
       </c>
       <c r="J59" s="4">
-        <f t="shared" ref="J59:J64" si="76">F59*E59</f>
+        <f t="shared" ref="J59:J64" si="45">F59*E59</f>
         <v>2.3482017221999998</v>
       </c>
       <c r="K59" s="4">
-        <f t="shared" ref="K59:K64" si="77">H59*G59</f>
+        <f t="shared" ref="K59:K64" si="46">H59*G59</f>
         <v>2.067783897</v>
       </c>
       <c r="L59" s="4">
-        <f>J59-K59</f>
+        <f t="shared" ref="L59:L64" si="47">J59-K59</f>
         <v>0.2804178251999998</v>
       </c>
       <c r="M59" s="4">
-        <f>K59/J59</f>
+        <f t="shared" ref="M59:M64" si="48">K59/J59</f>
         <v>0.88058188419294747</v>
       </c>
       <c r="N59" s="6">
@@ -3368,11 +7005,11 @@
         <v>0.1</v>
       </c>
       <c r="C60" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="42"/>
         <v>1.25</v>
       </c>
       <c r="D60" s="4" t="str">
-        <f t="shared" ref="D60:D64" si="78">TEXT(ROUND(E60,3),"#")&amp;"_"&amp;TEXT(B60,"0,##")</f>
+        <f t="shared" si="43"/>
         <v>9_0,1</v>
       </c>
       <c r="E60" s="7">
@@ -3388,23 +7025,23 @@
         <v>0.3826</v>
       </c>
       <c r="I60" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="44"/>
         <v>1.1704926403658726</v>
       </c>
       <c r="J60" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="45"/>
         <v>4.5286232200000001</v>
       </c>
       <c r="K60" s="4">
-        <f t="shared" si="77"/>
+        <f t="shared" si="46"/>
         <v>4.0343257000000001</v>
       </c>
       <c r="L60" s="4">
-        <f t="shared" ref="L60:L64" si="79">J60-K60</f>
+        <f t="shared" si="47"/>
         <v>0.49429751999999993</v>
       </c>
       <c r="M60" s="4">
-        <f t="shared" ref="M60:M64" si="80">K60/J60</f>
+        <f t="shared" si="48"/>
         <v>0.89085037637553788</v>
       </c>
       <c r="N60" s="6">
@@ -3416,11 +7053,11 @@
         <v>0.1</v>
       </c>
       <c r="C61" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="42"/>
         <v>1.25</v>
       </c>
       <c r="D61" s="4" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="43"/>
         <v>9_0,1</v>
       </c>
       <c r="E61" s="7">
@@ -3436,23 +7073,23 @@
         <v>0.69067999999999996</v>
       </c>
       <c r="I61" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="44"/>
         <v>1.1552775710175196</v>
       </c>
       <c r="J61" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="45"/>
         <v>8.0591339289999997</v>
       </c>
       <c r="K61" s="4">
-        <f t="shared" si="77"/>
+        <f t="shared" si="46"/>
         <v>7.1823813199999993</v>
       </c>
       <c r="L61" s="4">
-        <f t="shared" si="79"/>
+        <f t="shared" si="47"/>
         <v>0.8767526090000004</v>
       </c>
       <c r="M61" s="4">
-        <f t="shared" si="80"/>
+        <f t="shared" si="48"/>
         <v>0.89121007086814963</v>
       </c>
       <c r="N61" s="6">
@@ -3464,11 +7101,11 @@
         <v>0.1</v>
       </c>
       <c r="C62" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="42"/>
         <v>1.25</v>
       </c>
       <c r="D62" s="4" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="43"/>
         <v>9_0,1</v>
       </c>
       <c r="E62" s="7">
@@ -3484,23 +7121,23 @@
         <v>1.3509</v>
       </c>
       <c r="I62" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="44"/>
         <v>1.1356990489734247</v>
       </c>
       <c r="J62" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="45"/>
         <v>15.626198872</v>
       </c>
       <c r="K62" s="4">
-        <f t="shared" si="77"/>
+        <f t="shared" si="46"/>
         <v>13.809169980000002</v>
       </c>
       <c r="L62" s="4">
-        <f t="shared" si="79"/>
+        <f t="shared" si="47"/>
         <v>1.817028891999998</v>
       </c>
       <c r="M62" s="4">
-        <f t="shared" si="80"/>
+        <f t="shared" si="48"/>
         <v>0.88371907289264928</v>
       </c>
       <c r="N62" s="6">
@@ -3512,11 +7149,11 @@
         <v>0.1</v>
       </c>
       <c r="C63" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="42"/>
         <v>1.25</v>
       </c>
       <c r="D63" s="4" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="43"/>
         <v>9_0,1</v>
       </c>
       <c r="E63" s="7">
@@ -3532,23 +7169,23 @@
         <v>2.4567999999999999</v>
       </c>
       <c r="I63" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="44"/>
         <v>1.109671972718083</v>
       </c>
       <c r="J63" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="45"/>
         <v>28.318355063999999</v>
       </c>
       <c r="K63" s="4">
-        <f t="shared" si="77"/>
+        <f t="shared" si="46"/>
         <v>24.542449279999996</v>
       </c>
       <c r="L63" s="4">
-        <f t="shared" si="79"/>
+        <f t="shared" si="47"/>
         <v>3.7759057840000025</v>
       </c>
       <c r="M63" s="4">
-        <f t="shared" si="80"/>
+        <f t="shared" si="48"/>
         <v>0.8666622487264396</v>
       </c>
       <c r="N63" s="6">
@@ -3560,11 +7197,11 @@
         <v>0.1</v>
       </c>
       <c r="C64" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="42"/>
         <v>1.25</v>
       </c>
       <c r="D64" s="4" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="43"/>
         <v>9_0,1</v>
       </c>
       <c r="E64" s="7">
@@ -3580,23 +7217,23 @@
         <v>4.6704999999999997</v>
       </c>
       <c r="I64" s="4">
-        <f t="shared" si="75"/>
+        <f t="shared" si="44"/>
         <v>1.0759999999999998</v>
       </c>
       <c r="J64" s="4">
-        <f t="shared" si="76"/>
+        <f t="shared" si="45"/>
         <v>53.734500000000004</v>
       </c>
       <c r="K64" s="4">
-        <f t="shared" si="77"/>
+        <f t="shared" si="46"/>
         <v>45.229121999999997</v>
       </c>
       <c r="L64" s="4">
-        <f t="shared" si="79"/>
+        <f t="shared" si="47"/>
         <v>8.5053780000000074</v>
       </c>
       <c r="M64" s="4">
-        <f t="shared" si="80"/>
+        <f t="shared" si="48"/>
         <v>0.84171476425759972</v>
       </c>
       <c r="N64" s="6">
@@ -3608,7 +7245,7 @@
         <v>0.1</v>
       </c>
       <c r="C66" s="4">
-        <f t="shared" ref="C66:C70" si="81">1/(1-2*B66)</f>
+        <f>1/(1-2*B66)</f>
         <v>1.25</v>
       </c>
       <c r="D66" s="4" t="str">
@@ -3628,15 +7265,15 @@
         <v>0.26428000000000001</v>
       </c>
       <c r="I66" s="4">
-        <f t="shared" ref="I66:I70" si="82">G66/E66</f>
+        <f>G66/E66</f>
         <v>1.2140774677217825</v>
       </c>
       <c r="J66" s="4">
-        <f t="shared" ref="J66:J70" si="83">F66*E66</f>
+        <f>F66*E66</f>
         <v>4.2603343999999996</v>
       </c>
       <c r="K66" s="4">
-        <f t="shared" ref="K66:K70" si="84">H66*G66</f>
+        <f>H66*G66</f>
         <v>3.8518810000000001</v>
       </c>
       <c r="L66" s="4">
@@ -3656,11 +7293,11 @@
         <v>0.1</v>
       </c>
       <c r="C67" s="4">
-        <f t="shared" si="81"/>
+        <f>1/(1-2*B67)</f>
         <v>1.25</v>
       </c>
       <c r="D67" s="4" t="str">
-        <f t="shared" ref="D67:D70" si="85">TEXT(ROUND(E67,3),"#")&amp;"_"&amp;TEXT(B67,"0,##")</f>
+        <f>TEXT(ROUND(E67,3),"#")&amp;"_"&amp;TEXT(B67,"0,##")</f>
         <v>12_0,1</v>
       </c>
       <c r="E67" s="7">
@@ -3676,23 +7313,23 @@
         <v>0.52168999999999999</v>
       </c>
       <c r="I67" s="4">
-        <f t="shared" si="82"/>
+        <f>G67/E67</f>
         <v>1.1970546342032269</v>
       </c>
       <c r="J67" s="4">
-        <f t="shared" si="83"/>
+        <f>F67*E67</f>
         <v>8.2109048819999995</v>
       </c>
       <c r="K67" s="4">
-        <f t="shared" si="84"/>
+        <f>H67*G67</f>
         <v>7.4972069900000005</v>
       </c>
       <c r="L67" s="4">
-        <f t="shared" ref="L67:L70" si="86">J67-K67</f>
+        <f>J67-K67</f>
         <v>0.713697891999999</v>
       </c>
       <c r="M67" s="4">
-        <f t="shared" ref="M67:M70" si="87">K67/J67</f>
+        <f>K67/J67</f>
         <v>0.91307926443471876</v>
       </c>
       <c r="N67" s="6">
@@ -3704,11 +7341,11 @@
         <v>0.1</v>
       </c>
       <c r="C68" s="4">
-        <f t="shared" si="81"/>
+        <f>1/(1-2*B68)</f>
         <v>1.25</v>
       </c>
       <c r="D68" s="4" t="str">
-        <f t="shared" si="85"/>
+        <f>TEXT(ROUND(E68,3),"#")&amp;"_"&amp;TEXT(B68,"0,##")</f>
         <v>12_0,1</v>
       </c>
       <c r="E68" s="7">
@@ -3724,23 +7361,23 @@
         <v>0.94108000000000003</v>
       </c>
       <c r="I68" s="4">
-        <f t="shared" si="82"/>
+        <f>G68/E68</f>
         <v>1.1824473445320762</v>
       </c>
       <c r="J68" s="4">
-        <f t="shared" si="83"/>
+        <f>F68*E68</f>
         <v>14.634497240000002</v>
       </c>
       <c r="K68" s="4">
-        <f t="shared" si="84"/>
+        <f>H68*G68</f>
         <v>13.361453840000001</v>
       </c>
       <c r="L68" s="4">
-        <f t="shared" si="86"/>
+        <f>J68-K68</f>
         <v>1.2730434000000006</v>
       </c>
       <c r="M68" s="4">
-        <f t="shared" si="87"/>
+        <f>K68/J68</f>
         <v>0.91301078683315251</v>
       </c>
       <c r="N68" s="6">
@@ -3752,11 +7389,11 @@
         <v>0.1</v>
       </c>
       <c r="C69" s="4">
-        <f t="shared" si="81"/>
+        <f>1/(1-2*B69)</f>
         <v>1.25</v>
       </c>
       <c r="D69" s="4" t="str">
-        <f t="shared" si="85"/>
+        <f>TEXT(ROUND(E69,3),"#")&amp;"_"&amp;TEXT(B69,"0,##")</f>
         <v>12_0,1</v>
       </c>
       <c r="E69" s="7">
@@ -3772,23 +7409,23 @@
         <v>1.8482799999999999</v>
       </c>
       <c r="I69" s="4">
-        <f t="shared" si="82"/>
+        <f>G69/E69</f>
         <v>1.1644816844630275</v>
       </c>
       <c r="J69" s="4">
-        <f t="shared" si="83"/>
+        <f>F69*E69</f>
         <v>28.521928719999998</v>
       </c>
       <c r="K69" s="4">
-        <f t="shared" si="84"/>
+        <f>H69*G69</f>
         <v>25.840802679999999</v>
       </c>
       <c r="L69" s="4">
-        <f t="shared" si="86"/>
+        <f>J69-K69</f>
         <v>2.6811260399999988</v>
       </c>
       <c r="M69" s="4">
-        <f t="shared" si="87"/>
+        <f>K69/J69</f>
         <v>0.90599773015630769</v>
       </c>
       <c r="N69" s="6">
@@ -3800,11 +7437,11 @@
         <v>0.1</v>
       </c>
       <c r="C70" s="4">
-        <f t="shared" si="81"/>
+        <f>1/(1-2*B70)</f>
         <v>1.25</v>
       </c>
       <c r="D70" s="4" t="str">
-        <f t="shared" si="85"/>
+        <f>TEXT(ROUND(E70,3),"#")&amp;"_"&amp;TEXT(B70,"0,##")</f>
         <v>12_0,1</v>
       </c>
       <c r="E70" s="7">
@@ -3820,23 +7457,23 @@
         <v>4.7336999999999998</v>
       </c>
       <c r="I70" s="4">
-        <f t="shared" si="82"/>
+        <f>G70/E70</f>
         <v>1.1257142857142857</v>
       </c>
       <c r="J70" s="4">
-        <f t="shared" si="83"/>
+        <f>F70*E70</f>
         <v>73.192612499999996</v>
       </c>
       <c r="K70" s="4">
-        <f t="shared" si="84"/>
+        <f>H70*G70</f>
         <v>64.345184099999997</v>
       </c>
       <c r="L70" s="4">
-        <f t="shared" si="86"/>
+        <f>J70-K70</f>
         <v>8.8474283999999983</v>
       </c>
       <c r="M70" s="4">
-        <f t="shared" si="87"/>
+        <f>K70/J70</f>
         <v>0.87912129246650406</v>
       </c>
       <c r="N70" s="6">
@@ -3913,7 +7550,7 @@
         <v>1.25</v>
       </c>
       <c r="D73" s="4" t="str">
-        <f t="shared" ref="D73:D75" si="88">TEXT(ROUND(E73,3),"#")&amp;"_"&amp;TEXT(B73,"0,##")</f>
+        <f>TEXT(ROUND(E73,3),"#")&amp;"_"&amp;TEXT(B73,"0,##")</f>
         <v>24_0,1</v>
       </c>
       <c r="E73" s="7">
@@ -3941,11 +7578,11 @@
         <v>29.238391799999999</v>
       </c>
       <c r="L73" s="4">
-        <f t="shared" ref="L73:L75" si="89">J73-K73</f>
+        <f>J73-K73</f>
         <v>1.762931499999997</v>
       </c>
       <c r="M73" s="4">
-        <f t="shared" ref="M73:M75" si="90">K73/J73</f>
+        <f>K73/J73</f>
         <v>0.94313366939404175</v>
       </c>
       <c r="N73" s="6">
@@ -3961,7 +7598,7 @@
         <v>1.25</v>
       </c>
       <c r="D74" s="4" t="str">
-        <f t="shared" si="88"/>
+        <f>TEXT(ROUND(E74,3),"#")&amp;"_"&amp;TEXT(B74,"0,##")</f>
         <v>24_0,1</v>
       </c>
       <c r="E74" s="7">
@@ -3989,11 +7626,11 @@
         <v>57.245312699999999</v>
       </c>
       <c r="L74" s="4">
-        <f t="shared" si="89"/>
+        <f>J74-K74</f>
         <v>3.3871403000000058</v>
       </c>
       <c r="M74" s="4">
-        <f t="shared" si="90"/>
+        <f>K74/J74</f>
         <v>0.94413651217442895</v>
       </c>
       <c r="N74" s="6">
@@ -4009,7 +7646,7 @@
         <v>1.25</v>
       </c>
       <c r="D75" s="4" t="str">
-        <f t="shared" si="88"/>
+        <f>TEXT(ROUND(E75,3),"#")&amp;"_"&amp;TEXT(B75,"0,##")</f>
         <v>24_0,1</v>
       </c>
       <c r="E75" s="7">
@@ -4037,11 +7674,11 @@
         <v>137.47504069999999</v>
       </c>
       <c r="L75" s="4">
-        <f t="shared" si="89"/>
+        <f>J75-K75</f>
         <v>9.7374723000000358</v>
       </c>
       <c r="M75" s="4">
-        <f t="shared" si="90"/>
+        <f>K75/J75</f>
         <v>0.93385431644659156</v>
       </c>
       <c r="N75" s="6">
@@ -4053,11 +7690,11 @@
         <v>0.2</v>
       </c>
       <c r="C77" s="4">
-        <f t="shared" ref="C77:C82" si="91">1/(1-2*B77)</f>
+        <f t="shared" ref="C77:C82" si="49">1/(1-2*B77)</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="D77" s="4" t="str">
-        <f>TEXT(ROUND(E77,3),"#,#")&amp;"_"&amp;TEXT(B77,"0,##")</f>
+        <f t="shared" ref="D77:D82" si="50">TEXT(ROUND(E77,3),"#,#")&amp;"_"&amp;TEXT(B77,"0,##")</f>
         <v>3,3_0,2</v>
       </c>
       <c r="E77" s="7">
@@ -4073,23 +7710,23 @@
         <v>0.11538</v>
       </c>
       <c r="I77" s="4">
-        <f t="shared" ref="I77:I82" si="92">G77/E77</f>
+        <f t="shared" ref="I77:I82" si="51">G77/E77</f>
         <v>1.4024113174396413</v>
       </c>
       <c r="J77" s="4">
-        <f t="shared" ref="J77:J82" si="93">F77*E77</f>
+        <f t="shared" ref="J77:J82" si="52">F77*E77</f>
         <v>0.69528098309999997</v>
       </c>
       <c r="K77" s="4">
-        <f t="shared" ref="K77:K82" si="94">H77*G77</f>
+        <f t="shared" ref="K77:K82" si="53">H77*G77</f>
         <v>0.53415171000000006</v>
       </c>
       <c r="L77" s="4">
-        <f>J77-K77</f>
+        <f t="shared" ref="L77:L82" si="54">J77-K77</f>
         <v>0.16112927309999991</v>
       </c>
       <c r="M77" s="4">
-        <f>K77/J77</f>
+        <f t="shared" ref="M77:M82" si="55">K77/J77</f>
         <v>0.76825301278688185</v>
       </c>
       <c r="N77" s="6">
@@ -4101,11 +7738,11 @@
         <v>0.2</v>
       </c>
       <c r="C78" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="49"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="D78" s="4" t="str">
-        <f t="shared" ref="D78:D79" si="95">TEXT(ROUND(E78,3),"#,#")&amp;"_"&amp;TEXT(B78,"0,##")</f>
+        <f t="shared" si="50"/>
         <v>3,3_0,2</v>
       </c>
       <c r="E78" s="7">
@@ -4121,23 +7758,23 @@
         <v>0.224</v>
       </c>
       <c r="I78" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="51"/>
         <v>1.361431409122841</v>
       </c>
       <c r="J78" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="52"/>
         <v>1.3090370224000001</v>
       </c>
       <c r="K78" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="53"/>
         <v>1.0071264</v>
       </c>
       <c r="L78" s="4">
-        <f t="shared" ref="L78:L80" si="96">J78-K78</f>
+        <f t="shared" si="54"/>
         <v>0.30191062240000011</v>
       </c>
       <c r="M78" s="4">
-        <f t="shared" ref="M78:M80" si="97">K78/J78</f>
+        <f t="shared" si="55"/>
         <v>0.76936433635278356</v>
       </c>
       <c r="N78" s="6">
@@ -4149,11 +7786,11 @@
         <v>0.2</v>
       </c>
       <c r="C79" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="49"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="D79" s="4" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="50"/>
         <v>3,3_0,2</v>
       </c>
       <c r="E79" s="7">
@@ -4169,23 +7806,23 @@
         <v>0.43153999999999998</v>
       </c>
       <c r="I79" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="51"/>
         <v>1.3173679905480322</v>
       </c>
       <c r="J79" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="52"/>
         <v>2.476863324</v>
       </c>
       <c r="K79" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="53"/>
         <v>1.8765516899999997</v>
       </c>
       <c r="L79" s="4">
-        <f t="shared" si="96"/>
+        <f t="shared" si="54"/>
         <v>0.60031163400000032</v>
       </c>
       <c r="M79" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="55"/>
         <v>0.75763231334439174</v>
       </c>
       <c r="N79" s="6">
@@ -4197,11 +7834,11 @@
         <v>0.2</v>
       </c>
       <c r="C80" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="49"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="D80" s="4" t="str">
-        <f>TEXT(ROUND(E80,3),"#,#")&amp;"_"&amp;TEXT(B80,"0,##")</f>
+        <f t="shared" si="50"/>
         <v>3,3_0,2</v>
       </c>
       <c r="E80" s="7">
@@ -4217,23 +7854,23 @@
         <v>0.81740000000000002</v>
       </c>
       <c r="I80" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="51"/>
         <v>1.2601653092736687</v>
       </c>
       <c r="J80" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="52"/>
         <v>4.6498886780000008</v>
       </c>
       <c r="K80" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="53"/>
         <v>3.4021822800000003</v>
       </c>
       <c r="L80" s="4">
-        <f t="shared" si="96"/>
+        <f t="shared" si="54"/>
         <v>1.2477063980000005</v>
       </c>
       <c r="M80" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="55"/>
         <v>0.7316696195538468</v>
       </c>
       <c r="N80" s="6">
@@ -4245,11 +7882,11 @@
         <v>0.2</v>
       </c>
       <c r="C81" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="49"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="D81" s="4" t="str">
-        <f>TEXT(ROUND(E81,3),"#,#")&amp;"_"&amp;TEXT(B81,"0,##")</f>
+        <f t="shared" si="50"/>
         <v>3,3_0,2</v>
       </c>
       <c r="E81" s="7">
@@ -4265,23 +7902,23 @@
         <v>1.5181500000000001</v>
       </c>
       <c r="I81" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="51"/>
         <v>1.1800411522633745</v>
       </c>
       <c r="J81" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="52"/>
         <v>8.5975032959999993</v>
       </c>
       <c r="K81" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="53"/>
         <v>5.9204813700000001</v>
       </c>
       <c r="L81" s="4">
-        <f t="shared" ref="L81" si="98">J81-K81</f>
+        <f t="shared" si="54"/>
         <v>2.6770219259999992</v>
       </c>
       <c r="M81" s="4">
-        <f t="shared" ref="M81" si="99">K81/J81</f>
+        <f t="shared" si="55"/>
         <v>0.6886279849121445</v>
       </c>
       <c r="N81" s="6">
@@ -4293,11 +7930,11 @@
         <v>0.2</v>
       </c>
       <c r="C82" s="4">
-        <f t="shared" si="91"/>
+        <f t="shared" si="49"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="D82" s="4" t="str">
-        <f>TEXT(ROUND(E82,3),"#,#")&amp;"_"&amp;TEXT(B82,"0,##")</f>
+        <f t="shared" si="50"/>
         <v>3,3_0,2</v>
       </c>
       <c r="E82" s="7">
@@ -4313,23 +7950,23 @@
         <v>3.1640000000000001</v>
       </c>
       <c r="I82" s="4">
-        <f t="shared" si="92"/>
+        <f t="shared" si="51"/>
         <v>1.0281528122540413</v>
       </c>
       <c r="J82" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="52"/>
         <v>17.815566539999999</v>
       </c>
       <c r="K82" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="53"/>
         <v>10.7462096</v>
       </c>
       <c r="L82" s="4">
-        <f t="shared" ref="L82" si="100">J82-K82</f>
+        <f t="shared" si="54"/>
         <v>7.0693569399999987</v>
       </c>
       <c r="M82" s="4">
-        <f t="shared" ref="M82" si="101">K82/J82</f>
+        <f t="shared" si="55"/>
         <v>0.60319213401787231</v>
       </c>
       <c r="N82" s="6">
@@ -4393,7 +8030,7 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="D85" s="4" t="str">
-        <f t="shared" ref="D85:D88" si="102">TEXT(ROUND(E85,3),"#")&amp;"_"&amp;TEXT(B85,"0,##")</f>
+        <f>TEXT(ROUND(E85,3),"#")&amp;"_"&amp;TEXT(B85,"0,##")</f>
         <v>5_0,2</v>
       </c>
       <c r="E85" s="7">
@@ -4421,11 +8058,11 @@
         <v>2.6810177060000004</v>
       </c>
       <c r="L85" s="4">
-        <f t="shared" ref="L85:L88" si="103">J85-K85</f>
+        <f>J85-K85</f>
         <v>0.54448491999999948</v>
       </c>
       <c r="M85" s="4">
-        <f t="shared" ref="M85:M88" si="104">K85/J85</f>
+        <f>K85/J85</f>
         <v>0.83119377562707975</v>
       </c>
       <c r="N85" s="6">
@@ -4441,7 +8078,7 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="D86" s="4" t="str">
-        <f t="shared" si="102"/>
+        <f>TEXT(ROUND(E86,3),"#")&amp;"_"&amp;TEXT(B86,"0,##")</f>
         <v>5_0,2</v>
       </c>
       <c r="E86" s="7">
@@ -4469,11 +8106,11 @@
         <v>5.0477891799999997</v>
       </c>
       <c r="L86" s="4">
-        <f t="shared" si="103"/>
+        <f>J86-K86</f>
         <v>1.0983129800000002</v>
       </c>
       <c r="M86" s="4">
-        <f t="shared" si="104"/>
+        <f>K86/J86</f>
         <v>0.8212992639224207</v>
       </c>
       <c r="N86" s="6">
@@ -4489,7 +8126,7 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="D87" s="4" t="str">
-        <f t="shared" si="102"/>
+        <f>TEXT(ROUND(E87,3),"#")&amp;"_"&amp;TEXT(B87,"0,##")</f>
         <v>5_0,2</v>
       </c>
       <c r="E87" s="7">
@@ -4517,11 +8154,11 @@
         <v>9.2859415999999992</v>
       </c>
       <c r="L87" s="4">
-        <f t="shared" si="103"/>
+        <f>J87-K87</f>
         <v>2.3670830847000008</v>
       </c>
       <c r="M87" s="4">
-        <f t="shared" si="104"/>
+        <f>K87/J87</f>
         <v>0.79686964125220683</v>
       </c>
       <c r="N87" s="6">
@@ -4537,7 +8174,7 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="D88" s="4" t="str">
-        <f t="shared" si="102"/>
+        <f>TEXT(ROUND(E88,3),"#")&amp;"_"&amp;TEXT(B88,"0,##")</f>
         <v>5_0,2</v>
       </c>
       <c r="E88" s="7">
@@ -4565,11 +8202,11 @@
         <v>19.349623999999999</v>
       </c>
       <c r="L88" s="4">
-        <f t="shared" si="103"/>
+        <f>J88-K88</f>
         <v>6.859564915</v>
       </c>
       <c r="M88" s="4">
-        <f t="shared" si="104"/>
+        <f>K88/J88</f>
         <v>0.7382763374613952</v>
       </c>
       <c r="N88" s="6">
@@ -4581,7 +8218,7 @@
         <v>0.2</v>
       </c>
       <c r="C90" s="4">
-        <f t="shared" ref="C90:C94" si="105">1/(1-2*B90)</f>
+        <f>1/(1-2*B90)</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="D90" s="4" t="str">
@@ -4601,15 +8238,15 @@
         <v>0.31711</v>
       </c>
       <c r="I90" s="4">
-        <f t="shared" ref="I90:I94" si="106">G90/E90</f>
+        <f>G90/E90</f>
         <v>1.5887110212515414</v>
       </c>
       <c r="J90" s="4">
-        <f t="shared" ref="J90:J94" si="107">F90*E90</f>
+        <f>F90*E90</f>
         <v>5.153203199</v>
       </c>
       <c r="K90" s="4">
-        <f t="shared" ref="K90:K94" si="108">H90*G90</f>
+        <f>H90*G90</f>
         <v>4.535021821</v>
       </c>
       <c r="L90" s="4">
@@ -4629,11 +8266,11 @@
         <v>0.2</v>
       </c>
       <c r="C91" s="4">
-        <f t="shared" si="105"/>
+        <f>1/(1-2*B91)</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="D91" s="4" t="str">
-        <f t="shared" ref="D91:D94" si="109">TEXT(ROUND(E91,3),"#")&amp;"_"&amp;TEXT(B91,"0,##")</f>
+        <f>TEXT(ROUND(E91,3),"#")&amp;"_"&amp;TEXT(B91,"0,##")</f>
         <v>9_0,2</v>
       </c>
       <c r="E91" s="7">
@@ -4649,23 +8286,23 @@
         <v>0.69982999999999995</v>
       </c>
       <c r="I91" s="4">
-        <f t="shared" si="106"/>
+        <f>G91/E91</f>
         <v>1.5585670647042489</v>
       </c>
       <c r="J91" s="4">
-        <f t="shared" si="107"/>
+        <f>F91*E91</f>
         <v>11.061371749999999</v>
       </c>
       <c r="K91" s="4">
-        <f t="shared" si="108"/>
+        <f>H91*G91</f>
         <v>9.8193147300000003</v>
       </c>
       <c r="L91" s="4">
-        <f t="shared" ref="L91:L94" si="110">J91-K91</f>
+        <f>J91-K91</f>
         <v>1.242057019999999</v>
       </c>
       <c r="M91" s="4">
-        <f t="shared" ref="M91:M94" si="111">K91/J91</f>
+        <f>K91/J91</f>
         <v>0.88771220712295484</v>
       </c>
       <c r="N91" s="6">
@@ -4677,11 +8314,11 @@
         <v>0.2</v>
       </c>
       <c r="C92" s="4">
-        <f t="shared" si="105"/>
+        <f>1/(1-2*B92)</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="D92" s="4" t="str">
-        <f t="shared" si="109"/>
+        <f>TEXT(ROUND(E92,3),"#")&amp;"_"&amp;TEXT(B92,"0,##")</f>
         <v>9_0,2</v>
       </c>
       <c r="E92" s="7">
@@ -4697,23 +8334,23 @@
         <v>1.365</v>
       </c>
       <c r="I92" s="4">
-        <f t="shared" si="106"/>
+        <f>G92/E92</f>
         <v>1.5246123772713136</v>
       </c>
       <c r="J92" s="4">
-        <f t="shared" si="107"/>
+        <f>F92*E92</f>
         <v>21.326827320000003</v>
       </c>
       <c r="K92" s="4">
-        <f t="shared" si="108"/>
+        <f>H92*G92</f>
         <v>18.737355000000001</v>
       </c>
       <c r="L92" s="4">
-        <f t="shared" si="110"/>
+        <f>J92-K92</f>
         <v>2.5894723200000023</v>
       </c>
       <c r="M92" s="4">
-        <f t="shared" si="111"/>
+        <f>K92/J92</f>
         <v>0.8785814560625419</v>
       </c>
       <c r="N92" s="6">
@@ -4725,11 +8362,11 @@
         <v>0.2</v>
       </c>
       <c r="C93" s="4">
-        <f t="shared" si="105"/>
+        <f>1/(1-2*B93)</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="D93" s="4" t="str">
-        <f t="shared" si="109"/>
+        <f>TEXT(ROUND(E93,3),"#")&amp;"_"&amp;TEXT(B93,"0,##")</f>
         <v>9_0,2</v>
       </c>
       <c r="E93" s="7">
@@ -4745,23 +8382,23 @@
         <v>2.6255999999999999</v>
       </c>
       <c r="I93" s="4">
-        <f t="shared" si="106"/>
+        <f>G93/E93</f>
         <v>1.4758044815563303</v>
       </c>
       <c r="J93" s="4">
-        <f t="shared" si="107"/>
+        <f>F93*E93</f>
         <v>40.734133980000003</v>
       </c>
       <c r="K93" s="4">
-        <f t="shared" si="108"/>
+        <f>H93*G93</f>
         <v>34.896324480000004</v>
       </c>
       <c r="L93" s="4">
-        <f t="shared" si="110"/>
+        <f>J93-K93</f>
         <v>5.8378094999999988</v>
       </c>
       <c r="M93" s="4">
-        <f t="shared" si="111"/>
+        <f>K93/J93</f>
         <v>0.85668507147184481</v>
       </c>
       <c r="N93" s="6">
@@ -4773,11 +8410,11 @@
         <v>0.2</v>
       </c>
       <c r="C94" s="4">
-        <f t="shared" si="105"/>
+        <f>1/(1-2*B94)</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="D94" s="4" t="str">
-        <f t="shared" si="109"/>
+        <f>TEXT(ROUND(E94,3),"#")&amp;"_"&amp;TEXT(B94,"0,##")</f>
         <v>9_0,2</v>
       </c>
       <c r="E94" s="7">
@@ -4793,23 +8430,23 @@
         <v>3.5557400000000001</v>
       </c>
       <c r="I94" s="4">
-        <f t="shared" si="106"/>
+        <f>G94/E94</f>
         <v>1.4533133366661113</v>
       </c>
       <c r="J94" s="4">
-        <f t="shared" si="107"/>
+        <f>F94*E94</f>
         <v>55.194497550000001</v>
       </c>
       <c r="K94" s="4">
-        <f t="shared" si="108"/>
+        <f>H94*G94</f>
         <v>46.516190680000001</v>
       </c>
       <c r="L94" s="4">
-        <f t="shared" si="110"/>
+        <f>J94-K94</f>
         <v>8.6783068700000001</v>
       </c>
       <c r="M94" s="4">
-        <f t="shared" si="111"/>
+        <f>K94/J94</f>
         <v>0.84276862268492558</v>
       </c>
       <c r="N94" s="6">
@@ -4834,7 +8471,7 @@
         <v>0.2</v>
       </c>
       <c r="C96" s="4">
-        <f t="shared" ref="C96:C99" si="112">1/(1-2*B96)</f>
+        <f>1/(1-2*B96)</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="D96" s="4" t="str">
@@ -4854,15 +8491,15 @@
         <v>0.40562999999999999</v>
       </c>
       <c r="I96" s="4">
-        <f t="shared" ref="I96:I99" si="113">G96/E96</f>
+        <f>G96/E96</f>
         <v>1.6212171599600931</v>
       </c>
       <c r="J96" s="4">
-        <f t="shared" ref="J96:J99" si="114">F96*E96</f>
+        <f>F96*E96</f>
         <v>8.8071421599999997</v>
       </c>
       <c r="K96" s="4">
-        <f t="shared" ref="K96:K99" si="115">H96*G96</f>
+        <f>H96*G96</f>
         <v>7.9097849999999994</v>
       </c>
       <c r="L96" s="4">
@@ -4882,11 +8519,11 @@
         <v>0.2</v>
       </c>
       <c r="C97" s="4">
-        <f t="shared" si="112"/>
+        <f>1/(1-2*B97)</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="D97" s="4" t="str">
-        <f t="shared" ref="D97:D99" si="116">TEXT(ROUND(E97,3),"#")&amp;"_"&amp;TEXT(B97,"0,##")</f>
+        <f>TEXT(ROUND(E97,3),"#")&amp;"_"&amp;TEXT(B97,"0,##")</f>
         <v>12_0,2</v>
       </c>
       <c r="E97" s="7">
@@ -4902,23 +8539,23 @@
         <v>0.79822000000000004</v>
       </c>
       <c r="I97" s="4">
-        <f t="shared" si="113"/>
+        <f>G97/E97</f>
         <v>1.5976050497143712</v>
       </c>
       <c r="J97" s="4">
-        <f t="shared" si="114"/>
+        <f>F97*E97</f>
         <v>16.890095899999999</v>
       </c>
       <c r="K97" s="4">
-        <f t="shared" si="115"/>
+        <f>H97*G97</f>
         <v>15.3138507</v>
       </c>
       <c r="L97" s="4">
-        <f t="shared" ref="L97:L99" si="117">J97-K97</f>
+        <f>J97-K97</f>
         <v>1.5762451999999989</v>
       </c>
       <c r="M97" s="4">
-        <f t="shared" ref="M97:M99" si="118">K97/J97</f>
+        <f>K97/J97</f>
         <v>0.90667636173693966</v>
       </c>
       <c r="N97" s="6">
@@ -4930,11 +8567,11 @@
         <v>0.2</v>
       </c>
       <c r="C98" s="4">
-        <f t="shared" si="112"/>
+        <f>1/(1-2*B98)</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="D98" s="4" t="str">
-        <f t="shared" si="116"/>
+        <f>TEXT(ROUND(E98,3),"#")&amp;"_"&amp;TEXT(B98,"0,##")</f>
         <v>12_0,2</v>
       </c>
       <c r="E98" s="7">
@@ -4950,23 +8587,23 @@
         <v>1.5607</v>
       </c>
       <c r="I98" s="4">
-        <f t="shared" si="113"/>
+        <f>G98/E98</f>
         <v>1.5678551801089149</v>
       </c>
       <c r="J98" s="4">
-        <f t="shared" si="114"/>
+        <f>F98*E98</f>
         <v>32.627137920000003</v>
       </c>
       <c r="K98" s="4">
-        <f t="shared" si="115"/>
+        <f>H98*G98</f>
         <v>29.386420300000001</v>
       </c>
       <c r="L98" s="4">
-        <f t="shared" si="117"/>
+        <f>J98-K98</f>
         <v>3.2407176200000016</v>
       </c>
       <c r="M98" s="4">
-        <f t="shared" si="118"/>
+        <f>K98/J98</f>
         <v>0.90067416799027644</v>
       </c>
       <c r="N98" s="6">
@@ -4978,11 +8615,11 @@
         <v>0.2</v>
       </c>
       <c r="C99" s="4">
-        <f t="shared" si="112"/>
+        <f>1/(1-2*B99)</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="D99" s="4" t="str">
-        <f t="shared" si="116"/>
+        <f>TEXT(ROUND(E99,3),"#")&amp;"_"&amp;TEXT(B99,"0,##")</f>
         <v>12_0,2</v>
       </c>
       <c r="E99" s="7">
@@ -4998,23 +8635,23 @@
         <v>3.5592999999999999</v>
       </c>
       <c r="I99" s="4">
-        <f t="shared" si="113"/>
+        <f>G99/E99</f>
         <v>1.5203507610853739</v>
       </c>
       <c r="J99" s="4">
-        <f t="shared" si="114"/>
+        <f>F99*E99</f>
         <v>74.424607199999997</v>
       </c>
       <c r="K99" s="4">
-        <f t="shared" si="115"/>
+        <f>H99*G99</f>
         <v>65.412815399999999</v>
       </c>
       <c r="L99" s="4">
-        <f t="shared" si="117"/>
+        <f>J99-K99</f>
         <v>9.0117917999999975</v>
       </c>
       <c r="M99" s="4">
-        <f t="shared" si="118"/>
+        <f>K99/J99</f>
         <v>0.87891381440841521</v>
       </c>
       <c r="N99" s="6">
@@ -5091,7 +8728,7 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="D102" s="4" t="str">
-        <f t="shared" ref="D102:D103" si="119">TEXT(ROUND(E102,3),"#")&amp;"_"&amp;TEXT(B102,"0,##")</f>
+        <f>TEXT(ROUND(E102,3),"#")&amp;"_"&amp;TEXT(B102,"0,##")</f>
         <v>24_0,2</v>
       </c>
       <c r="E102" s="7">
@@ -5119,11 +8756,11 @@
         <v>62.500650499999999</v>
       </c>
       <c r="L102" s="4">
-        <f t="shared" ref="L102:L103" si="120">J102-K102</f>
+        <f>J102-K102</f>
         <v>4.4456907500000042</v>
       </c>
       <c r="M102" s="4">
-        <f t="shared" ref="M102:M103" si="121">K102/J102</f>
+        <f>K102/J102</f>
         <v>0.93359322306504688</v>
       </c>
       <c r="N102" s="6">
@@ -5139,7 +8776,7 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="D103" s="4" t="str">
-        <f t="shared" si="119"/>
+        <f>TEXT(ROUND(E103,3),"#")&amp;"_"&amp;TEXT(B103,"0,##")</f>
         <v>24_0,2</v>
       </c>
       <c r="E103" s="7">
@@ -5167,11 +8804,11 @@
         <v>137.34745559999999</v>
       </c>
       <c r="L103" s="4">
-        <f t="shared" si="120"/>
+        <f>J103-K103</f>
         <v>10.71195000000003</v>
       </c>
       <c r="M103" s="4">
-        <f t="shared" si="121"/>
+        <f>K103/J103</f>
         <v>0.9276509995660821</v>
       </c>
       <c r="N103" s="6">
@@ -5196,11 +8833,11 @@
         <v>0.25</v>
       </c>
       <c r="C105" s="4">
-        <f t="shared" ref="C105:C110" si="122">1/(1-2*B105)</f>
+        <f t="shared" ref="C105:C110" si="56">1/(1-2*B105)</f>
         <v>2</v>
       </c>
       <c r="D105" s="4" t="str">
-        <f>TEXT(ROUND(E105,3),"#,#")&amp;"_"&amp;TEXT(B105,"0,##")</f>
+        <f t="shared" ref="D105:D110" si="57">TEXT(ROUND(E105,3),"#,#")&amp;"_"&amp;TEXT(B105,"0,##")</f>
         <v>3,3_0,25</v>
       </c>
       <c r="E105" s="7">
@@ -5216,23 +8853,23 @@
         <v>0.12417</v>
       </c>
       <c r="I105" s="4">
-        <f t="shared" ref="I105:I110" si="123">G105/E105</f>
+        <f t="shared" ref="I105:I110" si="58">G105/E105</f>
         <v>1.7065319755206112</v>
       </c>
       <c r="J105" s="4">
-        <f t="shared" ref="J105:J110" si="124">F105*E105</f>
+        <f t="shared" ref="J105:J110" si="59">F105*E105</f>
         <v>0.9122136650999999</v>
       </c>
       <c r="K105" s="4">
-        <f t="shared" ref="K105:K110" si="125">H105*G105</f>
+        <f t="shared" ref="K105:K110" si="60">H105*G105</f>
         <v>0.69977245200000004</v>
       </c>
       <c r="L105" s="4">
-        <f>J105-K105</f>
+        <f t="shared" ref="L105:L110" si="61">J105-K105</f>
         <v>0.21244121309999986</v>
       </c>
       <c r="M105" s="4">
-        <f>K105/J105</f>
+        <f t="shared" ref="M105:M110" si="62">K105/J105</f>
         <v>0.76711463418308767</v>
       </c>
       <c r="N105" s="6">
@@ -5244,11 +8881,11 @@
         <v>0.25</v>
       </c>
       <c r="C106" s="4">
-        <f t="shared" si="122"/>
+        <f t="shared" si="56"/>
         <v>2</v>
       </c>
       <c r="D106" s="4" t="str">
-        <f t="shared" ref="D106:D108" si="126">TEXT(ROUND(E106,3),"#,#")&amp;"_"&amp;TEXT(B106,"0,##")</f>
+        <f t="shared" si="57"/>
         <v>3,3_0,25</v>
       </c>
       <c r="E106" s="7">
@@ -5264,23 +8901,23 @@
         <v>0.26949000000000001</v>
       </c>
       <c r="I106" s="4">
-        <f t="shared" si="123"/>
+        <f t="shared" si="58"/>
         <v>1.6445077076834549</v>
       </c>
       <c r="J106" s="4">
-        <f t="shared" si="124"/>
+        <f t="shared" si="59"/>
         <v>1.9011019440000001</v>
       </c>
       <c r="K106" s="4">
-        <f t="shared" si="125"/>
+        <f t="shared" si="60"/>
         <v>1.4633307</v>
       </c>
       <c r="L106" s="4">
-        <f t="shared" ref="L106:L108" si="127">J106-K106</f>
+        <f t="shared" si="61"/>
         <v>0.43777124400000011</v>
       </c>
       <c r="M106" s="4">
-        <f t="shared" ref="M106:M108" si="128">K106/J106</f>
+        <f t="shared" si="62"/>
         <v>0.76972763329097937</v>
       </c>
       <c r="N106" s="6">
@@ -5292,11 +8929,11 @@
         <v>0.25</v>
       </c>
       <c r="C107" s="4">
-        <f t="shared" si="122"/>
+        <f t="shared" si="56"/>
         <v>2</v>
       </c>
       <c r="D107" s="4" t="str">
-        <f t="shared" si="126"/>
+        <f t="shared" si="57"/>
         <v>3,3_0,25</v>
       </c>
       <c r="E107" s="7">
@@ -5312,23 +8949,23 @@
         <v>0.51817999999999997</v>
       </c>
       <c r="I107" s="4">
-        <f t="shared" si="123"/>
+        <f t="shared" si="58"/>
         <v>1.5812496216019858</v>
       </c>
       <c r="J107" s="4">
-        <f t="shared" si="124"/>
+        <f t="shared" si="59"/>
         <v>3.5925466020000001</v>
       </c>
       <c r="K107" s="4">
-        <f t="shared" si="125"/>
+        <f t="shared" si="60"/>
         <v>2.7067132299999996</v>
       </c>
       <c r="L107" s="4">
-        <f t="shared" si="127"/>
+        <f t="shared" si="61"/>
         <v>0.88583337200000045</v>
       </c>
       <c r="M107" s="4">
-        <f t="shared" si="128"/>
+        <f t="shared" si="62"/>
         <v>0.75342466775327288</v>
       </c>
       <c r="N107" s="6">
@@ -5340,11 +8977,11 @@
         <v>0.25</v>
       </c>
       <c r="C108" s="4">
-        <f t="shared" si="122"/>
+        <f t="shared" si="56"/>
         <v>2</v>
       </c>
       <c r="D108" s="4" t="str">
-        <f t="shared" si="126"/>
+        <f t="shared" si="57"/>
         <v>3,3_0,25</v>
       </c>
       <c r="E108" s="7">
@@ -5360,23 +8997,23 @@
         <v>0.97423000000000004</v>
       </c>
       <c r="I108" s="4">
-        <f t="shared" si="123"/>
+        <f t="shared" si="58"/>
         <v>1.495027163063074</v>
       </c>
       <c r="J108" s="4">
-        <f t="shared" si="124"/>
+        <f t="shared" si="59"/>
         <v>6.6965525759999993</v>
       </c>
       <c r="K108" s="4">
-        <f t="shared" si="125"/>
+        <f t="shared" si="60"/>
         <v>4.8151317750000002</v>
       </c>
       <c r="L108" s="4">
-        <f t="shared" si="127"/>
+        <f t="shared" si="61"/>
         <v>1.8814208009999991</v>
       </c>
       <c r="M108" s="4">
-        <f t="shared" si="128"/>
+        <f t="shared" si="62"/>
         <v>0.71904636308794367</v>
       </c>
       <c r="N108" s="6">
@@ -5388,11 +9025,11 @@
         <v>0.25</v>
       </c>
       <c r="C109" s="4">
-        <f t="shared" si="122"/>
+        <f t="shared" si="56"/>
         <v>2</v>
       </c>
       <c r="D109" s="4" t="str">
-        <f>TEXT(ROUND(E109,3),"#,#")&amp;"_"&amp;TEXT(B109,"0,##")</f>
+        <f t="shared" si="57"/>
         <v>3,3_0,25</v>
       </c>
       <c r="E109" s="7">
@@ -5408,23 +9045,23 @@
         <v>1.7615000000000001</v>
       </c>
       <c r="I109" s="4">
-        <f t="shared" si="123"/>
+        <f t="shared" si="58"/>
         <v>1.3694842363487689</v>
       </c>
       <c r="J109" s="4">
-        <f t="shared" si="124"/>
+        <f t="shared" si="59"/>
         <v>12.028821699999998</v>
       </c>
       <c r="K109" s="4">
-        <f t="shared" si="125"/>
+        <f t="shared" si="60"/>
         <v>7.9653268499999994</v>
       </c>
       <c r="L109" s="4">
-        <f t="shared" ref="L109" si="129">J109-K109</f>
+        <f t="shared" si="61"/>
         <v>4.0634948499999988</v>
       </c>
       <c r="M109" s="4">
-        <f t="shared" ref="M109" si="130">K109/J109</f>
+        <f t="shared" si="62"/>
         <v>0.66218679174536277</v>
       </c>
       <c r="N109" s="6">
@@ -5436,11 +9073,11 @@
         <v>0.25</v>
       </c>
       <c r="C110" s="4">
-        <f t="shared" si="122"/>
+        <f t="shared" si="56"/>
         <v>2</v>
       </c>
       <c r="D110" s="4" t="str">
-        <f>TEXT(ROUND(E110,3),"#,#")&amp;"_"&amp;TEXT(B110,"0,##")</f>
+        <f t="shared" si="57"/>
         <v>3,3_0,25</v>
       </c>
       <c r="E110" s="7">
@@ -5456,23 +9093,23 @@
         <v>2.9089999999999998</v>
       </c>
       <c r="I110" s="4">
-        <f t="shared" si="123"/>
+        <f t="shared" si="58"/>
         <v>1.2498487598306109</v>
       </c>
       <c r="J110" s="4">
-        <f t="shared" si="124"/>
+        <f t="shared" si="59"/>
         <v>19.799634000000001</v>
       </c>
       <c r="K110" s="4">
-        <f t="shared" si="125"/>
+        <f t="shared" si="60"/>
         <v>12.019987999999998</v>
       </c>
       <c r="L110" s="4">
-        <f t="shared" ref="L110" si="131">J110-K110</f>
+        <f t="shared" si="61"/>
         <v>7.7796460000000032</v>
       </c>
       <c r="M110" s="4">
-        <f t="shared" ref="M110" si="132">K110/J110</f>
+        <f t="shared" si="62"/>
         <v>0.60708132281637106</v>
       </c>
       <c r="N110" s="6">
@@ -5564,11 +9201,11 @@
         <v>3.2704776399999997</v>
       </c>
       <c r="L113" s="4">
-        <f t="shared" ref="L113:L116" si="133">J113-K113</f>
+        <f>J113-K113</f>
         <v>0.67689600800000038</v>
       </c>
       <c r="M113" s="4">
-        <f t="shared" ref="M113:M116" si="134">K113/J113</f>
+        <f>K113/J113</f>
         <v>0.82851990504041584</v>
       </c>
       <c r="N113" s="6">
@@ -5612,11 +9249,11 @@
         <v>6.1515471240000004</v>
       </c>
       <c r="L114" s="4">
-        <f t="shared" si="133"/>
+        <f>J114-K114</f>
         <v>1.3629584759999984</v>
       </c>
       <c r="M114" s="4">
-        <f t="shared" si="134"/>
+        <f>K114/J114</f>
         <v>0.81862300082656159</v>
       </c>
       <c r="N114" s="6">
@@ -5632,7 +9269,7 @@
         <v>2</v>
       </c>
       <c r="D115" s="4" t="str">
-        <f t="shared" ref="D115:D116" si="135">TEXT(ROUND(E115,3),"#")&amp;"_"&amp;TEXT(B115,"0,##")</f>
+        <f>TEXT(ROUND(E115,3),"#")&amp;"_"&amp;TEXT(B115,"0,##")</f>
         <v>5_0,25</v>
       </c>
       <c r="E115" s="7">
@@ -5660,11 +9297,11 @@
         <v>11.199571649999999</v>
       </c>
       <c r="L115" s="4">
-        <f t="shared" si="133"/>
+        <f>J115-K115</f>
         <v>2.9879379300000011</v>
       </c>
       <c r="M115" s="4">
-        <f t="shared" si="134"/>
+        <f>K115/J115</f>
         <v>0.78939658767088561</v>
       </c>
       <c r="N115" s="6">
@@ -5680,7 +9317,7 @@
         <v>2</v>
       </c>
       <c r="D116" s="4" t="str">
-        <f t="shared" si="135"/>
+        <f>TEXT(ROUND(E116,3),"#")&amp;"_"&amp;TEXT(B116,"0,##")</f>
         <v>5_0,25</v>
       </c>
       <c r="E116" s="7">
@@ -5708,11 +9345,11 @@
         <v>19.381598500000003</v>
       </c>
       <c r="L116" s="4">
-        <f t="shared" si="133"/>
+        <f>J116-K116</f>
         <v>6.6984877399999974</v>
       </c>
       <c r="M116" s="4">
-        <f t="shared" si="134"/>
+        <f>K116/J116</f>
         <v>0.74315699425386572</v>
       </c>
       <c r="N116" s="6">
@@ -5804,11 +9441,11 @@
         <v>11.467023279999999</v>
       </c>
       <c r="L119" s="4">
-        <f t="shared" ref="L119:L121" si="136">J119-K119</f>
+        <f>J119-K119</f>
         <v>1.5510689960000033</v>
       </c>
       <c r="M119" s="4">
-        <f t="shared" ref="M119:M121" si="137">K119/J119</f>
+        <f>K119/J119</f>
         <v>0.88085281905248625</v>
       </c>
       <c r="N119" s="6">
@@ -5852,11 +9489,11 @@
         <v>21.805305659999998</v>
       </c>
       <c r="L120" s="4">
-        <f t="shared" si="136"/>
+        <f>J120-K120</f>
         <v>3.1751191400000032</v>
       </c>
       <c r="M120" s="4">
-        <f t="shared" si="137"/>
+        <f>K120/J120</f>
         <v>0.87289571072466299</v>
       </c>
       <c r="N120" s="6">
@@ -5872,7 +9509,7 @@
         <v>2</v>
       </c>
       <c r="D121" s="4" t="str">
-        <f t="shared" ref="D121" si="138">TEXT(ROUND(E121,3),"#")&amp;"_"&amp;TEXT(B121,"0,##")</f>
+        <f>TEXT(ROUND(E121,3),"#")&amp;"_"&amp;TEXT(B121,"0,##")</f>
         <v>9_0,25</v>
       </c>
       <c r="E121" s="7">
@@ -5900,11 +9537,11 @@
         <v>45.935305023000005</v>
       </c>
       <c r="L121" s="4">
-        <f t="shared" si="136"/>
+        <f>J121-K121</f>
         <v>8.3988477870000011</v>
       </c>
       <c r="M121" s="4">
-        <f t="shared" si="137"/>
+        <f>K121/J121</f>
         <v>0.84542231078176999</v>
       </c>
       <c r="N121" s="6">
@@ -5929,7 +9566,7 @@
         <v>0.25</v>
       </c>
       <c r="C123" s="4">
-        <f t="shared" ref="C123:C126" si="139">1/(1-2*B123)</f>
+        <f>1/(1-2*B123)</f>
         <v>2</v>
       </c>
       <c r="D123" s="4" t="str">
@@ -5949,15 +9586,15 @@
         <v>0.46844000000000002</v>
       </c>
       <c r="I123" s="4">
-        <f t="shared" ref="I123:I126" si="140">G123/E123</f>
+        <f>G123/E123</f>
         <v>1.9520177206335461</v>
       </c>
       <c r="J123" s="4">
-        <f t="shared" ref="J123:J126" si="141">F123*E123</f>
+        <f>F123*E123</f>
         <v>12.333312543999998</v>
       </c>
       <c r="K123" s="4">
-        <f t="shared" ref="K123:K126" si="142">H123*G123</f>
+        <f>H123*G123</f>
         <v>10.980702040000001</v>
       </c>
       <c r="L123" s="4">
@@ -5977,11 +9614,11 @@
         <v>0.25</v>
       </c>
       <c r="C124" s="4">
-        <f t="shared" si="139"/>
+        <f>1/(1-2*B124)</f>
         <v>2</v>
       </c>
       <c r="D124" s="4" t="str">
-        <f t="shared" ref="D124:D126" si="143">TEXT(ROUND(E124,3),"#")&amp;"_"&amp;TEXT(B124,"0,##")</f>
+        <f>TEXT(ROUND(E124,3),"#")&amp;"_"&amp;TEXT(B124,"0,##")</f>
         <v>12_0,25</v>
       </c>
       <c r="E124" s="7">
@@ -5997,23 +9634,23 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="I124" s="4">
-        <f t="shared" si="140"/>
+        <f>G124/E124</f>
         <v>1.9199014581530063</v>
       </c>
       <c r="J124" s="4">
-        <f t="shared" si="141"/>
+        <f>F124*E124</f>
         <v>23.65552576</v>
       </c>
       <c r="K124" s="4">
-        <f t="shared" si="142"/>
+        <f>H124*G124</f>
         <v>21.25093364</v>
       </c>
       <c r="L124" s="4">
-        <f t="shared" ref="L124:L126" si="144">J124-K124</f>
+        <f>J124-K124</f>
         <v>2.4045921200000002</v>
       </c>
       <c r="M124" s="4">
-        <f t="shared" ref="M124:M126" si="145">K124/J124</f>
+        <f>K124/J124</f>
         <v>0.89834966491989732</v>
       </c>
       <c r="N124" s="6">
@@ -6025,11 +9662,11 @@
         <v>0.25</v>
       </c>
       <c r="C125" s="4">
-        <f t="shared" si="139"/>
+        <f>1/(1-2*B125)</f>
         <v>2</v>
       </c>
       <c r="D125" s="4" t="str">
-        <f t="shared" si="143"/>
+        <f>TEXT(ROUND(E125,3),"#")&amp;"_"&amp;TEXT(B125,"0,##")</f>
         <v>12_0,25</v>
       </c>
       <c r="E125" s="7">
@@ -6045,23 +9682,23 @@
         <v>1.7985</v>
       </c>
       <c r="I125" s="4">
-        <f t="shared" si="140"/>
+        <f>G125/E125</f>
         <v>1.8754463173627833</v>
       </c>
       <c r="J125" s="4">
-        <f t="shared" si="141"/>
+        <f>F125*E125</f>
         <v>45.691141999999999</v>
       </c>
       <c r="K125" s="4">
-        <f t="shared" si="142"/>
+        <f>H125*G125</f>
         <v>40.620920999999996</v>
       </c>
       <c r="L125" s="4">
-        <f t="shared" si="144"/>
+        <f>J125-K125</f>
         <v>5.0702210000000036</v>
       </c>
       <c r="M125" s="4">
-        <f t="shared" si="145"/>
+        <f>K125/J125</f>
         <v>0.88903273636714963</v>
       </c>
       <c r="N125" s="6">
@@ -6073,11 +9710,11 @@
         <v>0.25</v>
       </c>
       <c r="C126" s="4">
-        <f t="shared" si="139"/>
+        <f>1/(1-2*B126)</f>
         <v>2</v>
       </c>
       <c r="D126" s="4" t="str">
-        <f t="shared" si="143"/>
+        <f>TEXT(ROUND(E126,3),"#")&amp;"_"&amp;TEXT(B126,"0,##")</f>
         <v>12_0,25</v>
       </c>
       <c r="E126" s="7">
@@ -6093,23 +9730,23 @@
         <v>2.9192999999999998</v>
       </c>
       <c r="I126" s="4">
-        <f t="shared" si="140"/>
+        <f>G126/E126</f>
         <v>1.8343431653239231</v>
       </c>
       <c r="J126" s="4">
-        <f t="shared" si="141"/>
+        <f>F126*E126</f>
         <v>73.63635472</v>
       </c>
       <c r="K126" s="4">
-        <f t="shared" si="142"/>
+        <f>H126*G126</f>
         <v>64.341371999999993</v>
       </c>
       <c r="L126" s="4">
-        <f t="shared" si="144"/>
+        <f>J126-K126</f>
         <v>9.2949827200000072</v>
       </c>
       <c r="M126" s="4">
-        <f t="shared" si="145"/>
+        <f>K126/J126</f>
         <v>0.87377182432042033</v>
       </c>
       <c r="N126" s="6">
@@ -6121,7 +9758,7 @@
         <v>0.25</v>
       </c>
       <c r="C128" s="4">
-        <f t="shared" ref="C128:C131" si="146">1/(1-2*B128)</f>
+        <f>1/(1-2*B128)</f>
         <v>2</v>
       </c>
       <c r="D128" s="4" t="str">
@@ -6141,15 +9778,15 @@
         <v>0.96228000000000002</v>
       </c>
       <c r="I128" s="4">
-        <f t="shared" ref="I128:I131" si="147">G128/E128</f>
+        <f>G128/E128</f>
         <v>2.0040578261050701</v>
       </c>
       <c r="J128" s="4">
-        <f t="shared" ref="J128:J131" si="148">F128*E128</f>
+        <f>F128*E128</f>
         <v>50.478549029999996</v>
       </c>
       <c r="K128" s="4">
-        <f t="shared" ref="K128:K131" si="149">H128*G128</f>
+        <f>H128*G128</f>
         <v>46.288939752000005</v>
       </c>
       <c r="L128" s="4">
@@ -6169,11 +9806,11 @@
         <v>0.25</v>
       </c>
       <c r="C129" s="4">
-        <f t="shared" si="146"/>
+        <f>1/(1-2*B129)</f>
         <v>2</v>
       </c>
       <c r="D129" s="4" t="str">
-        <f t="shared" ref="D129:D131" si="150">TEXT(ROUND(E129,3),"#")&amp;"_"&amp;TEXT(B129,"0,##")</f>
+        <f>TEXT(ROUND(E129,3),"#")&amp;"_"&amp;TEXT(B129,"0,##")</f>
         <v>24_0,25</v>
       </c>
       <c r="E129" s="7">
@@ -6189,23 +9826,23 @@
         <v>1.5956999999999999</v>
       </c>
       <c r="I129" s="4">
-        <f t="shared" si="147"/>
+        <f>G129/E129</f>
         <v>1.9869187073289312</v>
       </c>
       <c r="J129" s="4">
-        <f t="shared" si="148"/>
+        <f>F129*E129</f>
         <v>82.609988720000004</v>
       </c>
       <c r="K129" s="4">
-        <f t="shared" si="149"/>
+        <f>H129*G129</f>
         <v>76.298395499999998</v>
       </c>
       <c r="L129" s="4">
-        <f t="shared" ref="L129:L131" si="151">J129-K129</f>
+        <f>J129-K129</f>
         <v>6.311593220000006</v>
       </c>
       <c r="M129" s="4">
-        <f t="shared" ref="M129:M131" si="152">K129/J129</f>
+        <f>K129/J129</f>
         <v>0.92359769904590294</v>
       </c>
       <c r="N129" s="6">
@@ -6217,11 +9854,11 @@
         <v>0.25</v>
       </c>
       <c r="C130" s="4">
-        <f t="shared" si="146"/>
+        <f>1/(1-2*B130)</f>
         <v>2</v>
       </c>
       <c r="D130" s="4" t="str">
-        <f t="shared" si="150"/>
+        <f>TEXT(ROUND(E130,3),"#")&amp;"_"&amp;TEXT(B130,"0,##")</f>
         <v>24_0,25</v>
       </c>
       <c r="E130" s="7">
@@ -6237,23 +9874,23 @@
         <v>2.3765000000000001</v>
       </c>
       <c r="I130" s="4">
-        <f t="shared" si="147"/>
+        <f>G130/E130</f>
         <v>1.9720660393455995</v>
       </c>
       <c r="J130" s="4">
-        <f t="shared" si="148"/>
+        <f>F130*E130</f>
         <v>121.89935691999999</v>
       </c>
       <c r="K130" s="4">
-        <f t="shared" si="149"/>
+        <f>H130*G130</f>
         <v>112.61045249999999</v>
       </c>
       <c r="L130" s="4">
-        <f t="shared" si="151"/>
+        <f>J130-K130</f>
         <v>9.2889044199999944</v>
       </c>
       <c r="M130" s="4">
-        <f t="shared" si="152"/>
+        <f>K130/J130</f>
         <v>0.92379857732886883</v>
       </c>
       <c r="N130" s="6">
@@ -6265,11 +9902,11 @@
         <v>0.25</v>
       </c>
       <c r="C131" s="4">
-        <f t="shared" si="146"/>
+        <f>1/(1-2*B131)</f>
         <v>2</v>
       </c>
       <c r="D131" s="4" t="str">
-        <f t="shared" si="150"/>
+        <f>TEXT(ROUND(E131,3),"#")&amp;"_"&amp;TEXT(B131,"0,##")</f>
         <v>24_0,25</v>
       </c>
       <c r="E131" s="7">
@@ -6285,23 +9922,23 @@
         <v>2.8490000000000002</v>
       </c>
       <c r="I131" s="4">
-        <f t="shared" si="147"/>
+        <f>G131/E131</f>
         <v>1.9631033190355223</v>
       </c>
       <c r="J131" s="4">
-        <f t="shared" si="148"/>
+        <f>F131*E131</f>
         <v>145.64124630000001</v>
       </c>
       <c r="K131" s="4">
-        <f t="shared" si="149"/>
+        <f>H131*G131</f>
         <v>134.30186</v>
       </c>
       <c r="L131" s="4">
-        <f t="shared" si="151"/>
+        <f>J131-K131</f>
         <v>11.339386300000001</v>
       </c>
       <c r="M131" s="4">
-        <f t="shared" si="152"/>
+        <f>K131/J131</f>
         <v>0.92214165569111861</v>
       </c>
       <c r="N131" s="6">
@@ -6310,15 +9947,15 @@
     </row>
     <row r="133" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B133" s="7">
-        <f>1/3</f>
+        <f t="shared" ref="B133:B138" si="63">1/3</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C133" s="4">
-        <f t="shared" ref="C133:C138" si="153">1/(1-2*B133)</f>
+        <f t="shared" ref="C133:C138" si="64">1/(1-2*B133)</f>
         <v>2.9999999999999996</v>
       </c>
       <c r="D133" s="4" t="str">
-        <f>TEXT(ROUND(E133,3),"#,#")&amp;"_"&amp;TEXT(B133,"0,##")</f>
+        <f t="shared" ref="D133:D138" si="65">TEXT(ROUND(E133,3),"#,#")&amp;"_"&amp;TEXT(B133,"0,##")</f>
         <v>3,3_0,33</v>
       </c>
       <c r="E133" s="7">
@@ -6334,23 +9971,23 @@
         <v>0.11681999999999999</v>
       </c>
       <c r="I133" s="4">
-        <f t="shared" ref="I133:I138" si="154">G133/E133</f>
+        <f t="shared" ref="I133:I138" si="66">G133/E133</f>
         <v>2.6593197278911562</v>
       </c>
       <c r="J133" s="4">
-        <f t="shared" ref="J133:J138" si="155">F133*E133</f>
+        <f t="shared" ref="J133:J138" si="67">F133*E133</f>
         <v>1.3765815000000001</v>
       </c>
       <c r="K133" s="4">
-        <f t="shared" ref="K133:K138" si="156">H133*G133</f>
+        <f t="shared" ref="K133:K138" si="68">H133*G133</f>
         <v>1.0275136739999999</v>
       </c>
       <c r="L133" s="4">
-        <f>J133-K133</f>
+        <f t="shared" ref="L133:L138" si="69">J133-K133</f>
         <v>0.34906782600000019</v>
       </c>
       <c r="M133" s="4">
-        <f>K133/J133</f>
+        <f t="shared" ref="M133:M138" si="70">K133/J133</f>
         <v>0.74642414851572525</v>
       </c>
       <c r="N133" s="6">
@@ -6359,15 +9996,15 @@
     </row>
     <row r="134" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B134" s="7">
-        <f>1/3</f>
+        <f t="shared" si="63"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="C134" s="4">
-        <f t="shared" si="153"/>
+        <f t="shared" si="64"/>
         <v>2.9999999999999996</v>
       </c>
       <c r="D134" s="4" t="str">
-        <f>TEXT(ROUND(E134,3),"#,#")&amp;"_"&amp;TEXT(B134,"0,##")</f>
+        <f t="shared" si="65"/>
         <v>3,3_0,33</v>
       </c>
       <c r="E134" s="7">
@@ -6383,23 +10020,23 @@
         <v>0.1527</v>
       </c>
       <c r="I134" s="4">
-        <f t="shared" si="154"/>
+        <f t="shared" si="66"/>
         <v>2.6036901263368373</v>
       </c>
       <c r="J134" s="4">
-        <f t="shared" si="155"/>
+        <f t="shared" si="67"/>
         <v>1.7388087600000002</v>
       </c>
       <c r="K134" s="4">
-        <f t="shared" si="156"/>
+        <f t="shared" si="68"/>
         <v>1.3123038</v>
       </c>
       <c r="L134" s="4">
-        <f>J134-K134</f>
+        <f t="shared" si="69"/>
         <v>0.42650496000000016</v>
       </c>
       <c r="M134" s="4">
-        <f>K134/J134</f>
+        <f t="shared" si="70"/>
         <v>0.75471427921722678</v>
       </c>
       <c r="N134" s="6">
@@ -6408,15 +10045,15 @@
     </row>
     <row r="135" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B135" s="7">
-        <f t="shared" ref="B135:B136" si="157">1/3</f>
+        <f t="shared" si="63"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="C135" s="4">
-        <f t="shared" si="153"/>
+        <f t="shared" si="64"/>
         <v>2.9999999999999996</v>
       </c>
       <c r="D135" s="4" t="str">
-        <f t="shared" ref="D135:D137" si="158">TEXT(ROUND(E135,3),"#,#")&amp;"_"&amp;TEXT(B135,"0,##")</f>
+        <f t="shared" si="65"/>
         <v>3,3_0,33</v>
       </c>
       <c r="E135" s="7">
@@ -6432,23 +10069,23 @@
         <v>0.29487999999999998</v>
       </c>
       <c r="I135" s="4">
-        <f t="shared" si="154"/>
+        <f t="shared" si="66"/>
         <v>2.5124269669724217</v>
       </c>
       <c r="J135" s="4">
-        <f t="shared" si="155"/>
+        <f t="shared" si="67"/>
         <v>3.21675354</v>
       </c>
       <c r="K135" s="4">
-        <f t="shared" si="156"/>
+        <f t="shared" si="68"/>
         <v>2.4472975839999997</v>
       </c>
       <c r="L135" s="4">
-        <f t="shared" ref="L135:L138" si="159">J135-K135</f>
+        <f t="shared" si="69"/>
         <v>0.76945595600000027</v>
       </c>
       <c r="M135" s="4">
-        <f t="shared" ref="M135:M138" si="160">K135/J135</f>
+        <f t="shared" si="70"/>
         <v>0.7607973547143434</v>
       </c>
       <c r="N135" s="6">
@@ -6457,15 +10094,15 @@
     </row>
     <row r="136" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B136" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="63"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="C136" s="4">
-        <f t="shared" si="153"/>
+        <f t="shared" si="64"/>
         <v>2.9999999999999996</v>
       </c>
       <c r="D136" s="4" t="str">
-        <f t="shared" si="158"/>
+        <f t="shared" si="65"/>
         <v>3,3_0,33</v>
       </c>
       <c r="E136" s="7">
@@ -6481,23 +10118,23 @@
         <v>0.56259000000000003</v>
       </c>
       <c r="I136" s="4">
-        <f t="shared" si="154"/>
+        <f t="shared" si="66"/>
         <v>2.3956442831215972</v>
       </c>
       <c r="J136" s="4">
-        <f t="shared" si="155"/>
+        <f t="shared" si="67"/>
         <v>6.0020429999999996</v>
       </c>
       <c r="K136" s="4">
-        <f t="shared" si="156"/>
+        <f t="shared" si="68"/>
         <v>4.4557128000000006</v>
       </c>
       <c r="L136" s="4">
-        <f t="shared" si="159"/>
+        <f t="shared" si="69"/>
         <v>1.546330199999999</v>
       </c>
       <c r="M136" s="4">
-        <f t="shared" si="160"/>
+        <f t="shared" si="70"/>
         <v>0.74236602436870258</v>
       </c>
       <c r="N136" s="6">
@@ -6506,15 +10143,15 @@
     </row>
     <row r="137" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B137" s="7">
-        <f>1/3</f>
+        <f t="shared" si="63"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="C137" s="4">
-        <f t="shared" si="153"/>
+        <f t="shared" si="64"/>
         <v>2.9999999999999996</v>
       </c>
       <c r="D137" s="4" t="str">
-        <f t="shared" si="158"/>
+        <f t="shared" si="65"/>
         <v>3,3_0,33</v>
       </c>
       <c r="E137" s="7">
@@ -6530,23 +10167,23 @@
         <v>1.03695</v>
       </c>
       <c r="I137" s="4">
-        <f t="shared" si="154"/>
+        <f t="shared" si="66"/>
         <v>2.2206071617836325</v>
       </c>
       <c r="J137" s="4">
-        <f t="shared" si="155"/>
+        <f t="shared" si="67"/>
         <v>10.928796374999999</v>
       </c>
       <c r="K137" s="4">
-        <f t="shared" si="156"/>
+        <f t="shared" si="68"/>
         <v>7.6039543500000004</v>
       </c>
       <c r="L137" s="4">
-        <f t="shared" si="159"/>
+        <f t="shared" si="69"/>
         <v>3.3248420249999988</v>
       </c>
       <c r="M137" s="4">
-        <f t="shared" si="160"/>
+        <f t="shared" si="70"/>
         <v>0.69577235123479009</v>
       </c>
       <c r="N137" s="6">
@@ -6555,15 +10192,15 @@
     </row>
     <row r="138" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B138" s="7">
-        <f>1/3</f>
+        <f t="shared" si="63"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="C138" s="4">
-        <f t="shared" si="153"/>
+        <f t="shared" si="64"/>
         <v>2.9999999999999996</v>
       </c>
       <c r="D138" s="4" t="str">
-        <f>TEXT(ROUND(E138,3),"#,#")&amp;"_"&amp;TEXT(B138,"0,##")</f>
+        <f t="shared" si="65"/>
         <v>3,3_0,33</v>
       </c>
       <c r="E138" s="7">
@@ -6579,23 +10216,23 @@
         <v>1.8996999999999999</v>
       </c>
       <c r="I138" s="4">
-        <f t="shared" si="154"/>
+        <f t="shared" si="66"/>
         <v>1.9454545454545455</v>
       </c>
       <c r="J138" s="4">
-        <f t="shared" si="155"/>
+        <f t="shared" si="67"/>
         <v>19.8429</v>
       </c>
       <c r="K138" s="4">
-        <f t="shared" si="156"/>
+        <f t="shared" si="68"/>
         <v>12.196073999999999</v>
       </c>
       <c r="L138" s="4">
-        <f t="shared" si="159"/>
+        <f t="shared" si="69"/>
         <v>7.6468260000000008</v>
       </c>
       <c r="M138" s="4">
-        <f t="shared" si="160"/>
+        <f t="shared" si="70"/>
         <v>0.61463163146515876</v>
       </c>
       <c r="N138" s="6">
@@ -6702,7 +10339,7 @@
     </row>
     <row r="142" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B142" s="7">
-        <f t="shared" ref="B142:B143" si="161">1/3</f>
+        <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C142" s="4">
@@ -6738,11 +10375,11 @@
         <v>7.3757852999999995</v>
       </c>
       <c r="L142" s="4">
-        <f t="shared" ref="L142:L144" si="162">J142-K142</f>
+        <f>J142-K142</f>
         <v>1.7161622999999997</v>
       </c>
       <c r="M142" s="4">
-        <f t="shared" ref="M142:M144" si="163">K142/J142</f>
+        <f>K142/J142</f>
         <v>0.81124370976357152</v>
       </c>
       <c r="N142" s="6">
@@ -6751,7 +10388,7 @@
     </row>
     <row r="143" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B143" s="7">
-        <f t="shared" si="161"/>
+        <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C143" s="4">
@@ -6787,11 +10424,11 @@
         <v>13.377925999999999</v>
       </c>
       <c r="L143" s="4">
-        <f t="shared" si="162"/>
+        <f>J143-K143</f>
         <v>3.6344395620000007</v>
       </c>
       <c r="M143" s="4">
-        <f t="shared" si="163"/>
+        <f>K143/J143</f>
         <v>0.78636483275917035</v>
       </c>
       <c r="N143" s="6">
@@ -6808,7 +10445,7 @@
         <v>2.9999999999999996</v>
       </c>
       <c r="D144" s="4" t="str">
-        <f t="shared" ref="D144" si="164">TEXT(ROUND(E144,3),"#")&amp;"_"&amp;TEXT(B144,"0,##")</f>
+        <f>TEXT(ROUND(E144,3),"#")&amp;"_"&amp;TEXT(B144,"0,##")</f>
         <v>5_0,33</v>
       </c>
       <c r="E144" s="7">
@@ -6836,11 +10473,11 @@
         <v>22.575936000000002</v>
       </c>
       <c r="L144" s="4">
-        <f t="shared" si="162"/>
+        <f>J144-K144</f>
         <v>7.9522414999999995</v>
       </c>
       <c r="M144" s="4">
-        <f t="shared" si="163"/>
+        <f>K144/J144</f>
         <v>0.7395114235037451</v>
       </c>
       <c r="N144" s="6">
@@ -6912,7 +10549,7 @@
     </row>
     <row r="147" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B147" s="7">
-        <f t="shared" ref="B147:B148" si="165">1/3</f>
+        <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C147" s="4">
@@ -6948,11 +10585,11 @@
         <v>13.100953599999999</v>
       </c>
       <c r="L147" s="4">
-        <f t="shared" ref="L147:L149" si="166">J147-K147</f>
+        <f>J147-K147</f>
         <v>2.2288439600000043</v>
       </c>
       <c r="M147" s="4">
-        <f t="shared" ref="M147:M149" si="167">K147/J147</f>
+        <f>K147/J147</f>
         <v>0.85460708458305279</v>
       </c>
       <c r="N147" s="6">
@@ -6961,7 +10598,7 @@
     </row>
     <row r="148" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B148" s="7">
-        <f t="shared" si="165"/>
+        <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C148" s="4">
@@ -6997,11 +10634,11 @@
         <v>24.99045272</v>
       </c>
       <c r="L148" s="4">
-        <f t="shared" si="166"/>
+        <f>J148-K148</f>
         <v>4.1353442399999985</v>
       </c>
       <c r="M148" s="4">
-        <f t="shared" si="167"/>
+        <f>K148/J148</f>
         <v>0.85801781679384481</v>
       </c>
       <c r="N148" s="6">
@@ -7018,7 +10655,7 @@
         <v>2.9999999999999996</v>
       </c>
       <c r="D149" s="4" t="str">
-        <f t="shared" ref="D149" si="168">TEXT(ROUND(E149,3),"#")&amp;"_"&amp;TEXT(B149,"0,##")</f>
+        <f>TEXT(ROUND(E149,3),"#")&amp;"_"&amp;TEXT(B149,"0,##")</f>
         <v>9_0,33</v>
       </c>
       <c r="E149" s="7">
@@ -7046,11 +10683,11 @@
         <v>46.109859999999998</v>
       </c>
       <c r="L149" s="4">
-        <f t="shared" si="166"/>
+        <f>J149-K149</f>
         <v>8.9595395400000015</v>
       </c>
       <c r="M149" s="4">
-        <f t="shared" si="167"/>
+        <f>K149/J149</f>
         <v>0.83730457177961082</v>
       </c>
       <c r="N149" s="6">
@@ -7073,15 +10710,15 @@
     </row>
     <row r="151" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B151" s="7">
-        <f t="shared" ref="B151:B152" si="169">1/3</f>
+        <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C151" s="4">
-        <f t="shared" ref="C151:C153" si="170">1/(1-2*B151)</f>
+        <f>1/(1-2*B151)</f>
         <v>2.9999999999999996</v>
       </c>
       <c r="D151" s="4" t="str">
-        <f t="shared" ref="D151:D153" si="171">TEXT(ROUND(E151,3),"#")&amp;"_"&amp;TEXT(B151,"0,##")</f>
+        <f>TEXT(ROUND(E151,3),"#")&amp;"_"&amp;TEXT(B151,"0,##")</f>
         <v>12_0,33</v>
       </c>
       <c r="E151" s="7">
@@ -7097,23 +10734,23 @@
         <v>0.49064000000000002</v>
       </c>
       <c r="I151" s="4">
-        <f t="shared" ref="I151:I153" si="172">G151/E151</f>
+        <f>G151/E151</f>
         <v>2.9840912876894885</v>
       </c>
       <c r="J151" s="4">
-        <f t="shared" ref="J151:J153" si="173">F151*E151</f>
+        <f>F151*E151</f>
         <v>20.438053920000002</v>
       </c>
       <c r="K151" s="4">
-        <f t="shared" ref="K151:K153" si="174">H151*G151</f>
+        <f>H151*G151</f>
         <v>17.578159280000001</v>
       </c>
       <c r="L151" s="4">
-        <f t="shared" ref="L151:L153" si="175">J151-K151</f>
+        <f>J151-K151</f>
         <v>2.8598946400000003</v>
       </c>
       <c r="M151" s="4">
-        <f t="shared" ref="M151:M153" si="176">K151/J151</f>
+        <f>K151/J151</f>
         <v>0.86007010984537025</v>
       </c>
       <c r="N151" s="6">
@@ -7122,15 +10759,15 @@
     </row>
     <row r="152" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B152" s="7">
-        <f t="shared" si="169"/>
+        <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C152" s="4">
-        <f t="shared" si="170"/>
+        <f>1/(1-2*B152)</f>
         <v>2.9999999999999996</v>
       </c>
       <c r="D152" s="4" t="str">
-        <f t="shared" si="171"/>
+        <f>TEXT(ROUND(E152,3),"#")&amp;"_"&amp;TEXT(B152,"0,##")</f>
         <v>12_0,33</v>
       </c>
       <c r="E152" s="7">
@@ -7146,23 +10783,23 @@
         <v>0.92720000000000002</v>
       </c>
       <c r="I152" s="4">
-        <f t="shared" si="172"/>
+        <f>G152/E152</f>
         <v>2.9343703210780236</v>
       </c>
       <c r="J152" s="4">
-        <f t="shared" si="173"/>
+        <f>F152*E152</f>
         <v>37.425688200000003</v>
       </c>
       <c r="K152" s="4">
-        <f t="shared" si="174"/>
+        <f>H152*G152</f>
         <v>32.708834400000001</v>
       </c>
       <c r="L152" s="4">
-        <f t="shared" si="175"/>
+        <f>J152-K152</f>
         <v>4.7168538000000026</v>
       </c>
       <c r="M152" s="4">
-        <f t="shared" si="176"/>
+        <f>K152/J152</f>
         <v>0.87396747990862589</v>
       </c>
       <c r="N152" s="6">
@@ -7175,11 +10812,11 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C153" s="4">
-        <f t="shared" si="170"/>
+        <f>1/(1-2*B153)</f>
         <v>2.9999999999999996</v>
       </c>
       <c r="D153" s="4" t="str">
-        <f t="shared" si="171"/>
+        <f>TEXT(ROUND(E153,3),"#")&amp;"_"&amp;TEXT(B153,"0,##")</f>
         <v>12_0,33</v>
       </c>
       <c r="E153" s="7">
@@ -7195,23 +10832,23 @@
         <v>1.8446</v>
       </c>
       <c r="I153" s="4">
-        <f t="shared" si="172"/>
+        <f>G153/E153</f>
         <v>2.8411603357991857</v>
       </c>
       <c r="J153" s="4">
-        <f t="shared" si="173"/>
+        <f>F153*E153</f>
         <v>72.775519000000003</v>
       </c>
       <c r="K153" s="4">
-        <f t="shared" si="174"/>
+        <f>H153*G153</f>
         <v>63.052117200000005</v>
       </c>
       <c r="L153" s="4">
-        <f t="shared" si="175"/>
+        <f>J153-K153</f>
         <v>9.7234017999999978</v>
       </c>
       <c r="M153" s="4">
-        <f t="shared" si="176"/>
+        <f>K153/J153</f>
         <v>0.86639185905359195</v>
       </c>
       <c r="N153" s="6">
@@ -7224,7 +10861,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C155" s="4">
-        <f t="shared" ref="C155:C156" si="177">1/(1-2*B155)</f>
+        <f>1/(1-2*B155)</f>
         <v>2.9999999999999996</v>
       </c>
       <c r="D155" s="4" t="str">
@@ -7244,15 +10881,15 @@
         <v>1.0148699999999999</v>
       </c>
       <c r="I155" s="4">
-        <f t="shared" ref="I155:I156" si="178">G155/E155</f>
+        <f>G155/E155</f>
         <v>3.0822128793239809</v>
       </c>
       <c r="J155" s="4">
-        <f t="shared" ref="J155:J156" si="179">F155*E155</f>
+        <f>F155*E155</f>
         <v>84.930914200000004</v>
       </c>
       <c r="K155" s="4">
-        <f t="shared" ref="K155:K156" si="180">H155*G155</f>
+        <f>H155*G155</f>
         <v>75.14503427999999</v>
       </c>
       <c r="L155" s="4">
@@ -7273,11 +10910,11 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C156" s="4">
-        <f t="shared" si="177"/>
+        <f>1/(1-2*B156)</f>
         <v>2.9999999999999996</v>
       </c>
       <c r="D156" s="4" t="str">
-        <f t="shared" ref="D156" si="181">TEXT(ROUND(E156,3),"#")&amp;"_"&amp;TEXT(B156,"0,##")</f>
+        <f>TEXT(ROUND(E156,3),"#")&amp;"_"&amp;TEXT(B156,"0,##")</f>
         <v>24_0,33</v>
       </c>
       <c r="E156" s="7">
@@ -7293,23 +10930,23 @@
         <v>1.78</v>
       </c>
       <c r="I156" s="4">
-        <f t="shared" si="178"/>
+        <f>G156/E156</f>
         <v>3.0341150497771481</v>
       </c>
       <c r="J156" s="4">
-        <f t="shared" si="179"/>
+        <f>F156*E156</f>
         <v>144.54614700000002</v>
       </c>
       <c r="K156" s="4">
-        <f t="shared" si="180"/>
+        <f>H156*G156</f>
         <v>129.65520000000001</v>
       </c>
       <c r="L156" s="4">
-        <f t="shared" ref="L156" si="182">J156-K156</f>
+        <f>J156-K156</f>
         <v>14.890947000000011</v>
       </c>
       <c r="M156" s="4">
-        <f t="shared" ref="M156" si="183">K156/J156</f>
+        <f>K156/J156</f>
         <v>0.89698136332890277</v>
       </c>
       <c r="N156" s="6">
@@ -7381,7 +11018,7 @@
     </row>
     <row r="159" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B159" s="7">
-        <f t="shared" ref="B159:B179" si="184">3/8</f>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C159" s="4">
@@ -7389,7 +11026,7 @@
         <v>4</v>
       </c>
       <c r="D159" s="4" t="str">
-        <f t="shared" ref="D159:D161" si="185">TEXT(ROUND(E159,3),"#,#")&amp;"_"&amp;TEXT(B159,"0,###")</f>
+        <f>TEXT(ROUND(E159,3),"#,#")&amp;"_"&amp;TEXT(B159,"0,###")</f>
         <v>3,3_0,375</v>
       </c>
       <c r="E159" s="7">
@@ -7417,11 +11054,11 @@
         <v>2.568768961</v>
       </c>
       <c r="L159" s="4">
-        <f t="shared" ref="L159:L161" si="186">J159-K159</f>
+        <f>J159-K159</f>
         <v>0.89364527900000024</v>
       </c>
       <c r="M159" s="4">
-        <f t="shared" ref="M159:M161" si="187">K159/J159</f>
+        <f>K159/J159</f>
         <v>0.7419011079968294</v>
       </c>
       <c r="N159" s="6">
@@ -7430,7 +11067,7 @@
     </row>
     <row r="160" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B160" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C160" s="4">
@@ -7438,7 +11075,7 @@
         <v>4</v>
       </c>
       <c r="D160" s="4" t="str">
-        <f t="shared" si="185"/>
+        <f>TEXT(ROUND(E160,3),"#,#")&amp;"_"&amp;TEXT(B160,"0,###")</f>
         <v>3,3_0,375</v>
       </c>
       <c r="E160" s="7">
@@ -7466,11 +11103,11 @@
         <v>4.6078275600000005</v>
       </c>
       <c r="L160" s="4">
-        <f t="shared" si="186"/>
+        <f>J160-K160</f>
         <v>1.7078203199999988</v>
       </c>
       <c r="M160" s="4">
-        <f t="shared" si="187"/>
+        <f>K160/J160</f>
         <v>0.72958905365699411</v>
       </c>
       <c r="N160" s="6">
@@ -7479,7 +11116,7 @@
     </row>
     <row r="161" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B161" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C161" s="4">
@@ -7487,7 +11124,7 @@
         <v>4</v>
       </c>
       <c r="D161" s="4" t="str">
-        <f t="shared" si="185"/>
+        <f>TEXT(ROUND(E161,3),"#,#")&amp;"_"&amp;TEXT(B161,"0,###")</f>
         <v>3,3_0,375</v>
       </c>
       <c r="E161" s="7">
@@ -7515,11 +11152,11 @@
         <v>7.8536175000000004</v>
       </c>
       <c r="L161" s="4">
-        <f t="shared" si="186"/>
+        <f>J161-K161</f>
         <v>3.5710352999999984</v>
       </c>
       <c r="M161" s="4">
-        <f t="shared" si="187"/>
+        <f>K161/J161</f>
         <v>0.68742723630078295</v>
       </c>
       <c r="N161" s="6">
@@ -7528,7 +11165,7 @@
     </row>
     <row r="162" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B162" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C162" s="4">
@@ -7564,7 +11201,7 @@
         <v>12.695278199999999</v>
       </c>
       <c r="L162" s="4">
-        <f t="shared" ref="L162" si="188">J162-K162</f>
+        <f>J162-K162</f>
         <v>7.5332558400000007</v>
       </c>
       <c r="M162" s="4">
@@ -7577,7 +11214,7 @@
     </row>
     <row r="164" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B164" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C164" s="4">
@@ -7626,7 +11263,7 @@
     </row>
     <row r="165" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B165" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C165" s="4">
@@ -7634,7 +11271,7 @@
         <v>4</v>
       </c>
       <c r="D165" s="4" t="str">
-        <f t="shared" ref="D165:D167" si="189">TEXT(ROUND(E165,3),"#")&amp;"_"&amp;TEXT(B165,"0,###")</f>
+        <f>TEXT(ROUND(E165,3),"#")&amp;"_"&amp;TEXT(B165,"0,###")</f>
         <v>5_0,375</v>
       </c>
       <c r="E165" s="7">
@@ -7662,11 +11299,11 @@
         <v>6.6860886199999996</v>
       </c>
       <c r="L165" s="4">
-        <f t="shared" ref="L165:L167" si="190">J165-K165</f>
+        <f>J165-K165</f>
         <v>1.778137430000001</v>
       </c>
       <c r="M165" s="4">
-        <f t="shared" ref="M165:M167" si="191">K165/J165</f>
+        <f>K165/J165</f>
         <v>0.7899232109945834</v>
       </c>
       <c r="N165" s="6">
@@ -7675,7 +11312,7 @@
     </row>
     <row r="166" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B166" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C166" s="4">
@@ -7683,7 +11320,7 @@
         <v>4</v>
       </c>
       <c r="D166" s="4" t="str">
-        <f t="shared" si="189"/>
+        <f>TEXT(ROUND(E166,3),"#")&amp;"_"&amp;TEXT(B166,"0,###")</f>
         <v>5_0,375</v>
       </c>
       <c r="E166" s="7">
@@ -7711,11 +11348,11 @@
         <v>12.173105</v>
       </c>
       <c r="L166" s="4">
-        <f t="shared" si="190"/>
+        <f>J166-K166</f>
         <v>3.4560340499999995</v>
       </c>
       <c r="M166" s="4">
-        <f t="shared" si="191"/>
+        <f>K166/J166</f>
         <v>0.77887239732504654</v>
       </c>
       <c r="N166" s="6">
@@ -7724,7 +11361,7 @@
     </row>
     <row r="167" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B167" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C167" s="4">
@@ -7732,7 +11369,7 @@
         <v>4</v>
       </c>
       <c r="D167" s="4" t="str">
-        <f t="shared" si="189"/>
+        <f>TEXT(ROUND(E167,3),"#")&amp;"_"&amp;TEXT(B167,"0,###")</f>
         <v>5_0,375</v>
       </c>
       <c r="E167" s="7">
@@ -7760,11 +11397,11 @@
         <v>22.290879999999998</v>
       </c>
       <c r="L167" s="4">
-        <f t="shared" si="190"/>
+        <f>J167-K167</f>
         <v>7.7511104000000017</v>
       </c>
       <c r="M167" s="4">
-        <f t="shared" si="191"/>
+        <f>K167/J167</f>
         <v>0.74199078367324156</v>
       </c>
       <c r="N167" s="6">
@@ -7773,7 +11410,7 @@
     </row>
     <row r="169" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B169" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C169" s="4">
@@ -7822,7 +11459,7 @@
     </row>
     <row r="170" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B170" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C170" s="4">
@@ -7850,19 +11487,19 @@
         <v>3.8607679317394008</v>
       </c>
       <c r="J170" s="4">
-        <f t="shared" ref="J170:J171" si="192">F170*E170</f>
+        <f>F170*E170</f>
         <v>29.0140788</v>
       </c>
       <c r="K170" s="4">
-        <f t="shared" ref="K170:K171" si="193">H170*G170</f>
+        <f>H170*G170</f>
         <v>24.125534999999999</v>
       </c>
       <c r="L170" s="4">
-        <f t="shared" ref="L170:L171" si="194">J170-K170</f>
+        <f>J170-K170</f>
         <v>4.8885438000000008</v>
       </c>
       <c r="M170" s="4">
-        <f t="shared" ref="M170:M171" si="195">K170/J170</f>
+        <f>K170/J170</f>
         <v>0.83151132132445993</v>
       </c>
       <c r="N170" s="6">
@@ -7871,7 +11508,7 @@
     </row>
     <row r="171" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B171" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C171" s="4">
@@ -7879,7 +11516,7 @@
         <v>4</v>
       </c>
       <c r="D171" s="4" t="str">
-        <f t="shared" ref="D171:D179" si="196">TEXT(ROUND(E171,3),"#")&amp;"_"&amp;TEXT(B171,"0,###")</f>
+        <f>TEXT(ROUND(E171,3),"#")&amp;"_"&amp;TEXT(B171,"0,###")</f>
         <v>9_0,375</v>
       </c>
       <c r="E171" s="6">
@@ -7895,23 +11532,23 @@
         <v>1.3471</v>
       </c>
       <c r="I171" s="4">
-        <f t="shared" ref="I171" si="197">G171/E171</f>
+        <f>G171/E171</f>
         <v>3.7435595629386165</v>
       </c>
       <c r="J171" s="4">
-        <f t="shared" si="192"/>
+        <f>F171*E171</f>
         <v>55.035923279999999</v>
       </c>
       <c r="K171" s="4">
-        <f t="shared" si="193"/>
+        <f>H171*G171</f>
         <v>45.414782299999999</v>
       </c>
       <c r="L171" s="4">
-        <f t="shared" si="194"/>
+        <f>J171-K171</f>
         <v>9.6211409799999998</v>
       </c>
       <c r="M171" s="4">
-        <f t="shared" si="195"/>
+        <f>K171/J171</f>
         <v>0.82518434494045612</v>
       </c>
       <c r="N171" s="6">
@@ -7934,15 +11571,15 @@
     </row>
     <row r="173" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B173" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C173" s="4">
-        <f t="shared" ref="C173:C176" si="198">1/(1-2*B173)</f>
+        <f>1/(1-2*B173)</f>
         <v>4</v>
       </c>
       <c r="D173" s="4" t="str">
-        <f t="shared" si="196"/>
+        <f>TEXT(ROUND(E173,3),"#")&amp;"_"&amp;TEXT(B173,"0,###")</f>
         <v>12_0,375</v>
       </c>
       <c r="E173" s="7">
@@ -7958,15 +11595,15 @@
         <v>0.49029</v>
       </c>
       <c r="I173" s="4">
-        <f t="shared" ref="I173:I176" si="199">G173/E173</f>
+        <f>G173/E173</f>
         <v>4.0641995841995842</v>
       </c>
       <c r="J173" s="4">
-        <f t="shared" ref="J173:J176" si="200">F173*E173</f>
+        <f>F173*E173</f>
         <v>28.932150000000004</v>
       </c>
       <c r="K173" s="4">
-        <f t="shared" ref="K173:K176" si="201">H173*G173</f>
+        <f>H173*G173</f>
         <v>23.96145288</v>
       </c>
       <c r="L173" s="4">
@@ -7983,15 +11620,15 @@
     </row>
     <row r="174" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B174" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C174" s="4">
-        <f t="shared" si="198"/>
+        <f>1/(1-2*B174)</f>
         <v>4</v>
       </c>
       <c r="D174" s="4" t="str">
-        <f t="shared" si="196"/>
+        <f>TEXT(ROUND(E174,3),"#")&amp;"_"&amp;TEXT(B174,"0,###")</f>
         <v>12_0,375</v>
       </c>
       <c r="E174" s="7">
@@ -8007,23 +11644,23 @@
         <v>0.63936000000000004</v>
       </c>
       <c r="I174" s="4">
-        <f t="shared" si="199"/>
+        <f>G174/E174</f>
         <v>4.0037446950153948</v>
       </c>
       <c r="J174" s="4">
-        <f t="shared" si="200"/>
+        <f>F174*E174</f>
         <v>36.770818299999995</v>
       </c>
       <c r="K174" s="4">
-        <f t="shared" si="201"/>
+        <f>H174*G174</f>
         <v>30.76152768</v>
       </c>
       <c r="L174" s="4">
-        <f t="shared" ref="L174:L176" si="202">J174-K174</f>
+        <f>J174-K174</f>
         <v>6.0092906199999945</v>
       </c>
       <c r="M174" s="4">
-        <f t="shared" ref="M174:M176" si="203">K174/J174</f>
+        <f>K174/J174</f>
         <v>0.83657446589922657</v>
       </c>
       <c r="N174" s="6">
@@ -8032,15 +11669,15 @@
     </row>
     <row r="175" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B175" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C175" s="4">
-        <f t="shared" si="198"/>
+        <f>1/(1-2*B175)</f>
         <v>4</v>
       </c>
       <c r="D175" s="4" t="str">
-        <f t="shared" si="196"/>
+        <f>TEXT(ROUND(E175,3),"#")&amp;"_"&amp;TEXT(B175,"0,###")</f>
         <v>12_0,375</v>
       </c>
       <c r="E175" s="7">
@@ -8056,23 +11693,23 @@
         <v>0.94730000000000003</v>
       </c>
       <c r="I175" s="4">
-        <f t="shared" si="199"/>
+        <f>G175/E175</f>
         <v>3.9426078703973495</v>
       </c>
       <c r="J175" s="4">
-        <f t="shared" si="200"/>
+        <f>F175*E175</f>
         <v>53.089878370000001</v>
       </c>
       <c r="K175" s="4">
-        <f t="shared" si="201"/>
+        <f>H175*G175</f>
         <v>44.863180700000001</v>
       </c>
       <c r="L175" s="4">
-        <f t="shared" si="202"/>
+        <f>J175-K175</f>
         <v>8.2266976700000001</v>
       </c>
       <c r="M175" s="4">
-        <f t="shared" si="203"/>
+        <f>K175/J175</f>
         <v>0.8450420697394414</v>
       </c>
       <c r="N175" s="6">
@@ -8081,15 +11718,15 @@
     </row>
     <row r="176" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B176" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C176" s="4">
-        <f t="shared" si="198"/>
+        <f>1/(1-2*B176)</f>
         <v>4</v>
       </c>
       <c r="D176" s="4" t="str">
-        <f t="shared" si="196"/>
+        <f>TEXT(ROUND(E176,3),"#")&amp;"_"&amp;TEXT(B176,"0,###")</f>
         <v>12_0,375</v>
       </c>
       <c r="E176" s="7">
@@ -8105,23 +11742,23 @@
         <v>1.3089999999999999</v>
       </c>
       <c r="I176" s="4">
-        <f t="shared" si="199"/>
+        <f>G176/E176</f>
         <v>3.9085974725502379</v>
       </c>
       <c r="J176" s="4">
-        <f t="shared" si="200"/>
+        <f>F176*E176</f>
         <v>72.932349750000014</v>
       </c>
       <c r="K176" s="4">
-        <f t="shared" si="201"/>
+        <f>H176*G176</f>
         <v>61.741602999999998</v>
       </c>
       <c r="L176" s="4">
-        <f t="shared" si="202"/>
+        <f>J176-K176</f>
         <v>11.190746750000017</v>
       </c>
       <c r="M176" s="4">
-        <f t="shared" si="203"/>
+        <f>K176/J176</f>
         <v>0.84655990396086178</v>
       </c>
       <c r="N176" s="6">
@@ -8130,15 +11767,15 @@
     </row>
     <row r="178" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B178" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C178" s="4">
-        <f t="shared" ref="C178" si="204">1/(1-2*B178)</f>
+        <f>1/(1-2*B178)</f>
         <v>4</v>
       </c>
       <c r="D178" s="4" t="str">
-        <f t="shared" si="196"/>
+        <f>TEXT(ROUND(E178,3),"#")&amp;"_"&amp;TEXT(B178,"0,###")</f>
         <v>24_0,375</v>
       </c>
       <c r="E178" s="7">
@@ -8154,15 +11791,15 @@
         <v>1.0111000000000001</v>
       </c>
       <c r="I178" s="4">
-        <f t="shared" ref="I178" si="205">G178/E178</f>
+        <f>G178/E178</f>
         <v>4.2047531992687386</v>
       </c>
       <c r="J178" s="4">
-        <f t="shared" ref="J178" si="206">F178*E178</f>
+        <f>F178*E178</f>
         <v>120.35465959999999</v>
       </c>
       <c r="K178" s="4">
-        <f t="shared" ref="K178" si="207">H178*G178</f>
+        <f>H178*G178</f>
         <v>102.09076700000001</v>
       </c>
       <c r="L178" s="4">
@@ -8179,15 +11816,15 @@
     </row>
     <row r="179" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B179" s="7">
-        <f t="shared" si="184"/>
+        <f>3/8</f>
         <v>0.375</v>
       </c>
       <c r="C179" s="4">
-        <f t="shared" ref="C179" si="208">1/(1-2*B179)</f>
+        <f>1/(1-2*B179)</f>
         <v>4</v>
       </c>
       <c r="D179" s="4" t="str">
-        <f t="shared" si="196"/>
+        <f>TEXT(ROUND(E179,3),"#")&amp;"_"&amp;TEXT(B179,"0,###")</f>
         <v>24_0,375</v>
       </c>
       <c r="E179" s="7">
@@ -8203,15 +11840,15 @@
         <v>1.2577</v>
       </c>
       <c r="I179" s="4">
-        <f t="shared" ref="I179" si="209">G179/E179</f>
+        <f>G179/E179</f>
         <v>4.1702711695225414</v>
       </c>
       <c r="J179" s="4">
-        <f t="shared" ref="J179" si="210">F179*E179</f>
+        <f>F179*E179</f>
         <v>147.29113960000001</v>
       </c>
       <c r="K179" s="4">
-        <f t="shared" ref="K179" si="211">H179*G179</f>
+        <f>H179*G179</f>
         <v>126.109579</v>
       </c>
       <c r="L179" s="4">
@@ -8283,7 +11920,7 @@
         <v>5.0000000000000009</v>
       </c>
       <c r="D182" s="4" t="str">
-        <f t="shared" ref="D182:D184" si="212">TEXT(ROUND(E182,3),"#,#")&amp;"_"&amp;TEXT(B182,"0,###")</f>
+        <f>TEXT(ROUND(E182,3),"#,#")&amp;"_"&amp;TEXT(B182,"0,###")</f>
         <v>3,3_0,4</v>
       </c>
       <c r="E182" s="7">
@@ -8311,11 +11948,11 @@
         <v>3.8870171199999999</v>
       </c>
       <c r="L182" s="4">
-        <f t="shared" ref="L182:L185" si="213">J182-K182</f>
+        <f>J182-K182</f>
         <v>1.5373279099999997</v>
       </c>
       <c r="M182" s="4">
-        <f t="shared" ref="M182:M184" si="214">K182/J182</f>
+        <f>K182/J182</f>
         <v>0.71658736649353594</v>
       </c>
       <c r="N182" s="6">
@@ -8331,7 +11968,7 @@
         <v>5.0000000000000009</v>
       </c>
       <c r="D183" s="4" t="str">
-        <f t="shared" si="212"/>
+        <f>TEXT(ROUND(E183,3),"#,#")&amp;"_"&amp;TEXT(B183,"0,###")</f>
         <v>3,3_0,4</v>
       </c>
       <c r="E183" s="7">
@@ -8359,11 +11996,11 @@
         <v>6.7311500999999998</v>
       </c>
       <c r="L183" s="4">
-        <f t="shared" si="213"/>
+        <f>J183-K183</f>
         <v>2.9953279299999993</v>
       </c>
       <c r="M183" s="4">
-        <f t="shared" si="214"/>
+        <f>K183/J183</f>
         <v>0.692043931959614</v>
       </c>
       <c r="N183" s="6">
@@ -8379,7 +12016,7 @@
         <v>5.0000000000000009</v>
       </c>
       <c r="D184" s="4" t="str">
-        <f t="shared" si="212"/>
+        <f>TEXT(ROUND(E184,3),"#,#")&amp;"_"&amp;TEXT(B184,"0,###")</f>
         <v>3,3_0,4</v>
       </c>
       <c r="E184" s="7">
@@ -8407,11 +12044,11 @@
         <v>10.936458242999999</v>
       </c>
       <c r="L184" s="4">
-        <f t="shared" si="213"/>
+        <f>J184-K184</f>
         <v>6.2459817570000009</v>
       </c>
       <c r="M184" s="4">
-        <f t="shared" si="214"/>
+        <f>K184/J184</f>
         <v>0.63649040782333588</v>
       </c>
       <c r="N184" s="6">
@@ -8455,7 +12092,7 @@
         <v>12.320879999999999</v>
       </c>
       <c r="L185" s="4">
-        <f t="shared" si="213"/>
+        <f>J185-K185</f>
         <v>7.5306308000000008</v>
       </c>
       <c r="M185" s="4">
@@ -8523,7 +12160,7 @@
         <v>5.0000000000000009</v>
       </c>
       <c r="D188" s="4" t="str">
-        <f t="shared" ref="D188:D190" si="215">TEXT(ROUND(E188,3),"#")&amp;"_"&amp;TEXT(B188,"0,###")</f>
+        <f>TEXT(ROUND(E188,3),"#")&amp;"_"&amp;TEXT(B188,"0,###")</f>
         <v>5_0,4</v>
       </c>
       <c r="E188" s="7">
@@ -8551,11 +12188,11 @@
         <v>7.0451251000000008</v>
       </c>
       <c r="L188" s="4">
-        <f t="shared" ref="L188:L190" si="216">J188-K188</f>
+        <f>J188-K188</f>
         <v>2.1727035299999988</v>
       </c>
       <c r="M188" s="4">
-        <f t="shared" ref="M188:M190" si="217">K188/J188</f>
+        <f>K188/J188</f>
         <v>0.76429334746701638</v>
       </c>
       <c r="N188" s="6">
@@ -8571,7 +12208,7 @@
         <v>5.0000000000000009</v>
       </c>
       <c r="D189" s="4" t="str">
-        <f t="shared" si="215"/>
+        <f>TEXT(ROUND(E189,3),"#")&amp;"_"&amp;TEXT(B189,"0,###")</f>
         <v>5_0,4</v>
       </c>
       <c r="E189" s="7">
@@ -8599,11 +12236,11 @@
         <v>12.784231499999999</v>
       </c>
       <c r="L189" s="4">
-        <f t="shared" si="216"/>
+        <f>J189-K189</f>
         <v>3.9372915000000024</v>
       </c>
       <c r="M189" s="4">
-        <f t="shared" si="217"/>
+        <f>K189/J189</f>
         <v>0.76453750654171859</v>
       </c>
       <c r="N189" s="6">
@@ -8619,7 +12256,7 @@
         <v>5.0000000000000009</v>
       </c>
       <c r="D190" s="4" t="str">
-        <f t="shared" si="215"/>
+        <f>TEXT(ROUND(E190,3),"#")&amp;"_"&amp;TEXT(B190,"0,###")</f>
         <v>5_0,4</v>
       </c>
       <c r="E190" s="7">
@@ -8647,11 +12284,11 @@
         <v>22.102320000000002</v>
       </c>
       <c r="L190" s="4">
-        <f t="shared" si="216"/>
+        <f>J190-K190</f>
         <v>8.121929999999999</v>
       </c>
       <c r="M190" s="4">
-        <f t="shared" si="217"/>
+        <f>K190/J190</f>
         <v>0.73127769919849128</v>
       </c>
       <c r="N190" s="6">
@@ -8735,19 +12372,19 @@
         <v>4.9915117891816925</v>
       </c>
       <c r="J193" s="4">
-        <f t="shared" ref="J193" si="218">F193*E193</f>
+        <f>F193*E193</f>
         <v>28.05681375</v>
       </c>
       <c r="K193" s="4">
-        <f t="shared" ref="K193" si="219">H193*G193</f>
+        <f>H193*G193</f>
         <v>22.48265322</v>
       </c>
       <c r="L193" s="4">
-        <f t="shared" ref="L193" si="220">J193-K193</f>
+        <f>J193-K193</f>
         <v>5.5741605300000003</v>
       </c>
       <c r="M193" s="4">
-        <f t="shared" ref="M193" si="221">K193/J193</f>
+        <f>K193/J193</f>
         <v>0.80132596025804959</v>
       </c>
       <c r="N193" s="6">
@@ -8783,19 +12420,19 @@
         <v>4.9529349080898672</v>
       </c>
       <c r="J194" s="4">
-        <f t="shared" ref="J194" si="222">F194*E194</f>
+        <f>F194*E194</f>
         <v>35.199183360000006</v>
       </c>
       <c r="K194" s="4">
-        <f t="shared" ref="K194" si="223">H194*G194</f>
+        <f>H194*G194</f>
         <v>28.351101799999999</v>
       </c>
       <c r="L194" s="4">
-        <f t="shared" ref="L194" si="224">J194-K194</f>
+        <f>J194-K194</f>
         <v>6.8480815600000078</v>
       </c>
       <c r="M194" s="4">
-        <f t="shared" ref="M194" si="225">K194/J194</f>
+        <f>K194/J194</f>
         <v>0.80544771479607402</v>
       </c>
       <c r="N194" s="6">
@@ -8811,7 +12448,7 @@
         <v>5.0000000000000009</v>
       </c>
       <c r="D195" s="4" t="str">
-        <f t="shared" ref="D195" si="226">TEXT(ROUND(E195,3),"#")&amp;"_"&amp;TEXT(B195,"0,###")</f>
+        <f>TEXT(ROUND(E195,3),"#")&amp;"_"&amp;TEXT(B195,"0,###")</f>
         <v>9_0,4</v>
       </c>
       <c r="E195" s="6">
@@ -8827,7 +12464,7 @@
         <v>0.87346000000000001</v>
       </c>
       <c r="I195" s="4">
-        <f t="shared" ref="I195" si="227">G195/E195</f>
+        <f>G195/E195</f>
         <v>4.8517403428469859</v>
       </c>
       <c r="J195" s="4">
@@ -8858,7 +12495,7 @@
         <v>0.4</v>
       </c>
       <c r="C197" s="4">
-        <f t="shared" ref="C197:C200" si="228">1/(1-2*B197)</f>
+        <f>1/(1-2*B197)</f>
         <v>5.0000000000000009</v>
       </c>
       <c r="D197" s="4" t="str">
@@ -8882,11 +12519,11 @@
         <v>5.1454604512480531</v>
       </c>
       <c r="J197" s="4">
-        <f t="shared" ref="J197" si="229">F197*E197</f>
+        <f>F197*E197</f>
         <v>39.748180350000005</v>
       </c>
       <c r="K197" s="4">
-        <f t="shared" ref="K197" si="230">H197*G197</f>
+        <f>H197*G197</f>
         <v>31.683255199999998</v>
       </c>
       <c r="L197" s="4">
@@ -8906,11 +12543,11 @@
         <v>0.4</v>
       </c>
       <c r="C198" s="4">
-        <f t="shared" si="228"/>
+        <f>1/(1-2*B198)</f>
         <v>5.0000000000000009</v>
       </c>
       <c r="D198" s="4" t="str">
-        <f t="shared" ref="D198:D200" si="231">TEXT(ROUND(E198,3),"#")&amp;"_"&amp;TEXT(B198,"0,##")</f>
+        <f>TEXT(ROUND(E198,3),"#")&amp;"_"&amp;TEXT(B198,"0,##")</f>
         <v>12_0,4</v>
       </c>
       <c r="E198" s="7">
@@ -8926,23 +12563,23 @@
         <v>0.67900000000000005</v>
       </c>
       <c r="I198" s="4">
-        <f t="shared" ref="I198:I200" si="232">G198/E198</f>
+        <f>G198/E198</f>
         <v>5.1035028530967557</v>
       </c>
       <c r="J198" s="4">
-        <f t="shared" ref="J198:J200" si="233">F198*E198</f>
+        <f>F198*E198</f>
         <v>51.283224000000004</v>
       </c>
       <c r="K198" s="4">
-        <f t="shared" ref="K198:K200" si="234">H198*G198</f>
+        <f>H198*G198</f>
         <v>41.598935000000004</v>
       </c>
       <c r="L198" s="4">
-        <f t="shared" ref="L198:L200" si="235">J198-K198</f>
+        <f>J198-K198</f>
         <v>9.6842889999999997</v>
       </c>
       <c r="M198" s="4">
-        <f t="shared" ref="M198:M200" si="236">K198/J198</f>
+        <f>K198/J198</f>
         <v>0.81116068287750398</v>
       </c>
       <c r="N198" s="6">
@@ -8954,11 +12591,11 @@
         <v>0.4</v>
       </c>
       <c r="C199" s="4">
-        <f t="shared" si="228"/>
+        <f>1/(1-2*B199)</f>
         <v>5.0000000000000009</v>
       </c>
       <c r="D199" s="4" t="str">
-        <f t="shared" si="231"/>
+        <f>TEXT(ROUND(E199,3),"#")&amp;"_"&amp;TEXT(B199,"0,##")</f>
         <v>12_0,4</v>
       </c>
       <c r="E199" s="7">
@@ -8974,23 +12611,23 @@
         <v>0.86529</v>
       </c>
       <c r="I199" s="4">
-        <f t="shared" si="232"/>
+        <f>G199/E199</f>
         <v>5.0516666666666667</v>
       </c>
       <c r="J199" s="4">
-        <f t="shared" si="233"/>
+        <f>F199*E199</f>
         <v>64.078800000000001</v>
       </c>
       <c r="K199" s="4">
-        <f t="shared" si="234"/>
+        <f>H199*G199</f>
         <v>52.453879799999996</v>
       </c>
       <c r="L199" s="4">
-        <f t="shared" si="235"/>
+        <f>J199-K199</f>
         <v>11.624920200000005</v>
       </c>
       <c r="M199" s="4">
-        <f t="shared" si="236"/>
+        <f>K199/J199</f>
         <v>0.81858399033689766</v>
       </c>
       <c r="N199" s="6">
@@ -9002,11 +12639,11 @@
         <v>0.4</v>
       </c>
       <c r="C200" s="4">
-        <f t="shared" si="228"/>
+        <f>1/(1-2*B200)</f>
         <v>5.0000000000000009</v>
       </c>
       <c r="D200" s="4" t="str">
-        <f t="shared" si="231"/>
+        <f>TEXT(ROUND(E200,3),"#")&amp;"_"&amp;TEXT(B200,"0,##")</f>
         <v>12_0,4</v>
       </c>
       <c r="E200" s="7">
@@ -9022,23 +12659,23 @@
         <v>1.00624</v>
       </c>
       <c r="I200" s="4">
-        <f t="shared" si="232"/>
+        <f>G200/E200</f>
         <v>5.0235269623152199</v>
       </c>
       <c r="J200" s="4">
-        <f t="shared" si="233"/>
+        <f>F200*E200</f>
         <v>73.936181250000004</v>
       </c>
       <c r="K200" s="4">
-        <f t="shared" si="234"/>
+        <f>H200*G200</f>
         <v>60.696396800000002</v>
       </c>
       <c r="L200" s="4">
-        <f t="shared" si="235"/>
+        <f>J200-K200</f>
         <v>13.239784450000002</v>
       </c>
       <c r="M200" s="4">
-        <f t="shared" si="236"/>
+        <f>K200/J200</f>
         <v>0.82092956078929213</v>
       </c>
       <c r="N200" s="6">
@@ -9096,7 +12733,7 @@
     </row>
     <row r="203" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B203" s="7">
-        <f t="shared" ref="B203:B216" si="237">3/7</f>
+        <f>3/7</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="C203" s="4">
@@ -9104,7 +12741,7 @@
         <v>6.9999999999999973</v>
       </c>
       <c r="D203" s="4" t="str">
-        <f t="shared" ref="D203:D205" si="238">TEXT(ROUND(E203,3),"#,#")&amp;"_"&amp;TEXT(B203,"0,###")</f>
+        <f>TEXT(ROUND(E203,3),"#,#")&amp;"_"&amp;TEXT(B203,"0,###")</f>
         <v>3,3_0,429</v>
       </c>
       <c r="E203" s="7">
@@ -9132,11 +12769,11 @@
         <v>4.7264663000000002</v>
       </c>
       <c r="L203" s="4">
-        <f t="shared" ref="L203:L205" si="239">J203-K203</f>
+        <f>J203-K203</f>
         <v>2.2512406500000006</v>
       </c>
       <c r="M203" s="4">
-        <f t="shared" ref="M203:M205" si="240">K203/J203</f>
+        <f>K203/J203</f>
         <v>0.67736669565923802</v>
       </c>
       <c r="N203" s="6">
@@ -9145,7 +12782,7 @@
     </row>
     <row r="204" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B204" s="7">
-        <f t="shared" si="237"/>
+        <f>3/7</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="C204" s="4">
@@ -9153,7 +12790,7 @@
         <v>6.9999999999999973</v>
       </c>
       <c r="D204" s="4" t="str">
-        <f t="shared" si="238"/>
+        <f>TEXT(ROUND(E204,3),"#,#")&amp;"_"&amp;TEXT(B204,"0,###")</f>
         <v>3,3_0,429</v>
       </c>
       <c r="E204" s="7">
@@ -9181,11 +12818,11 @@
         <v>7.9287394230000006</v>
       </c>
       <c r="L204" s="4">
-        <f t="shared" si="239"/>
+        <f>J204-K204</f>
         <v>4.093923446999999</v>
       </c>
       <c r="M204" s="4">
-        <f t="shared" si="240"/>
+        <f>K204/J204</f>
         <v>0.65948280416183713</v>
       </c>
       <c r="N204" s="6">
@@ -9194,7 +12831,7 @@
     </row>
     <row r="205" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B205" s="7">
-        <f t="shared" si="237"/>
+        <f>3/7</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="C205" s="4">
@@ -9202,7 +12839,7 @@
         <v>6.9999999999999973</v>
       </c>
       <c r="D205" s="4" t="str">
-        <f t="shared" si="238"/>
+        <f>TEXT(ROUND(E205,3),"#,#")&amp;"_"&amp;TEXT(B205,"0,###")</f>
         <v>3,3_0,429</v>
       </c>
       <c r="E205" s="7">
@@ -9230,11 +12867,11 @@
         <v>12.1981626</v>
       </c>
       <c r="L205" s="4">
-        <f t="shared" si="239"/>
+        <f>J205-K205</f>
         <v>7.364132399999999</v>
       </c>
       <c r="M205" s="4">
-        <f t="shared" si="240"/>
+        <f>K205/J205</f>
         <v>0.62355478229931616</v>
       </c>
       <c r="N205" s="6">
@@ -9305,7 +12942,7 @@
     </row>
     <row r="208" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B208" s="7">
-        <f t="shared" si="237"/>
+        <f>3/7</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="C208" s="4">
@@ -9354,7 +12991,7 @@
     </row>
     <row r="209" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B209" s="7">
-        <f t="shared" si="237"/>
+        <f>3/7</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="C209" s="4">
@@ -9452,7 +13089,7 @@
     </row>
     <row r="212" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B212" s="7">
-        <f t="shared" si="237"/>
+        <f>3/7</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="C212" s="4">
@@ -9480,19 +13117,19 @@
         <v>7.299485732692073</v>
       </c>
       <c r="J212" s="4">
-        <f t="shared" ref="J212:J213" si="241">F212*E212</f>
+        <f>F212*E212</f>
         <v>41.801393300000001</v>
       </c>
       <c r="K212" s="4">
-        <f t="shared" ref="K212:K213" si="242">H212*G212</f>
+        <f>H212*G212</f>
         <v>30.719221920000003</v>
       </c>
       <c r="L212" s="4">
-        <f t="shared" ref="L212:L213" si="243">J212-K212</f>
+        <f>J212-K212</f>
         <v>11.082171379999998</v>
       </c>
       <c r="M212" s="4">
-        <f t="shared" ref="M212:M213" si="244">K212/J212</f>
+        <f>K212/J212</f>
         <v>0.73488511972638004</v>
       </c>
       <c r="N212" s="6">
@@ -9501,7 +13138,7 @@
     </row>
     <row r="213" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B213" s="7">
-        <f t="shared" si="237"/>
+        <f>3/7</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="C213" s="4">
@@ -9509,7 +13146,7 @@
         <v>6.9999999999999973</v>
       </c>
       <c r="D213" s="4" t="str">
-        <f t="shared" ref="D213:D216" si="245">TEXT(ROUND(E213,3),"#")&amp;"_"&amp;TEXT(B213,"0,###")</f>
+        <f>TEXT(ROUND(E213,3),"#")&amp;"_"&amp;TEXT(B213,"0,###")</f>
         <v>9_0,429</v>
       </c>
       <c r="E213" s="6">
@@ -9525,23 +13162,23 @@
         <v>0.61919999999999997</v>
       </c>
       <c r="I213" s="4">
-        <f t="shared" ref="I213" si="246">G213/E213</f>
+        <f>G213/E213</f>
         <v>7.2345980778845611</v>
       </c>
       <c r="J213" s="4">
-        <f t="shared" si="241"/>
+        <f>F213*E213</f>
         <v>53.831990500000003</v>
       </c>
       <c r="K213" s="4">
-        <f t="shared" si="242"/>
+        <f>H213*G213</f>
         <v>40.319207999999996</v>
       </c>
       <c r="L213" s="4">
-        <f t="shared" si="243"/>
+        <f>J213-K213</f>
         <v>13.512782500000007</v>
       </c>
       <c r="M213" s="4">
-        <f t="shared" si="244"/>
+        <f>K213/J213</f>
         <v>0.74898229891759238</v>
       </c>
       <c r="N213" s="6">
@@ -9554,11 +13191,11 @@
         <v>0.42857142857142855</v>
       </c>
       <c r="C215" s="4">
-        <f t="shared" ref="C215:C216" si="247">1/(1-2*B215)</f>
+        <f>1/(1-2*B215)</f>
         <v>6.9999999999999973</v>
       </c>
       <c r="D215" s="4" t="str">
-        <f t="shared" si="245"/>
+        <f>TEXT(ROUND(E215,3),"#")&amp;"_"&amp;TEXT(B215,"0,###")</f>
         <v>12_0,429</v>
       </c>
       <c r="E215" s="7">
@@ -9578,11 +13215,11 @@
         <v>7.6191308691308688</v>
       </c>
       <c r="J215" s="4">
-        <f t="shared" ref="J215:J216" si="248">F215*E215</f>
+        <f>F215*E215</f>
         <v>60.732672000000001</v>
       </c>
       <c r="K215" s="4">
-        <f t="shared" ref="K215:K216" si="249">H215*G215</f>
+        <f>H215*G215</f>
         <v>44.026177050000001</v>
       </c>
       <c r="L215" s="4">
@@ -9599,15 +13236,15 @@
     </row>
     <row r="216" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B216" s="7">
-        <f t="shared" si="237"/>
+        <f>3/7</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="C216" s="4">
-        <f t="shared" si="247"/>
+        <f>1/(1-2*B216)</f>
         <v>6.9999999999999973</v>
       </c>
       <c r="D216" s="4" t="str">
-        <f t="shared" si="245"/>
+        <f>TEXT(ROUND(E216,3),"#")&amp;"_"&amp;TEXT(B216,"0,###")</f>
         <v>12_0,429</v>
       </c>
       <c r="E216" s="7">
@@ -9623,23 +13260,23 @@
         <v>0.60178799999999999</v>
       </c>
       <c r="I216" s="4">
-        <f t="shared" ref="I216" si="250">G216/E216</f>
+        <f>G216/E216</f>
         <v>7.5350000000000001</v>
       </c>
       <c r="J216" s="4">
-        <f t="shared" si="248"/>
+        <f>F216*E216</f>
         <v>73.403999999999996</v>
       </c>
       <c r="K216" s="4">
-        <f t="shared" si="249"/>
+        <f>H216*G216</f>
         <v>54.413670959999997</v>
       </c>
       <c r="L216" s="4">
-        <f t="shared" ref="L216" si="251">J216-K216</f>
+        <f>J216-K216</f>
         <v>18.990329039999999</v>
       </c>
       <c r="M216" s="4">
-        <f t="shared" ref="M216" si="252">K216/J216</f>
+        <f>K216/J216</f>
         <v>0.74129026974006862</v>
       </c>
       <c r="N216" s="6">
@@ -9703,7 +13340,7 @@
         <v>10.000000000000002</v>
       </c>
       <c r="D219" s="4" t="str">
-        <f t="shared" ref="D219:D221" si="253">TEXT(ROUND(E219,3),"#,#")&amp;"_"&amp;TEXT(B219,"0,##")</f>
+        <f>TEXT(ROUND(E219,3),"#,#")&amp;"_"&amp;TEXT(B219,"0,##")</f>
         <v>3,3_0,45</v>
       </c>
       <c r="E219" s="7">
@@ -9731,11 +13368,11 @@
         <v>5.7340043100000004</v>
       </c>
       <c r="L219" s="4">
-        <f t="shared" ref="L219:L221" si="254">J219-K219</f>
+        <f>J219-K219</f>
         <v>3.8911284900000007</v>
       </c>
       <c r="M219" s="4">
-        <f t="shared" ref="M219:M221" si="255">K219/J219</f>
+        <f>K219/J219</f>
         <v>0.59573248797149059</v>
       </c>
       <c r="N219" s="6">
@@ -9751,7 +13388,7 @@
         <v>10.000000000000002</v>
       </c>
       <c r="D220" s="4" t="str">
-        <f t="shared" si="253"/>
+        <f>TEXT(ROUND(E220,3),"#,#")&amp;"_"&amp;TEXT(B220,"0,##")</f>
         <v>3,3_0,45</v>
       </c>
       <c r="E220" s="7">
@@ -9779,11 +13416,11 @@
         <v>8.17730991</v>
       </c>
       <c r="L220" s="4">
-        <f t="shared" si="254"/>
+        <f>J220-K220</f>
         <v>5.4686106900000002</v>
       </c>
       <c r="M220" s="4">
-        <f t="shared" si="255"/>
+        <f>K220/J220</f>
         <v>0.5992494130443643</v>
       </c>
       <c r="N220" s="6">
@@ -9799,7 +13436,7 @@
         <v>10.000000000000002</v>
       </c>
       <c r="D221" s="4" t="str">
-        <f t="shared" si="253"/>
+        <f>TEXT(ROUND(E221,3),"#,#")&amp;"_"&amp;TEXT(B221,"0,##")</f>
         <v>3,3_0,45</v>
       </c>
       <c r="E221" s="7">
@@ -9827,11 +13464,11 @@
         <v>11.70476762</v>
       </c>
       <c r="L221" s="4">
-        <f t="shared" si="254"/>
+        <f>J221-K221</f>
         <v>8.3894413799999992</v>
       </c>
       <c r="M221" s="4">
-        <f t="shared" si="255"/>
+        <f>K221/J221</f>
         <v>0.58249456945530931</v>
       </c>
       <c r="N221" s="6">
@@ -9895,7 +13532,7 @@
         <v>10.000000000000002</v>
       </c>
       <c r="D224" s="4" t="str">
-        <f t="shared" ref="D224" si="256">TEXT(ROUND(E224,3),"#")&amp;"_"&amp;TEXT(B224,"0,###")</f>
+        <f>TEXT(ROUND(E224,3),"#")&amp;"_"&amp;TEXT(B224,"0,###")</f>
         <v>5_0,45</v>
       </c>
       <c r="E224" s="7">
@@ -9923,11 +13560,11 @@
         <v>12.71081</v>
       </c>
       <c r="L224" s="4">
-        <f t="shared" ref="L224" si="257">J224-K224</f>
+        <f>J224-K224</f>
         <v>7.8897137999999973</v>
       </c>
       <c r="M224" s="4">
-        <f t="shared" ref="M224" si="258">K224/J224</f>
+        <f>K224/J224</f>
         <v>0.6170139227236543</v>
       </c>
       <c r="N224" s="6">
@@ -9943,7 +13580,7 @@
         <v>10.000000000000002</v>
       </c>
       <c r="D225" s="4" t="str">
-        <f t="shared" ref="D225:D226" si="259">TEXT(ROUND(E225,3),"#")&amp;"_"&amp;TEXT(B225,"0,###")</f>
+        <f>TEXT(ROUND(E225,3),"#")&amp;"_"&amp;TEXT(B225,"0,###")</f>
         <v>5_0,45</v>
       </c>
       <c r="E225" s="7">
@@ -9971,11 +13608,11 @@
         <v>16.137384000000001</v>
       </c>
       <c r="L225" s="4">
-        <f t="shared" ref="L225:L226" si="260">J225-K225</f>
+        <f>J225-K225</f>
         <v>9.4229430000000001</v>
       </c>
       <c r="M225" s="4">
-        <f t="shared" ref="M225:M226" si="261">K225/J225</f>
+        <f>K225/J225</f>
         <v>0.63134497457720318</v>
       </c>
       <c r="N225" s="6">
@@ -9991,7 +13628,7 @@
         <v>10.000000000000002</v>
       </c>
       <c r="D226" s="4" t="str">
-        <f t="shared" si="259"/>
+        <f>TEXT(ROUND(E226,3),"#")&amp;"_"&amp;TEXT(B226,"0,###")</f>
         <v>5_0,45</v>
       </c>
       <c r="E226" s="7">
@@ -10019,11 +13656,11 @@
         <v>18.9244512</v>
       </c>
       <c r="L226" s="4">
-        <f t="shared" si="260"/>
+        <f>J226-K226</f>
         <v>10.851502800000002</v>
       </c>
       <c r="M226" s="4">
-        <f t="shared" si="261"/>
+        <f>K226/J226</f>
         <v>0.63556154069824256</v>
       </c>
       <c r="N226" s="6">
@@ -10035,7 +13672,7 @@
         <v>0.45</v>
       </c>
       <c r="C228" s="4">
-        <f t="shared" ref="C228:C229" si="262">1/(1-2*B228)</f>
+        <f>1/(1-2*B228)</f>
         <v>10.000000000000002</v>
       </c>
       <c r="D228" s="4" t="str">
@@ -10059,11 +13696,11 @@
         <v>11.418596918984818</v>
       </c>
       <c r="J228" s="4">
-        <f t="shared" ref="J228:J229" si="263">F228*E228</f>
+        <f>F228*E228</f>
         <v>51.070180000000001</v>
       </c>
       <c r="K228" s="4">
-        <f t="shared" ref="K228:K229" si="264">H228*G228</f>
+        <f>H228*G228</f>
         <v>30.1033054</v>
       </c>
       <c r="L228" s="4">
@@ -10083,11 +13720,11 @@
         <v>0.45</v>
       </c>
       <c r="C229" s="4">
-        <f t="shared" si="262"/>
+        <f>1/(1-2*B229)</f>
         <v>10.000000000000002</v>
       </c>
       <c r="D229" s="4" t="str">
-        <f t="shared" ref="D229" si="265">TEXT(ROUND(E229,3),"#")&amp;"_"&amp;TEXT(B229,"0,##")</f>
+        <f>TEXT(ROUND(E229,3),"#")&amp;"_"&amp;TEXT(B229,"0,##")</f>
         <v>9_0,45</v>
       </c>
       <c r="E229" s="7">
@@ -10103,23 +13740,23 @@
         <v>0.32579999999999998</v>
       </c>
       <c r="I229" s="4">
-        <f t="shared" ref="I229" si="266">G229/E229</f>
+        <f>G229/E229</f>
         <v>11.339136257114161</v>
       </c>
       <c r="J229" s="4">
-        <f t="shared" si="263"/>
+        <f>F229*E229</f>
         <v>54.913008000000005</v>
       </c>
       <c r="K229" s="4">
-        <f t="shared" si="264"/>
+        <f>H229*G229</f>
         <v>33.104537999999998</v>
       </c>
       <c r="L229" s="4">
-        <f t="shared" ref="L229" si="267">J229-K229</f>
+        <f>J229-K229</f>
         <v>21.808470000000007</v>
       </c>
       <c r="M229" s="4">
-        <f t="shared" ref="M229" si="268">K229/J229</f>
+        <f>K229/J229</f>
         <v>0.60285420896994013</v>
       </c>
       <c r="N229" s="6">
@@ -10132,7 +13769,8 @@
     <mergeCell ref="I6:M6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -10253,19 +13891,19 @@
       <c r="D6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="19" t="s">
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
       <c r="N6" s="6" t="s">
         <v>30</v>
       </c>
@@ -12153,49 +15791,49 @@
       </c>
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B50" s="6">
+      <c r="B50" s="18">
         <v>0.26300000000000001</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D50" s="4" t="str">
+      <c r="D50" s="20" t="str">
         <f>TEXT(ROUND(E50,3),"#,#")&amp;"_"&amp;TEXT(G50,"0")</f>
         <v>12,_24</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E50" s="21">
         <v>12.0039</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F50" s="21">
         <v>2.6869900000000002</v>
       </c>
-      <c r="G50" s="7">
+      <c r="G50" s="21">
         <v>24.07</v>
       </c>
-      <c r="H50" s="7">
+      <c r="H50" s="21">
         <v>1.19234</v>
       </c>
-      <c r="I50" s="4">
+      <c r="I50" s="20">
         <f t="shared" si="61"/>
         <v>2.0051816492973118</v>
       </c>
-      <c r="J50" s="4">
+      <c r="J50" s="20">
         <f t="shared" si="62"/>
         <v>32.254359261000005</v>
       </c>
-      <c r="K50" s="4">
+      <c r="K50" s="20">
         <f t="shared" si="63"/>
         <v>28.699623799999998</v>
       </c>
-      <c r="L50" s="4">
+      <c r="L50" s="20">
         <f t="shared" si="64"/>
         <v>3.554735461000007</v>
       </c>
-      <c r="M50" s="4">
+      <c r="M50" s="20">
         <f t="shared" si="65"/>
         <v>0.88979054173002359</v>
       </c>
-      <c r="N50" s="6">
+      <c r="N50" s="18">
         <v>20</v>
       </c>
       <c r="O50" s="12" t="str">
@@ -13029,49 +16667,49 @@
       </c>
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B70" s="6">
+      <c r="B70" s="18">
         <v>0.253</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C70" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D70" s="4" t="str">
+      <c r="D70" s="20" t="str">
         <f t="shared" si="101"/>
         <v>24,_48</v>
       </c>
-      <c r="E70" s="7">
+      <c r="E70" s="21">
         <v>24.0136</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F70" s="21">
         <v>4.2225000000000001</v>
       </c>
-      <c r="G70" s="7">
+      <c r="G70" s="21">
         <v>48.113</v>
       </c>
-      <c r="H70" s="7">
+      <c r="H70" s="21">
         <v>1.9397</v>
       </c>
-      <c r="I70" s="4">
+      <c r="I70" s="20">
         <f t="shared" si="96"/>
         <v>2.0035729753139888</v>
       </c>
-      <c r="J70" s="4">
+      <c r="J70" s="20">
         <f t="shared" si="102"/>
         <v>101.39742600000001</v>
       </c>
-      <c r="K70" s="4">
+      <c r="K70" s="20">
         <f t="shared" si="103"/>
         <v>93.324786099999997</v>
       </c>
-      <c r="L70" s="4">
+      <c r="L70" s="20">
         <f t="shared" si="104"/>
         <v>8.0726399000000129</v>
       </c>
-      <c r="M70" s="4">
+      <c r="M70" s="20">
         <f t="shared" si="105"/>
         <v>0.92038614569959587</v>
       </c>
-      <c r="N70" s="6">
+      <c r="N70" s="18">
         <v>25</v>
       </c>
       <c r="O70" s="12" t="str">
@@ -15046,6 +18684,7 @@
     <mergeCell ref="I6:M6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15573,4 +19212,133 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA1FC67-3AFA-4CE4-9F6C-317DA59B97A1}">
+  <dimension ref="A2:G6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="24">
+        <v>26.5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2">
+        <v>24.08</v>
+      </c>
+      <c r="E3" s="2">
+        <v>31.55</v>
+      </c>
+      <c r="F3" s="2">
+        <v>29</v>
+      </c>
+      <c r="G3" s="2">
+        <v>91.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="24">
+        <v>25.8</v>
+      </c>
+      <c r="C4" s="26">
+        <v>24</v>
+      </c>
+      <c r="D4" s="27">
+        <v>47.96</v>
+      </c>
+      <c r="E4" s="2">
+        <v>97.04</v>
+      </c>
+      <c r="F4" s="2">
+        <v>92</v>
+      </c>
+      <c r="G4" s="2">
+        <v>94.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="24">
+        <v>26.3</v>
+      </c>
+      <c r="C5" s="27">
+        <v>12.0039</v>
+      </c>
+      <c r="D5" s="27">
+        <v>24.07</v>
+      </c>
+      <c r="E5" s="27">
+        <v>32.254359261000005</v>
+      </c>
+      <c r="F5" s="27">
+        <v>28.699623799999998</v>
+      </c>
+      <c r="G5" s="28">
+        <v>88.979054173002396</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="24">
+        <v>25.3</v>
+      </c>
+      <c r="C6" s="27">
+        <v>24.0136</v>
+      </c>
+      <c r="D6" s="27">
+        <v>48.113</v>
+      </c>
+      <c r="E6" s="27">
+        <v>101.39742600000001</v>
+      </c>
+      <c r="F6" s="27">
+        <v>93.324786099999997</v>
+      </c>
+      <c r="G6" s="28">
+        <v>92.038614569959606</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>